--- a/macros fac/FAC_ RPNC1-4240426.xlsx
+++ b/macros fac/FAC_ RPNC1-4240426.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Ivan\Documents\gitdocs-2026\macros fac\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3B75B202-94D0-43DC-B04E-FD7ADC89F59D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2A87985C-40D9-43DA-916B-3A3D889C2732}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" tabRatio="682" firstSheet="2" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -100,7 +100,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="501" uniqueCount="367">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="500" uniqueCount="366">
   <si>
     <t>ASP</t>
   </si>
@@ -1350,9 +1350,6 @@
   </si>
   <si>
     <t>RPNC1-4240426</t>
-  </si>
-  <si>
-    <t> CAJAS ITZEP, RAFAEL SALVADOR</t>
   </si>
 </sst>
 </file>
@@ -5646,7 +5643,7 @@
       </c>
       <c r="D8" s="214">
         <f ca="1">TODAY()</f>
-        <v>46173</v>
+        <v>46174</v>
       </c>
       <c r="E8" s="215"/>
       <c r="J8" s="58"/>
@@ -5656,9 +5653,7 @@
       <c r="C9" s="18" t="s">
         <v>118</v>
       </c>
-      <c r="D9" s="212" t="s">
-        <v>366</v>
-      </c>
+      <c r="D9" s="212"/>
       <c r="E9" s="213"/>
       <c r="J9" s="58"/>
     </row>
@@ -6652,9 +6647,9 @@
       <c r="F12" s="77" t="s">
         <v>175</v>
       </c>
-      <c r="G12" s="227" t="str">
+      <c r="G12" s="227">
         <f>FACTIBILIDAD!D9</f>
-        <v> CAJAS ITZEP, RAFAEL SALVADOR</v>
+        <v>0</v>
       </c>
       <c r="H12" s="228"/>
       <c r="I12" s="228"/>
@@ -6686,7 +6681,7 @@
       </c>
       <c r="G14" s="230">
         <f ca="1">FACTIBILIDAD!D8</f>
-        <v>46173</v>
+        <v>46174</v>
       </c>
       <c r="H14" s="231"/>
       <c r="I14" s="231"/>
@@ -7926,7 +7921,7 @@
       </c>
       <c r="G82" s="248">
         <f ca="1">G14</f>
-        <v>46173</v>
+        <v>46174</v>
       </c>
       <c r="H82" s="248"/>
       <c r="I82" s="220" t="s">
@@ -7949,9 +7944,9 @@
         <v>258</v>
       </c>
       <c r="H83" s="219"/>
-      <c r="I83" s="279" t="str">
+      <c r="I83" s="279">
         <f>G12</f>
-        <v> CAJAS ITZEP, RAFAEL SALVADOR</v>
+        <v>0</v>
       </c>
       <c r="J83" s="279"/>
       <c r="K83" s="219" t="s">
@@ -8936,9 +8931,9 @@
       <c r="F12" s="67" t="s">
         <v>175</v>
       </c>
-      <c r="G12" s="287" t="str">
+      <c r="G12" s="287">
         <f>FACTIBILIDAD!D9</f>
-        <v> CAJAS ITZEP, RAFAEL SALVADOR</v>
+        <v>0</v>
       </c>
       <c r="H12" s="288"/>
       <c r="I12" s="288"/>
@@ -8972,7 +8967,7 @@
       </c>
       <c r="G14" s="287">
         <f ca="1">FACTIBILIDAD!D8</f>
-        <v>46173</v>
+        <v>46174</v>
       </c>
       <c r="H14" s="288"/>
       <c r="I14" s="288"/>
@@ -9358,7 +9353,7 @@
       </c>
       <c r="G39" s="308">
         <f ca="1">G14</f>
-        <v>46173</v>
+        <v>46174</v>
       </c>
       <c r="H39" s="308"/>
       <c r="I39" s="309" t="s">
@@ -9382,9 +9377,9 @@
         <v>258</v>
       </c>
       <c r="H40" s="311"/>
-      <c r="I40" s="311" t="str">
+      <c r="I40" s="311">
         <f>G12</f>
-        <v> CAJAS ITZEP, RAFAEL SALVADOR</v>
+        <v>0</v>
       </c>
       <c r="J40" s="311"/>
       <c r="K40" s="311" t="s">
@@ -10238,9 +10233,9 @@
       </c>
       <c r="G24" s="197"/>
       <c r="H24" s="197"/>
-      <c r="I24" s="338" t="str">
+      <c r="I24" s="338">
         <f>FACTIBILIDAD!D9</f>
-        <v> CAJAS ITZEP, RAFAEL SALVADOR</v>
+        <v>0</v>
       </c>
       <c r="J24" s="338"/>
       <c r="K24" s="338"/>

--- a/macros fac/FAC_ RPNC1-4240426.xlsx
+++ b/macros fac/FAC_ RPNC1-4240426.xlsx
@@ -5,12 +5,12 @@
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Ubicacion C a D\Documentos\gitdocs-2026\macros fac\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Ivan\Documents\gitdocs-2026\macros fac\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{91FA5EFD-B23A-4CD4-9585-56F14349F6CB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BB046319-A8A1-47BE-903E-2DF27D0CE184}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" tabRatio="682" firstSheet="2" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" tabRatio="682" firstSheet="2" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="menore" sheetId="1" state="hidden" r:id="rId1"/>
@@ -4543,8 +4543,8 @@
       </xdr:nvGrpSpPr>
       <xdr:grpSpPr>
         <a:xfrm>
-          <a:off x="0" y="8949378"/>
-          <a:ext cx="7066188" cy="1158007"/>
+          <a:off x="0" y="9017413"/>
+          <a:ext cx="7036253" cy="1168893"/>
           <a:chOff x="0" y="0"/>
           <a:chExt cx="6918960" cy="1096453"/>
         </a:xfrm>
@@ -5013,14 +5013,14 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr codeName="Hoja1"/>
   <dimension ref="A1:R21"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="48" customWidth="1"/>
-    <col min="4" max="4" width="16.109375" customWidth="1"/>
-    <col min="7" max="8" width="11.44140625" customWidth="1"/>
+    <col min="4" max="4" width="16.140625" customWidth="1"/>
+    <col min="7" max="8" width="11.42578125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A1" s="208" t="s">
         <v>27</v>
       </c>
@@ -5033,7 +5033,7 @@
       <c r="H1" s="208"/>
       <c r="I1" s="208"/>
     </row>
-    <row r="2" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A2" s="7"/>
       <c r="B2" s="7"/>
       <c r="C2" s="7"/>
@@ -5044,7 +5044,7 @@
       <c r="H2" s="7"/>
       <c r="I2" s="7"/>
     </row>
-    <row r="3" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A3" s="7"/>
       <c r="B3" s="7"/>
       <c r="C3" s="7"/>
@@ -5055,7 +5055,7 @@
       <c r="H3" s="7"/>
       <c r="I3" s="7"/>
     </row>
-    <row r="4" spans="1:18" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A4" s="6" t="s">
         <v>0</v>
       </c>
@@ -5070,7 +5070,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="5" spans="1:18" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A5" s="6" t="s">
         <v>2</v>
       </c>
@@ -5105,7 +5105,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="6" spans="1:18" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A6" s="6" t="s">
         <v>4</v>
       </c>
@@ -5138,7 +5138,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="7" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A7" s="6" t="s">
         <v>7</v>
       </c>
@@ -5152,7 +5152,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="8" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A8" s="6" t="s">
         <v>10</v>
       </c>
@@ -5167,7 +5167,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="9" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A9" s="6" t="s">
         <v>14</v>
       </c>
@@ -5185,7 +5185,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="12" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:18" x14ac:dyDescent="0.25">
       <c r="B12" s="6" t="s">
         <v>35</v>
       </c>
@@ -5197,7 +5197,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="13" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:18" x14ac:dyDescent="0.25">
       <c r="B13" s="6" t="s">
         <v>36</v>
       </c>
@@ -5208,7 +5208,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="14" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:18" x14ac:dyDescent="0.25">
       <c r="B14" s="6" t="s">
         <v>37</v>
       </c>
@@ -5223,7 +5223,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="15" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:18" x14ac:dyDescent="0.25">
       <c r="B15" s="6" t="s">
         <v>38</v>
       </c>
@@ -5239,7 +5239,7 @@
         <v>0.1</v>
       </c>
     </row>
-    <row r="16" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A16" s="6"/>
       <c r="B16" s="6" t="s">
         <v>40</v>
@@ -5256,7 +5256,7 @@
       <c r="H16" s="6"/>
       <c r="I16" s="6"/>
     </row>
-    <row r="17" spans="2:6" x14ac:dyDescent="0.3">
+    <row r="17" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B17" s="6" t="s">
         <v>41</v>
       </c>
@@ -5268,7 +5268,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="18" spans="2:6" x14ac:dyDescent="0.3">
+    <row r="18" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B18" s="6" t="s">
         <v>42</v>
       </c>
@@ -5280,7 +5280,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="19" spans="2:6" x14ac:dyDescent="0.3">
+    <row r="19" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B19" s="13" t="s">
         <v>44</v>
       </c>
@@ -5299,7 +5299,7 @@
         <v>3499.9999999999991</v>
       </c>
     </row>
-    <row r="20" spans="2:6" x14ac:dyDescent="0.3">
+    <row r="20" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B20" s="13" t="s">
         <v>45</v>
       </c>
@@ -5310,7 +5310,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="21" spans="2:6" x14ac:dyDescent="0.3">
+    <row r="21" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B21" s="6" t="s">
         <v>46</v>
       </c>
@@ -5361,15 +5361,15 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <sheetPr codeName="Hoja2"/>
   <dimension ref="A1:S19"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="2" width="34.88671875" customWidth="1"/>
+    <col min="2" max="2" width="34.85546875" customWidth="1"/>
     <col min="4" max="4" width="22" bestFit="1" customWidth="1"/>
-    <col min="7" max="8" width="11.44140625" hidden="1" customWidth="1"/>
-    <col min="9" max="9" width="16.33203125" bestFit="1" customWidth="1"/>
+    <col min="7" max="8" width="11.42578125" hidden="1" customWidth="1"/>
+    <col min="9" max="9" width="16.28515625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A1" s="208" t="s">
         <v>28</v>
       </c>
@@ -5382,7 +5382,7 @@
       <c r="H1" s="208"/>
       <c r="I1" s="208"/>
     </row>
-    <row r="2" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A2" s="7"/>
       <c r="B2" s="7"/>
       <c r="C2" s="6"/>
@@ -5393,7 +5393,7 @@
       <c r="H2" s="7"/>
       <c r="I2" s="7"/>
     </row>
-    <row r="3" spans="1:19" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A3" s="7"/>
       <c r="B3" s="7"/>
       <c r="C3" s="6"/>
@@ -5404,7 +5404,7 @@
       <c r="H3" s="7"/>
       <c r="I3" s="7"/>
     </row>
-    <row r="4" spans="1:19" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A4" s="6" t="s">
         <v>8</v>
       </c>
@@ -5422,7 +5422,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="5" spans="1:19" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A5" s="6" t="s">
         <v>2</v>
       </c>
@@ -5457,7 +5457,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="6" spans="1:19" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A6" s="6" t="s">
         <v>4</v>
       </c>
@@ -5490,7 +5490,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="7" spans="1:19" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A7" s="6" t="s">
         <v>7</v>
       </c>
@@ -5504,7 +5504,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="8" spans="1:19" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A8" s="6" t="s">
         <v>14</v>
       </c>
@@ -5522,7 +5522,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="13" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:19" x14ac:dyDescent="0.25">
       <c r="B13" s="6" t="s">
         <v>29</v>
       </c>
@@ -5534,7 +5534,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="14" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:19" x14ac:dyDescent="0.25">
       <c r="B14" s="6" t="s">
         <v>30</v>
       </c>
@@ -5546,7 +5546,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="15" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:19" x14ac:dyDescent="0.25">
       <c r="B15" s="6" t="s">
         <v>32</v>
       </c>
@@ -5563,7 +5563,7 @@
       <c r="H15" s="6"/>
       <c r="I15" s="6"/>
     </row>
-    <row r="19" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="19" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B19" t="s">
         <v>34</v>
       </c>
@@ -5601,21 +5601,21 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <sheetPr codeName="Hoja3"/>
   <dimension ref="A1:J82"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="11.44140625" defaultRowHeight="13.2" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11.42578125" defaultRowHeight="14.25" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="6.44140625" style="56" customWidth="1"/>
-    <col min="2" max="2" width="3.88671875" style="19" customWidth="1"/>
-    <col min="3" max="3" width="51.44140625" style="18" customWidth="1"/>
-    <col min="4" max="4" width="24.44140625" style="24" customWidth="1"/>
-    <col min="5" max="5" width="20.88671875" style="18" customWidth="1"/>
-    <col min="6" max="6" width="42.44140625" style="18" customWidth="1"/>
-    <col min="7" max="7" width="3.6640625" style="18" customWidth="1"/>
-    <col min="8" max="9" width="22.33203125" style="18" hidden="1" customWidth="1"/>
-    <col min="10" max="10" width="6.33203125" style="56" customWidth="1"/>
-    <col min="11" max="16384" width="11.44140625" style="18"/>
+    <col min="1" max="1" width="6.42578125" style="56" customWidth="1"/>
+    <col min="2" max="2" width="3.85546875" style="19" customWidth="1"/>
+    <col min="3" max="3" width="51.42578125" style="18" customWidth="1"/>
+    <col min="4" max="4" width="24.42578125" style="24" customWidth="1"/>
+    <col min="5" max="5" width="20.85546875" style="18" customWidth="1"/>
+    <col min="6" max="6" width="42.42578125" style="18" customWidth="1"/>
+    <col min="7" max="7" width="3.7109375" style="18" customWidth="1"/>
+    <col min="8" max="9" width="22.28515625" style="18" hidden="1" customWidth="1"/>
+    <col min="10" max="10" width="6.28515625" style="56" customWidth="1"/>
+    <col min="11" max="16384" width="11.42578125" style="18"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" ht="13.8" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A1" s="54"/>
       <c r="B1" s="16"/>
       <c r="C1" s="17"/>
@@ -5661,11 +5661,11 @@
       <c r="A6" s="55"/>
       <c r="J6" s="58"/>
     </row>
-    <row r="7" spans="1:10" ht="13.8" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A7" s="55"/>
       <c r="J7" s="58"/>
     </row>
-    <row r="8" spans="1:10" ht="13.8" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A8" s="55"/>
       <c r="C8" s="18" t="s">
         <v>117</v>
@@ -5758,7 +5758,7 @@
       <c r="A16" s="55"/>
       <c r="J16" s="58"/>
     </row>
-    <row r="17" spans="1:10" ht="13.8" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A17" s="55"/>
       <c r="D17" s="32" t="s">
         <v>88</v>
@@ -5784,7 +5784,7 @@
       <c r="E18" s="52"/>
       <c r="J18" s="58"/>
     </row>
-    <row r="19" spans="1:10" ht="13.8" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A19" s="55"/>
       <c r="B19" s="19">
         <v>2</v>
@@ -5797,7 +5797,7 @@
       </c>
       <c r="J19" s="58"/>
     </row>
-    <row r="20" spans="1:10" ht="13.8" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A20" s="55"/>
       <c r="B20" s="19">
         <v>3</v>
@@ -5810,7 +5810,7 @@
       </c>
       <c r="J20" s="58"/>
     </row>
-    <row r="21" spans="1:10" ht="13.8" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A21" s="55"/>
       <c r="B21" s="19">
         <v>4</v>
@@ -5823,7 +5823,7 @@
       </c>
       <c r="J21" s="58"/>
     </row>
-    <row r="22" spans="1:10" ht="13.8" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A22" s="55"/>
       <c r="B22" s="19">
         <v>5</v>
@@ -5836,7 +5836,7 @@
       </c>
       <c r="J22" s="58"/>
     </row>
-    <row r="23" spans="1:10" ht="13.8" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A23" s="55"/>
       <c r="B23" s="19">
         <v>6</v>
@@ -5849,7 +5849,7 @@
       </c>
       <c r="J23" s="58"/>
     </row>
-    <row r="24" spans="1:10" ht="13.8" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A24" s="55"/>
       <c r="B24" s="19">
         <v>7</v>
@@ -5862,7 +5862,7 @@
       </c>
       <c r="J24" s="58"/>
     </row>
-    <row r="25" spans="1:10" ht="13.8" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A25" s="55"/>
       <c r="B25" s="19">
         <v>8</v>
@@ -5875,7 +5875,7 @@
       </c>
       <c r="J25" s="58"/>
     </row>
-    <row r="26" spans="1:10" ht="13.8" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A26" s="55"/>
       <c r="B26" s="19">
         <v>9</v>
@@ -5888,7 +5888,7 @@
       </c>
       <c r="J26" s="58"/>
     </row>
-    <row r="27" spans="1:10" ht="13.8" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A27" s="55"/>
       <c r="C27" s="23" t="s">
         <v>219</v>
@@ -5898,7 +5898,7 @@
       </c>
       <c r="J27" s="58"/>
     </row>
-    <row r="28" spans="1:10" ht="13.8" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A28" s="55"/>
       <c r="C28" s="23" t="s">
         <v>242</v>
@@ -5908,17 +5908,17 @@
       </c>
       <c r="J28" s="58"/>
     </row>
-    <row r="29" spans="1:10" ht="13.8" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A29" s="55"/>
       <c r="C29" s="23"/>
       <c r="F29" s="51"/>
       <c r="J29" s="58"/>
     </row>
-    <row r="30" spans="1:10" ht="13.8" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A30" s="55"/>
       <c r="J30" s="58"/>
     </row>
-    <row r="31" spans="1:10" ht="13.8" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A31" s="55"/>
       <c r="C31" s="21" t="s">
         <v>300</v>
@@ -5929,7 +5929,7 @@
       <c r="F31" s="24"/>
       <c r="J31" s="58"/>
     </row>
-    <row r="32" spans="1:10" ht="13.8" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A32" s="55"/>
       <c r="C32" s="21" t="s">
         <v>183</v>
@@ -5944,12 +5944,12 @@
       <c r="C33" s="21"/>
       <c r="J33" s="58"/>
     </row>
-    <row r="34" spans="1:10" ht="13.8" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="34" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A34" s="55"/>
       <c r="D34" s="18"/>
       <c r="J34" s="58"/>
     </row>
-    <row r="35" spans="1:10" ht="13.8" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="35" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A35" s="55"/>
       <c r="C35" s="21" t="s">
         <v>297</v>
@@ -5963,7 +5963,7 @@
       </c>
       <c r="J35" s="58"/>
     </row>
-    <row r="36" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="36" spans="1:10" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A36" s="55"/>
       <c r="C36" s="21" t="s">
         <v>295</v>
@@ -5979,13 +5979,13 @@
       </c>
       <c r="J36" s="58"/>
     </row>
-    <row r="37" spans="1:10" ht="27" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="37" spans="1:10" ht="42" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A37" s="55"/>
       <c r="C37" s="23" t="s">
         <v>292</v>
       </c>
       <c r="D37" s="147">
-        <v>4444</v>
+        <v>66666</v>
       </c>
       <c r="E37" s="18" t="s">
         <v>315</v>
@@ -5995,7 +5995,7 @@
       </c>
       <c r="J37" s="58"/>
     </row>
-    <row r="38" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="38" spans="1:10" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A38" s="55"/>
       <c r="C38" s="23" t="s">
         <v>293</v>
@@ -6012,13 +6012,13 @@
       </c>
       <c r="J38" s="58"/>
     </row>
-    <row r="39" spans="1:10" ht="27" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="39" spans="1:10" ht="29.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A39" s="55"/>
       <c r="C39" s="23" t="s">
         <v>294</v>
       </c>
       <c r="D39" s="147">
-        <v>30</v>
+        <v>77777</v>
       </c>
       <c r="E39" s="18" t="s">
         <v>315</v>
@@ -6028,7 +6028,7 @@
       </c>
       <c r="J39" s="58"/>
     </row>
-    <row r="40" spans="1:10" ht="13.8" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="40" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A40" s="55"/>
       <c r="C40" s="21" t="s">
         <v>299</v>
@@ -6044,21 +6044,21 @@
       </c>
       <c r="J40" s="58"/>
     </row>
-    <row r="41" spans="1:10" ht="27" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="41" spans="1:10" ht="29.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A41" s="55"/>
       <c r="C41" s="21" t="s">
         <v>291</v>
       </c>
       <c r="D41" s="39">
         <f>ROUNDUP($D$37/D35,2)</f>
-        <v>22.22</v>
+        <v>333.33</v>
       </c>
       <c r="F41" s="104" t="s">
         <v>302</v>
       </c>
       <c r="J41" s="58"/>
     </row>
-    <row r="42" spans="1:10" ht="13.8" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="42" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A42" s="55"/>
       <c r="C42" s="21" t="s">
         <v>289</v>
@@ -6072,21 +6072,21 @@
       </c>
       <c r="J42" s="58"/>
     </row>
-    <row r="43" spans="1:10" ht="27" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="43" spans="1:10" ht="29.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A43" s="55"/>
       <c r="C43" s="21" t="s">
         <v>290</v>
       </c>
       <c r="D43" s="101">
         <f>IFERROR(((D36+D37)/D31),"")</f>
-        <v>22.22</v>
+        <v>333.33</v>
       </c>
       <c r="F43" s="105" t="s">
         <v>303</v>
       </c>
       <c r="J43" s="58"/>
     </row>
-    <row r="44" spans="1:10" ht="13.8" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="44" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A44" s="55"/>
       <c r="C44" s="21" t="s">
         <v>222</v>
@@ -6097,7 +6097,7 @@
       </c>
       <c r="J44" s="58"/>
     </row>
-    <row r="45" spans="1:10" ht="13.8" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="45" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A45" s="55"/>
       <c r="C45" s="21" t="s">
         <v>228</v>
@@ -6107,18 +6107,18 @@
       </c>
       <c r="J45" s="58"/>
     </row>
-    <row r="46" spans="1:10" ht="13.8" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="46" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A46" s="55"/>
       <c r="C46" s="21" t="s">
         <v>307</v>
       </c>
       <c r="D46" s="112">
         <f>ROUNDUP(D39/D31,2)</f>
-        <v>0.15</v>
+        <v>388.89</v>
       </c>
       <c r="J46" s="58"/>
     </row>
-    <row r="47" spans="1:10" ht="13.8" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="47" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A47" s="55"/>
       <c r="C47" s="23"/>
       <c r="F47" s="107" t="s">
@@ -6126,7 +6126,7 @@
       </c>
       <c r="J47" s="58"/>
     </row>
-    <row r="48" spans="1:10" ht="13.8" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="48" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A48" s="55"/>
       <c r="C48" s="216" t="s">
         <v>309</v>
@@ -6139,14 +6139,14 @@
       <c r="I48" s="45"/>
       <c r="J48" s="58"/>
     </row>
-    <row r="49" spans="1:10" ht="13.8" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="49" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A49" s="55"/>
       <c r="C49" s="48" t="s">
         <v>179</v>
       </c>
       <c r="D49" s="148">
         <f>+D37</f>
-        <v>4444</v>
+        <v>66666</v>
       </c>
       <c r="E49" s="37" t="s">
         <v>119</v>
@@ -6158,7 +6158,7 @@
       <c r="I49" s="46"/>
       <c r="J49" s="58"/>
     </row>
-    <row r="50" spans="1:10" ht="13.8" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="50" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A50" s="55"/>
       <c r="C50" s="48" t="s">
         <v>180</v>
@@ -6171,7 +6171,7 @@
       <c r="I50" s="46"/>
       <c r="J50" s="58"/>
     </row>
-    <row r="51" spans="1:10" ht="13.8" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="51" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A51" s="55"/>
       <c r="C51" s="48" t="s">
         <v>181</v>
@@ -6184,7 +6184,7 @@
       <c r="I51" s="46"/>
       <c r="J51" s="58"/>
     </row>
-    <row r="52" spans="1:10" ht="13.8" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="52" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A52" s="55"/>
       <c r="C52" s="49" t="s">
         <v>182</v>
@@ -6197,19 +6197,19 @@
       <c r="I52" s="46"/>
       <c r="J52" s="58"/>
     </row>
-    <row r="53" spans="1:10" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:10" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A53" s="55"/>
       <c r="C53" s="21"/>
       <c r="D53" s="24">
         <f>SUM(D49:D52)</f>
-        <v>4444</v>
+        <v>66666</v>
       </c>
       <c r="E53" s="18" t="s">
         <v>315</v>
       </c>
       <c r="J53" s="58"/>
     </row>
-    <row r="54" spans="1:10" ht="13.8" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="54" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A54" s="55"/>
       <c r="C54" s="21"/>
       <c r="D54" s="36"/>
@@ -6222,7 +6222,7 @@
       </c>
       <c r="D55" s="40">
         <f>SUMIF(E49:E52,"RESIDENCIAL",D49:D52)</f>
-        <v>4444</v>
+        <v>66666</v>
       </c>
       <c r="J55" s="58"/>
     </row>
@@ -6237,7 +6237,7 @@
       </c>
       <c r="J56" s="58"/>
     </row>
-    <row r="57" spans="1:10" ht="13.8" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="57" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="C57" s="21" t="s">
         <v>185</v>
       </c>
@@ -6246,8 +6246,8 @@
         <v>0</v>
       </c>
     </row>
-    <row r="58" spans="1:10" ht="13.8" thickBot="1" x14ac:dyDescent="0.35"/>
-    <row r="59" spans="1:10" ht="13.8" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="58" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
+    <row r="59" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A59" s="55"/>
       <c r="C59" s="21" t="s">
         <v>248</v>
@@ -6258,7 +6258,7 @@
       </c>
       <c r="J59" s="58"/>
     </row>
-    <row r="60" spans="1:10" ht="13.8" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="60" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A60" s="55"/>
       <c r="C60" s="21"/>
       <c r="E60" s="20" t="s">
@@ -6266,7 +6266,7 @@
       </c>
       <c r="J60" s="58"/>
     </row>
-    <row r="61" spans="1:10" ht="13.8" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="61" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A61" s="55"/>
       <c r="C61" s="21" t="s">
         <v>187</v>
@@ -6277,7 +6277,7 @@
       <c r="E61" s="50"/>
       <c r="J61" s="58"/>
     </row>
-    <row r="62" spans="1:10" ht="13.8" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="62" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A62" s="55"/>
       <c r="C62" s="21" t="s">
         <v>189</v>
@@ -6293,7 +6293,7 @@
       </c>
       <c r="J62" s="58"/>
     </row>
-    <row r="63" spans="1:10" ht="24.6" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="63" spans="1:10" ht="28.5" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A63" s="55"/>
       <c r="C63" s="23" t="s">
         <v>220</v>
@@ -6303,20 +6303,20 @@
       </c>
       <c r="J63" s="58"/>
     </row>
-    <row r="64" spans="1:10" ht="13.8" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="64" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A64" s="55"/>
       <c r="C64" s="23"/>
       <c r="D64" s="35"/>
       <c r="J64" s="58"/>
     </row>
-    <row r="65" spans="1:10" ht="13.8" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="65" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A65" s="55"/>
       <c r="C65" s="21" t="s">
         <v>191</v>
       </c>
       <c r="D65" s="53">
         <f>IF($D$35&gt;10000,((($D$35*$D$41)/($F$62+$D$41))*IF($D$59=100%,1,1.3)),(($D$35*($D$41*0.75))/($D$62+($D$41*0.75))*(IF($D$63="NO",1,0.75))*(IF($D$59=100%,1,1.3))))</f>
-        <v>130.50117462803445</v>
+        <v>193.14334276526088</v>
       </c>
       <c r="J65" s="58"/>
     </row>
@@ -6325,12 +6325,12 @@
       <c r="C66" s="21"/>
       <c r="J66" s="58"/>
     </row>
-    <row r="67" spans="1:10" ht="13.8" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="67" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A67" s="55"/>
       <c r="C67" s="21"/>
       <c r="J67" s="58"/>
     </row>
-    <row r="68" spans="1:10" ht="13.8" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="68" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A68" s="55"/>
       <c r="C68" s="71" t="s">
         <v>268</v>
@@ -6343,7 +6343,7 @@
       </c>
       <c r="J68" s="58"/>
     </row>
-    <row r="69" spans="1:10" ht="13.8" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="69" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A69" s="55"/>
       <c r="C69" s="21"/>
       <c r="D69" s="70">
@@ -6352,7 +6352,7 @@
       <c r="E69" s="22"/>
       <c r="J69" s="58"/>
     </row>
-    <row r="70" spans="1:10" ht="13.8" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="70" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A70" s="55"/>
       <c r="C70" s="21"/>
       <c r="D70" s="70">
@@ -6361,7 +6361,7 @@
       <c r="E70" s="22"/>
       <c r="J70" s="58"/>
     </row>
-    <row r="71" spans="1:10" ht="13.8" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="71" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A71" s="55"/>
       <c r="C71" s="21"/>
       <c r="D71" s="70">
@@ -6370,11 +6370,11 @@
       <c r="E71" s="22"/>
       <c r="J71" s="58"/>
     </row>
-    <row r="72" spans="1:10" ht="13.8" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="72" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A72" s="55"/>
       <c r="J72" s="58"/>
     </row>
-    <row r="73" spans="1:10" ht="13.8" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="73" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A73" s="55"/>
       <c r="C73" s="209" t="s">
         <v>269</v>
@@ -6396,7 +6396,7 @@
       <c r="E74" s="22"/>
       <c r="J74" s="58"/>
     </row>
-    <row r="75" spans="1:10" ht="13.8" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="75" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A75" s="55"/>
       <c r="D75" s="70">
         <v>3</v>
@@ -6404,7 +6404,7 @@
       <c r="E75" s="22"/>
       <c r="J75" s="58"/>
     </row>
-    <row r="76" spans="1:10" ht="13.8" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="76" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A76" s="55"/>
       <c r="D76" s="70">
         <v>4</v>
@@ -6420,12 +6420,12 @@
       <c r="A78" s="55"/>
       <c r="J78" s="58"/>
     </row>
-    <row r="79" spans="1:10" ht="13.8" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="79" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A79" s="55"/>
       <c r="C79" s="21"/>
       <c r="J79" s="58"/>
     </row>
-    <row r="80" spans="1:10" ht="13.8" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="80" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A80" s="55"/>
       <c r="C80" s="21" t="s">
         <v>2</v>
@@ -6539,28 +6539,28 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:T143"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="11.44140625" defaultRowHeight="13.2" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11.42578125" defaultRowHeight="13.5" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="4.88671875" style="143" customWidth="1"/>
-    <col min="2" max="3" width="4.88671875" style="146" customWidth="1"/>
-    <col min="4" max="4" width="4.88671875" style="143" customWidth="1"/>
-    <col min="5" max="5" width="5.33203125" style="143" customWidth="1"/>
-    <col min="6" max="6" width="41.6640625" style="143" customWidth="1"/>
-    <col min="7" max="7" width="21.44140625" style="143" customWidth="1"/>
-    <col min="8" max="8" width="10.44140625" style="143" customWidth="1"/>
-    <col min="9" max="9" width="44.33203125" style="143" customWidth="1"/>
+    <col min="1" max="1" width="4.85546875" style="143" customWidth="1"/>
+    <col min="2" max="3" width="4.85546875" style="146" customWidth="1"/>
+    <col min="4" max="4" width="4.85546875" style="143" customWidth="1"/>
+    <col min="5" max="5" width="5.28515625" style="143" customWidth="1"/>
+    <col min="6" max="6" width="41.7109375" style="143" customWidth="1"/>
+    <col min="7" max="7" width="21.42578125" style="143" customWidth="1"/>
+    <col min="8" max="8" width="10.42578125" style="143" customWidth="1"/>
+    <col min="9" max="9" width="44.28515625" style="143" customWidth="1"/>
     <col min="10" max="10" width="20" style="143" customWidth="1"/>
-    <col min="11" max="11" width="12.33203125" style="143" customWidth="1"/>
-    <col min="12" max="12" width="29.33203125" style="143" customWidth="1"/>
-    <col min="13" max="13" width="5.6640625" style="143" customWidth="1"/>
-    <col min="14" max="14" width="5.44140625" style="143" customWidth="1"/>
+    <col min="11" max="11" width="12.28515625" style="143" customWidth="1"/>
+    <col min="12" max="12" width="29.28515625" style="143" customWidth="1"/>
+    <col min="13" max="13" width="5.7109375" style="143" customWidth="1"/>
+    <col min="14" max="14" width="5.42578125" style="143" customWidth="1"/>
     <col min="15" max="15" width="9" style="143" hidden="1" customWidth="1"/>
-    <col min="16" max="17" width="4.88671875" style="146" customWidth="1"/>
-    <col min="18" max="18" width="4.88671875" style="143" customWidth="1"/>
-    <col min="19" max="16384" width="11.44140625" style="143"/>
+    <col min="16" max="17" width="4.85546875" style="146" customWidth="1"/>
+    <col min="18" max="18" width="4.85546875" style="143" customWidth="1"/>
+    <col min="19" max="16384" width="11.42578125" style="143"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:17" s="73" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="2:17" s="73" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D1" s="77"/>
       <c r="E1" s="77"/>
       <c r="F1" s="77"/>
@@ -6571,7 +6571,7 @@
       <c r="K1" s="77"/>
       <c r="O1" s="77"/>
     </row>
-    <row r="2" spans="2:17" s="73" customFormat="1" ht="17.399999999999999" x14ac:dyDescent="0.3">
+    <row r="2" spans="2:17" s="73" customFormat="1" ht="18" x14ac:dyDescent="0.25">
       <c r="D2" s="82"/>
       <c r="E2" s="114"/>
       <c r="F2" s="114"/>
@@ -6585,8 +6585,8 @@
       <c r="N2" s="114"/>
       <c r="O2" s="114"/>
     </row>
-    <row r="3" spans="2:17" s="73" customFormat="1" ht="17.399999999999999" thickBot="1" x14ac:dyDescent="0.35"/>
-    <row r="4" spans="2:17" s="73" customFormat="1" ht="20.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="2:17" s="73" customFormat="1" ht="18.75" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="4" spans="2:17" s="73" customFormat="1" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B4" s="93"/>
       <c r="C4" s="93"/>
       <c r="G4" s="221" t="s">
@@ -6602,13 +6602,13 @@
       <c r="P4" s="93"/>
       <c r="Q4" s="93"/>
     </row>
-    <row r="5" spans="2:17" s="73" customFormat="1" ht="17.399999999999999" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="5" spans="2:17" s="73" customFormat="1" ht="18.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B5" s="93"/>
       <c r="C5" s="93"/>
       <c r="P5" s="93"/>
       <c r="Q5" s="93"/>
     </row>
-    <row r="6" spans="2:17" s="73" customFormat="1" ht="21" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="2:17" s="73" customFormat="1" ht="21" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B6" s="93"/>
       <c r="C6" s="93"/>
       <c r="G6" s="234" t="s">
@@ -6619,7 +6619,7 @@
       <c r="P6" s="93"/>
       <c r="Q6" s="93"/>
     </row>
-    <row r="7" spans="2:17" s="73" customFormat="1" ht="16.8" x14ac:dyDescent="0.3">
+    <row r="7" spans="2:17" s="73" customFormat="1" ht="18" x14ac:dyDescent="0.25">
       <c r="B7" s="93"/>
       <c r="C7" s="93"/>
       <c r="G7" s="237"/>
@@ -6628,14 +6628,14 @@
       <c r="P7" s="93"/>
       <c r="Q7" s="93"/>
     </row>
-    <row r="8" spans="2:17" s="73" customFormat="1" ht="18" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="8" spans="2:17" s="73" customFormat="1" ht="18.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B8" s="93"/>
       <c r="C8" s="93"/>
       <c r="F8" s="82"/>
       <c r="P8" s="93"/>
       <c r="Q8" s="93"/>
     </row>
-    <row r="9" spans="2:17" s="73" customFormat="1" ht="23.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="9" spans="2:17" s="73" customFormat="1" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B9" s="93"/>
       <c r="C9" s="93"/>
       <c r="F9" s="223" t="s">
@@ -6650,13 +6650,13 @@
       <c r="P9" s="93"/>
       <c r="Q9" s="93"/>
     </row>
-    <row r="10" spans="2:17" s="73" customFormat="1" ht="17.399999999999999" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="10" spans="2:17" s="73" customFormat="1" ht="18.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B10" s="93"/>
       <c r="C10" s="93"/>
       <c r="P10" s="93"/>
       <c r="Q10" s="93"/>
     </row>
-    <row r="11" spans="2:17" s="73" customFormat="1" ht="20.399999999999999" x14ac:dyDescent="0.3">
+    <row r="11" spans="2:17" s="73" customFormat="1" ht="20.25" x14ac:dyDescent="0.25">
       <c r="B11" s="93"/>
       <c r="C11" s="93"/>
       <c r="F11" s="77" t="s">
@@ -6672,7 +6672,7 @@
       <c r="P11" s="93"/>
       <c r="Q11" s="93"/>
     </row>
-    <row r="12" spans="2:17" s="73" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="12" spans="2:17" s="73" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B12" s="93"/>
       <c r="C12" s="93"/>
       <c r="F12" s="77" t="s">
@@ -6688,7 +6688,7 @@
       <c r="P12" s="93"/>
       <c r="Q12" s="93"/>
     </row>
-    <row r="13" spans="2:17" s="73" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="13" spans="2:17" s="73" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B13" s="93"/>
       <c r="C13" s="93"/>
       <c r="F13" s="77" t="s">
@@ -6704,7 +6704,7 @@
       <c r="P13" s="93"/>
       <c r="Q13" s="93"/>
     </row>
-    <row r="14" spans="2:17" s="73" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="14" spans="2:17" s="73" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B14" s="93"/>
       <c r="C14" s="93"/>
       <c r="F14" s="77" t="s">
@@ -6720,7 +6720,7 @@
       <c r="P14" s="93"/>
       <c r="Q14" s="93"/>
     </row>
-    <row r="15" spans="2:17" s="73" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="15" spans="2:17" s="73" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B15" s="93"/>
       <c r="C15" s="93"/>
       <c r="F15" s="77" t="s">
@@ -6736,7 +6736,7 @@
       <c r="P15" s="93"/>
       <c r="Q15" s="93"/>
     </row>
-    <row r="16" spans="2:17" s="73" customFormat="1" ht="17.399999999999999" x14ac:dyDescent="0.3">
+    <row r="16" spans="2:17" s="73" customFormat="1" ht="18" x14ac:dyDescent="0.25">
       <c r="B16" s="93"/>
       <c r="C16" s="93"/>
       <c r="F16" s="77" t="s">
@@ -6752,7 +6752,7 @@
       <c r="P16" s="93"/>
       <c r="Q16" s="93"/>
     </row>
-    <row r="17" spans="2:20" s="73" customFormat="1" ht="17.399999999999999" x14ac:dyDescent="0.3">
+    <row r="17" spans="2:20" s="73" customFormat="1" ht="18" x14ac:dyDescent="0.25">
       <c r="B17" s="93"/>
       <c r="C17" s="93"/>
       <c r="F17" s="77" t="s">
@@ -6773,7 +6773,7 @@
       <c r="P17" s="93"/>
       <c r="Q17" s="93"/>
     </row>
-    <row r="18" spans="2:20" s="73" customFormat="1" ht="18" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="18" spans="2:20" s="73" customFormat="1" ht="18.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B18" s="93"/>
       <c r="C18" s="93"/>
       <c r="F18" s="77" t="s">
@@ -6789,7 +6789,7 @@
       <c r="P18" s="93"/>
       <c r="Q18" s="93"/>
     </row>
-    <row r="19" spans="2:20" s="73" customFormat="1" ht="18" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="19" spans="2:20" s="73" customFormat="1" ht="18.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B19" s="93"/>
       <c r="C19" s="93"/>
       <c r="F19" s="77"/>
@@ -6800,7 +6800,7 @@
       <c r="P19" s="93"/>
       <c r="Q19" s="93"/>
     </row>
-    <row r="20" spans="2:20" s="73" customFormat="1" ht="20.399999999999999" x14ac:dyDescent="0.3">
+    <row r="20" spans="2:20" s="73" customFormat="1" ht="20.25" x14ac:dyDescent="0.25">
       <c r="B20" s="93"/>
       <c r="C20" s="93"/>
       <c r="F20" s="223" t="s">
@@ -6815,14 +6815,14 @@
       <c r="P20" s="93"/>
       <c r="Q20" s="93"/>
     </row>
-    <row r="21" spans="2:20" s="73" customFormat="1" ht="18" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="21" spans="2:20" s="73" customFormat="1" ht="18.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B21" s="93"/>
       <c r="C21" s="93"/>
       <c r="F21" s="77"/>
       <c r="P21" s="93"/>
       <c r="Q21" s="93"/>
     </row>
-    <row r="22" spans="2:20" s="73" customFormat="1" ht="36" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="22" spans="2:20" s="73" customFormat="1" ht="36" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B22" s="93"/>
       <c r="C22" s="93"/>
       <c r="F22" s="118" t="s">
@@ -6839,7 +6839,7 @@
       <c r="P22" s="93"/>
       <c r="Q22" s="93"/>
     </row>
-    <row r="23" spans="2:20" s="73" customFormat="1" ht="18" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="23" spans="2:20" s="73" customFormat="1" ht="18.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B23" s="93"/>
       <c r="C23" s="93"/>
       <c r="F23" s="118"/>
@@ -6851,7 +6851,7 @@
       <c r="P23" s="93"/>
       <c r="Q23" s="93"/>
     </row>
-    <row r="24" spans="2:20" s="73" customFormat="1" ht="21" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="24" spans="2:20" s="73" customFormat="1" ht="21" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B24" s="93"/>
       <c r="C24" s="93"/>
       <c r="F24" s="274" t="s">
@@ -6870,7 +6870,7 @@
       <c r="P24" s="93"/>
       <c r="Q24" s="93"/>
     </row>
-    <row r="25" spans="2:20" s="73" customFormat="1" ht="19.8" x14ac:dyDescent="0.3">
+    <row r="25" spans="2:20" s="73" customFormat="1" ht="20.25" x14ac:dyDescent="0.25">
       <c r="B25" s="93"/>
       <c r="C25" s="93"/>
       <c r="F25" s="120" t="s">
@@ -6896,7 +6896,7 @@
       <c r="P25" s="93"/>
       <c r="Q25" s="93"/>
     </row>
-    <row r="26" spans="2:20" s="73" customFormat="1" ht="17.399999999999999" x14ac:dyDescent="0.3">
+    <row r="26" spans="2:20" s="73" customFormat="1" ht="18" x14ac:dyDescent="0.25">
       <c r="B26" s="93"/>
       <c r="C26" s="93"/>
       <c r="F26" s="74" t="s">
@@ -6922,7 +6922,7 @@
       <c r="P26" s="93"/>
       <c r="Q26" s="93"/>
     </row>
-    <row r="27" spans="2:20" s="73" customFormat="1" ht="17.399999999999999" x14ac:dyDescent="0.3">
+    <row r="27" spans="2:20" s="73" customFormat="1" ht="18" x14ac:dyDescent="0.25">
       <c r="B27" s="93"/>
       <c r="C27" s="93"/>
       <c r="F27" s="74" t="s">
@@ -6948,7 +6948,7 @@
       <c r="P27" s="93"/>
       <c r="Q27" s="93"/>
     </row>
-    <row r="28" spans="2:20" s="73" customFormat="1" ht="17.399999999999999" x14ac:dyDescent="0.3">
+    <row r="28" spans="2:20" s="73" customFormat="1" ht="36" x14ac:dyDescent="0.25">
       <c r="B28" s="93"/>
       <c r="C28" s="93"/>
       <c r="F28" s="74" t="s">
@@ -6974,7 +6974,7 @@
       <c r="P28" s="93"/>
       <c r="Q28" s="93"/>
     </row>
-    <row r="29" spans="2:20" s="73" customFormat="1" ht="34.799999999999997" x14ac:dyDescent="0.3">
+    <row r="29" spans="2:20" s="73" customFormat="1" ht="36" x14ac:dyDescent="0.25">
       <c r="B29" s="93"/>
       <c r="C29" s="93"/>
       <c r="F29" s="74" t="s">
@@ -7000,7 +7000,7 @@
       <c r="P29" s="93"/>
       <c r="Q29" s="93"/>
     </row>
-    <row r="30" spans="2:20" s="73" customFormat="1" ht="54.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="30" spans="2:20" s="73" customFormat="1" ht="54.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B30" s="93"/>
       <c r="C30" s="93"/>
       <c r="F30" s="74" t="s">
@@ -7016,7 +7016,7 @@
       </c>
       <c r="J30" s="123">
         <f>IF(J25&lt;150,"NO DEBE DEJAR AREA PERMEABLE",FACTIBILIDAD!D39/FACTIBILIDAD!D35)</f>
-        <v>0.15</v>
+        <v>388.88499999999999</v>
       </c>
       <c r="K30" s="124"/>
       <c r="L30" s="99" t="str">
@@ -7026,7 +7026,7 @@
       <c r="P30" s="93"/>
       <c r="Q30" s="93"/>
     </row>
-    <row r="31" spans="2:20" s="73" customFormat="1" ht="19.8" x14ac:dyDescent="0.3">
+    <row r="31" spans="2:20" s="73" customFormat="1" ht="38.25" x14ac:dyDescent="0.25">
       <c r="B31" s="93"/>
       <c r="C31" s="93"/>
       <c r="F31" s="74" t="s">
@@ -7052,7 +7052,7 @@
       <c r="P31" s="93"/>
       <c r="Q31" s="93"/>
     </row>
-    <row r="32" spans="2:20" s="73" customFormat="1" ht="37.200000000000003" x14ac:dyDescent="0.3">
+    <row r="32" spans="2:20" s="73" customFormat="1" ht="38.25" x14ac:dyDescent="0.25">
       <c r="B32" s="93"/>
       <c r="C32" s="93"/>
       <c r="F32" s="74" t="s">
@@ -7079,7 +7079,7 @@
       <c r="Q32" s="93"/>
       <c r="T32" s="206"/>
     </row>
-    <row r="33" spans="2:20" s="73" customFormat="1" ht="34.799999999999997" x14ac:dyDescent="0.3">
+    <row r="33" spans="2:20" s="73" customFormat="1" ht="36" x14ac:dyDescent="0.25">
       <c r="B33" s="93"/>
       <c r="C33" s="93"/>
       <c r="F33" s="74" t="s">
@@ -7105,7 +7105,7 @@
       <c r="P33" s="93"/>
       <c r="Q33" s="93"/>
     </row>
-    <row r="34" spans="2:20" s="73" customFormat="1" ht="17.399999999999999" x14ac:dyDescent="0.3">
+    <row r="34" spans="2:20" s="73" customFormat="1" ht="36" x14ac:dyDescent="0.25">
       <c r="B34" s="93"/>
       <c r="C34" s="93"/>
       <c r="F34" s="74" t="s">
@@ -7121,7 +7121,7 @@
       </c>
       <c r="J34" s="127">
         <f>FACTIBILIDAD!D43</f>
-        <v>22.22</v>
+        <v>333.33</v>
       </c>
       <c r="K34" s="114"/>
       <c r="L34" s="99" t="str">
@@ -7132,7 +7132,7 @@
       <c r="Q34" s="93"/>
       <c r="S34" s="207"/>
     </row>
-    <row r="35" spans="2:20" s="73" customFormat="1" ht="37.799999999999997" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="35" spans="2:20" s="73" customFormat="1" ht="39" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B35" s="93"/>
       <c r="C35" s="93"/>
       <c r="F35" s="128" t="s">
@@ -7148,7 +7148,7 @@
       </c>
       <c r="J35" s="129">
         <f>FACTIBILIDAD!D37+FACTIBILIDAD!D36</f>
-        <v>4444</v>
+        <v>66666</v>
       </c>
       <c r="K35" s="114"/>
       <c r="L35" s="100" t="str">
@@ -7165,7 +7165,7 @@
       <c r="S35" s="206"/>
       <c r="T35" s="206"/>
     </row>
-    <row r="36" spans="2:20" s="73" customFormat="1" ht="18" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="36" spans="2:20" s="73" customFormat="1" ht="18.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B36" s="93"/>
       <c r="C36" s="93"/>
       <c r="F36" s="77"/>
@@ -7179,7 +7179,7 @@
       <c r="P36" s="93"/>
       <c r="Q36" s="93"/>
     </row>
-    <row r="37" spans="2:20" s="73" customFormat="1" ht="18.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="37" spans="2:20" s="73" customFormat="1" ht="18.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B37" s="93"/>
       <c r="C37" s="93"/>
       <c r="F37" s="281" t="s">
@@ -7198,7 +7198,7 @@
       <c r="P37" s="93"/>
       <c r="Q37" s="93"/>
     </row>
-    <row r="38" spans="2:20" s="73" customFormat="1" ht="19.8" x14ac:dyDescent="0.3">
+    <row r="38" spans="2:20" s="73" customFormat="1" ht="20.25" x14ac:dyDescent="0.25">
       <c r="B38" s="93"/>
       <c r="C38" s="93"/>
       <c r="F38" s="149" t="s">
@@ -7223,7 +7223,7 @@
       <c r="P38" s="93"/>
       <c r="Q38" s="93"/>
     </row>
-    <row r="39" spans="2:20" s="73" customFormat="1" ht="37.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="39" spans="2:20" s="73" customFormat="1" ht="37.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B39" s="93"/>
       <c r="C39" s="93"/>
       <c r="F39" s="150" t="s">
@@ -7243,7 +7243,7 @@
       <c r="P39" s="93"/>
       <c r="Q39" s="93"/>
     </row>
-    <row r="40" spans="2:20" s="73" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="40" spans="2:20" s="73" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B40" s="93"/>
       <c r="C40" s="93"/>
       <c r="F40" s="284" t="str">
@@ -7256,7 +7256,7 @@
       <c r="P40" s="93"/>
       <c r="Q40" s="93"/>
     </row>
-    <row r="41" spans="2:20" s="73" customFormat="1" ht="21" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="41" spans="2:20" s="73" customFormat="1" ht="21" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B41" s="93"/>
       <c r="C41" s="93"/>
       <c r="F41" s="130"/>
@@ -7264,7 +7264,7 @@
       <c r="P41" s="93"/>
       <c r="Q41" s="93"/>
     </row>
-    <row r="42" spans="2:20" s="73" customFormat="1" ht="20.399999999999999" x14ac:dyDescent="0.3">
+    <row r="42" spans="2:20" s="73" customFormat="1" ht="20.25" x14ac:dyDescent="0.25">
       <c r="B42" s="93"/>
       <c r="C42" s="93"/>
       <c r="F42" s="223" t="s">
@@ -7279,7 +7279,7 @@
       <c r="P42" s="93"/>
       <c r="Q42" s="93"/>
     </row>
-    <row r="43" spans="2:20" s="73" customFormat="1" ht="17.399999999999999" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="43" spans="2:20" s="73" customFormat="1" ht="18.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B43" s="93"/>
       <c r="C43" s="93"/>
       <c r="F43" s="130"/>
@@ -7287,7 +7287,7 @@
       <c r="P43" s="93"/>
       <c r="Q43" s="93"/>
     </row>
-    <row r="44" spans="2:20" s="73" customFormat="1" ht="34.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="44" spans="2:20" s="73" customFormat="1" ht="34.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B44" s="93"/>
       <c r="C44" s="93"/>
       <c r="E44" s="73">
@@ -7306,7 +7306,7 @@
       <c r="P44" s="93"/>
       <c r="Q44" s="93"/>
     </row>
-    <row r="45" spans="2:20" s="73" customFormat="1" ht="16.8" x14ac:dyDescent="0.3">
+    <row r="45" spans="2:20" s="73" customFormat="1" ht="18" x14ac:dyDescent="0.25">
       <c r="B45" s="93"/>
       <c r="C45" s="93"/>
       <c r="E45" s="73">
@@ -7325,7 +7325,7 @@
       <c r="P45" s="93"/>
       <c r="Q45" s="93"/>
     </row>
-    <row r="46" spans="2:20" s="73" customFormat="1" ht="16.8" x14ac:dyDescent="0.3">
+    <row r="46" spans="2:20" s="73" customFormat="1" ht="18" x14ac:dyDescent="0.25">
       <c r="B46" s="93"/>
       <c r="C46" s="93"/>
       <c r="E46" s="73">
@@ -7344,7 +7344,7 @@
       <c r="P46" s="93"/>
       <c r="Q46" s="93"/>
     </row>
-    <row r="47" spans="2:20" s="73" customFormat="1" ht="16.8" x14ac:dyDescent="0.3">
+    <row r="47" spans="2:20" s="73" customFormat="1" ht="18" x14ac:dyDescent="0.25">
       <c r="B47" s="93"/>
       <c r="C47" s="93"/>
       <c r="E47" s="73">
@@ -7363,7 +7363,7 @@
       <c r="P47" s="93"/>
       <c r="Q47" s="93"/>
     </row>
-    <row r="48" spans="2:20" s="73" customFormat="1" ht="16.8" x14ac:dyDescent="0.3">
+    <row r="48" spans="2:20" s="73" customFormat="1" ht="18" x14ac:dyDescent="0.25">
       <c r="B48" s="93"/>
       <c r="C48" s="93"/>
       <c r="E48" s="73">
@@ -7382,7 +7382,7 @@
       <c r="P48" s="93"/>
       <c r="Q48" s="93"/>
     </row>
-    <row r="49" spans="2:17" s="73" customFormat="1" ht="16.8" x14ac:dyDescent="0.3">
+    <row r="49" spans="2:17" s="73" customFormat="1" ht="18" x14ac:dyDescent="0.25">
       <c r="B49" s="93"/>
       <c r="C49" s="93"/>
       <c r="E49" s="73">
@@ -7401,7 +7401,7 @@
       <c r="P49" s="93"/>
       <c r="Q49" s="93"/>
     </row>
-    <row r="50" spans="2:17" s="73" customFormat="1" ht="34.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="50" spans="2:17" s="73" customFormat="1" ht="34.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B50" s="93"/>
       <c r="C50" s="93"/>
       <c r="E50" s="73">
@@ -7420,7 +7420,7 @@
       <c r="P50" s="93"/>
       <c r="Q50" s="93"/>
     </row>
-    <row r="51" spans="2:17" s="73" customFormat="1" ht="20.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="51" spans="2:17" s="73" customFormat="1" ht="20.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B51" s="93"/>
       <c r="C51" s="93"/>
       <c r="E51" s="73">
@@ -7439,7 +7439,7 @@
       <c r="P51" s="93"/>
       <c r="Q51" s="93"/>
     </row>
-    <row r="52" spans="2:17" s="73" customFormat="1" ht="16.8" x14ac:dyDescent="0.3">
+    <row r="52" spans="2:17" s="73" customFormat="1" ht="18" x14ac:dyDescent="0.25">
       <c r="B52" s="93"/>
       <c r="C52" s="93"/>
       <c r="F52" s="220"/>
@@ -7448,7 +7448,7 @@
       <c r="P52" s="93"/>
       <c r="Q52" s="93"/>
     </row>
-    <row r="53" spans="2:17" s="73" customFormat="1" ht="16.8" x14ac:dyDescent="0.3">
+    <row r="53" spans="2:17" s="73" customFormat="1" ht="18" x14ac:dyDescent="0.25">
       <c r="B53" s="93"/>
       <c r="C53" s="93"/>
       <c r="F53" s="264" t="s">
@@ -7463,7 +7463,7 @@
       <c r="P53" s="93"/>
       <c r="Q53" s="93"/>
     </row>
-    <row r="54" spans="2:17" s="73" customFormat="1" ht="39.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="54" spans="2:17" s="73" customFormat="1" ht="39.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B54" s="93"/>
       <c r="C54" s="93"/>
       <c r="F54" s="267"/>
@@ -7476,7 +7476,7 @@
       <c r="P54" s="93"/>
       <c r="Q54" s="93"/>
     </row>
-    <row r="55" spans="2:17" s="73" customFormat="1" ht="17.399999999999999" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="55" spans="2:17" s="73" customFormat="1" ht="18.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B55" s="93"/>
       <c r="C55" s="93"/>
       <c r="F55" s="113"/>
@@ -7485,7 +7485,7 @@
       <c r="P55" s="93"/>
       <c r="Q55" s="93"/>
     </row>
-    <row r="56" spans="2:17" s="73" customFormat="1" ht="20.399999999999999" x14ac:dyDescent="0.3">
+    <row r="56" spans="2:17" s="73" customFormat="1" ht="20.25" x14ac:dyDescent="0.25">
       <c r="B56" s="93"/>
       <c r="C56" s="93"/>
       <c r="F56" s="223" t="s">
@@ -7500,7 +7500,7 @@
       <c r="P56" s="93"/>
       <c r="Q56" s="93"/>
     </row>
-    <row r="57" spans="2:17" s="73" customFormat="1" ht="17.399999999999999" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="57" spans="2:17" s="73" customFormat="1" ht="18.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B57" s="93"/>
       <c r="C57" s="93"/>
       <c r="F57" s="261"/>
@@ -7509,7 +7509,7 @@
       <c r="P57" s="93"/>
       <c r="Q57" s="93"/>
     </row>
-    <row r="58" spans="2:17" s="73" customFormat="1" ht="36" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="58" spans="2:17" s="73" customFormat="1" ht="36" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B58" s="93"/>
       <c r="C58" s="93"/>
       <c r="F58" s="251" t="s">
@@ -7531,7 +7531,7 @@
       <c r="P58" s="93"/>
       <c r="Q58" s="93"/>
     </row>
-    <row r="59" spans="2:17" s="73" customFormat="1" ht="23.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="59" spans="2:17" s="73" customFormat="1" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B59" s="93"/>
       <c r="C59" s="93"/>
       <c r="F59" s="133" t="s">
@@ -7561,7 +7561,7 @@
       <c r="P59" s="93"/>
       <c r="Q59" s="93"/>
     </row>
-    <row r="60" spans="2:17" s="73" customFormat="1" ht="18" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="60" spans="2:17" s="73" customFormat="1" ht="18.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B60" s="93"/>
       <c r="C60" s="93"/>
       <c r="F60" s="137"/>
@@ -7589,7 +7589,7 @@
       <c r="P60" s="93"/>
       <c r="Q60" s="93"/>
     </row>
-    <row r="61" spans="2:17" s="73" customFormat="1" ht="17.399999999999999" x14ac:dyDescent="0.3">
+    <row r="61" spans="2:17" s="73" customFormat="1" ht="18" x14ac:dyDescent="0.25">
       <c r="B61" s="93"/>
       <c r="C61" s="93"/>
       <c r="F61" s="77"/>
@@ -7614,7 +7614,7 @@
       <c r="P61" s="93"/>
       <c r="Q61" s="93"/>
     </row>
-    <row r="62" spans="2:17" s="73" customFormat="1" ht="17.399999999999999" x14ac:dyDescent="0.3">
+    <row r="62" spans="2:17" s="73" customFormat="1" ht="18" x14ac:dyDescent="0.25">
       <c r="B62" s="93"/>
       <c r="C62" s="93"/>
       <c r="F62" s="77"/>
@@ -7639,7 +7639,7 @@
       <c r="P62" s="93"/>
       <c r="Q62" s="93"/>
     </row>
-    <row r="63" spans="2:17" s="73" customFormat="1" ht="17.399999999999999" x14ac:dyDescent="0.3">
+    <row r="63" spans="2:17" s="73" customFormat="1" ht="18" x14ac:dyDescent="0.25">
       <c r="B63" s="93"/>
       <c r="C63" s="93"/>
       <c r="F63" s="77"/>
@@ -7651,7 +7651,7 @@
       <c r="P63" s="93"/>
       <c r="Q63" s="93"/>
     </row>
-    <row r="64" spans="2:17" s="73" customFormat="1" ht="17.399999999999999" x14ac:dyDescent="0.3">
+    <row r="64" spans="2:17" s="73" customFormat="1" ht="18" x14ac:dyDescent="0.25">
       <c r="B64" s="93"/>
       <c r="C64" s="93"/>
       <c r="F64" s="286" t="s">
@@ -7666,7 +7666,7 @@
       <c r="P64" s="93"/>
       <c r="Q64" s="93"/>
     </row>
-    <row r="65" spans="2:17" s="73" customFormat="1" ht="40.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="65" spans="2:17" s="73" customFormat="1" ht="40.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B65" s="93"/>
       <c r="C65" s="93"/>
       <c r="F65" s="220" t="s">
@@ -7681,7 +7681,7 @@
       <c r="P65" s="93"/>
       <c r="Q65" s="93"/>
     </row>
-    <row r="66" spans="2:17" s="73" customFormat="1" ht="40.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="66" spans="2:17" s="73" customFormat="1" ht="40.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B66" s="93"/>
       <c r="C66" s="93"/>
       <c r="F66" s="220" t="s">
@@ -7696,7 +7696,7 @@
       <c r="P66" s="93"/>
       <c r="Q66" s="93"/>
     </row>
-    <row r="67" spans="2:17" s="73" customFormat="1" ht="20.399999999999999" x14ac:dyDescent="0.3">
+    <row r="67" spans="2:17" s="73" customFormat="1" ht="20.25" x14ac:dyDescent="0.25">
       <c r="B67" s="93"/>
       <c r="C67" s="93"/>
       <c r="F67" s="223" t="s">
@@ -7711,7 +7711,7 @@
       <c r="P67" s="93"/>
       <c r="Q67" s="93"/>
     </row>
-    <row r="68" spans="2:17" s="73" customFormat="1" ht="18" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="68" spans="2:17" s="73" customFormat="1" ht="18.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B68" s="93"/>
       <c r="C68" s="93"/>
       <c r="F68" s="77"/>
@@ -7723,7 +7723,7 @@
       <c r="P68" s="93"/>
       <c r="Q68" s="93"/>
     </row>
-    <row r="69" spans="2:17" s="73" customFormat="1" ht="19.2" x14ac:dyDescent="0.3">
+    <row r="69" spans="2:17" s="73" customFormat="1" ht="21" x14ac:dyDescent="0.25">
       <c r="B69" s="93"/>
       <c r="C69" s="93"/>
       <c r="F69" s="139" t="s">
@@ -7737,7 +7737,7 @@
       <c r="I69" s="255"/>
       <c r="J69" s="157">
         <f>IF(FACTIBILIDAD!D49=0,"",FACTIBILIDAD!D49)</f>
-        <v>4444</v>
+        <v>66666</v>
       </c>
       <c r="K69" s="158" t="s">
         <v>322</v>
@@ -7745,7 +7745,7 @@
       <c r="P69" s="93"/>
       <c r="Q69" s="93"/>
     </row>
-    <row r="70" spans="2:17" s="73" customFormat="1" ht="19.2" x14ac:dyDescent="0.3">
+    <row r="70" spans="2:17" s="73" customFormat="1" ht="21" x14ac:dyDescent="0.25">
       <c r="B70" s="93"/>
       <c r="C70" s="93"/>
       <c r="F70" s="74" t="s">
@@ -7767,7 +7767,7 @@
       <c r="P70" s="93"/>
       <c r="Q70" s="93"/>
     </row>
-    <row r="71" spans="2:17" s="73" customFormat="1" ht="19.2" x14ac:dyDescent="0.3">
+    <row r="71" spans="2:17" s="73" customFormat="1" ht="21" x14ac:dyDescent="0.25">
       <c r="B71" s="93"/>
       <c r="C71" s="93"/>
       <c r="F71" s="74" t="s">
@@ -7789,7 +7789,7 @@
       <c r="P71" s="93"/>
       <c r="Q71" s="93"/>
     </row>
-    <row r="72" spans="2:17" s="73" customFormat="1" ht="19.8" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="72" spans="2:17" s="73" customFormat="1" ht="21.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B72" s="93"/>
       <c r="C72" s="93"/>
       <c r="F72" s="128" t="s">
@@ -7811,7 +7811,7 @@
       <c r="P72" s="93"/>
       <c r="Q72" s="93"/>
     </row>
-    <row r="73" spans="2:17" s="73" customFormat="1" ht="18" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="73" spans="2:17" s="73" customFormat="1" ht="18.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B73" s="93"/>
       <c r="C73" s="93"/>
       <c r="F73" s="77"/>
@@ -7823,7 +7823,7 @@
       <c r="P73" s="93"/>
       <c r="Q73" s="93"/>
     </row>
-    <row r="74" spans="2:17" s="73" customFormat="1" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="74" spans="2:17" s="73" customFormat="1" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B74" s="93"/>
       <c r="C74" s="93"/>
       <c r="F74" s="251" t="s">
@@ -7837,7 +7837,7 @@
       <c r="P74" s="93"/>
       <c r="Q74" s="93"/>
     </row>
-    <row r="75" spans="2:17" s="73" customFormat="1" ht="18" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="75" spans="2:17" s="73" customFormat="1" ht="18.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B75" s="93"/>
       <c r="C75" s="93"/>
       <c r="F75" s="77"/>
@@ -7849,7 +7849,7 @@
       <c r="P75" s="93"/>
       <c r="Q75" s="93"/>
     </row>
-    <row r="76" spans="2:17" s="73" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="76" spans="2:17" s="73" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B76" s="93"/>
       <c r="C76" s="93"/>
       <c r="D76" s="113"/>
@@ -7869,7 +7869,7 @@
       <c r="P76" s="93"/>
       <c r="Q76" s="93"/>
     </row>
-    <row r="77" spans="2:17" s="73" customFormat="1" ht="40.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="77" spans="2:17" s="73" customFormat="1" ht="40.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B77" s="93"/>
       <c r="C77" s="93"/>
       <c r="F77" s="250" t="s">
@@ -7884,7 +7884,7 @@
       <c r="P77" s="93"/>
       <c r="Q77" s="93"/>
     </row>
-    <row r="78" spans="2:17" s="73" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="78" spans="2:17" s="73" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B78" s="93"/>
       <c r="C78" s="93"/>
       <c r="F78" s="220">
@@ -7899,7 +7899,7 @@
       <c r="P78" s="93"/>
       <c r="Q78" s="93"/>
     </row>
-    <row r="79" spans="2:17" s="73" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="79" spans="2:17" s="73" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B79" s="93"/>
       <c r="C79" s="93"/>
       <c r="F79" s="220">
@@ -7914,7 +7914,7 @@
       <c r="P79" s="93"/>
       <c r="Q79" s="93"/>
     </row>
-    <row r="80" spans="2:17" s="73" customFormat="1" ht="17.399999999999999" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="80" spans="2:17" s="73" customFormat="1" ht="18.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B80" s="93"/>
       <c r="C80" s="93"/>
       <c r="F80" s="285">
@@ -7929,7 +7929,7 @@
       <c r="P80" s="93"/>
       <c r="Q80" s="93"/>
     </row>
-    <row r="81" spans="1:17" s="73" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="81" spans="1:17" s="73" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B81" s="93"/>
       <c r="C81" s="93"/>
       <c r="F81" s="245" t="s">
@@ -7944,7 +7944,7 @@
       <c r="P81" s="93"/>
       <c r="Q81" s="93"/>
     </row>
-    <row r="82" spans="1:17" s="73" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="82" spans="1:17" s="73" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B82" s="93"/>
       <c r="C82" s="93"/>
       <c r="F82" s="94" t="s">
@@ -7964,7 +7964,7 @@
       <c r="P82" s="93"/>
       <c r="Q82" s="93"/>
     </row>
-    <row r="83" spans="1:17" s="73" customFormat="1" ht="17.399999999999999" x14ac:dyDescent="0.3">
+    <row r="83" spans="1:17" s="73" customFormat="1" ht="18" x14ac:dyDescent="0.25">
       <c r="B83" s="93"/>
       <c r="C83" s="93"/>
       <c r="F83" s="95" t="str">
@@ -7987,7 +7987,7 @@
       <c r="P83" s="93"/>
       <c r="Q83" s="93"/>
     </row>
-    <row r="84" spans="1:17" s="73" customFormat="1" ht="17.399999999999999" x14ac:dyDescent="0.3">
+    <row r="84" spans="1:17" s="73" customFormat="1" ht="18" x14ac:dyDescent="0.25">
       <c r="B84" s="93"/>
       <c r="C84" s="93"/>
       <c r="F84" s="95"/>
@@ -8005,7 +8005,7 @@
       <c r="P84" s="93"/>
       <c r="Q84" s="93"/>
     </row>
-    <row r="85" spans="1:17" s="73" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="85" spans="1:17" s="73" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B85" s="93"/>
       <c r="C85" s="93"/>
       <c r="F85" s="94" t="s">
@@ -8022,7 +8022,7 @@
       <c r="P85" s="93"/>
       <c r="Q85" s="93"/>
     </row>
-    <row r="86" spans="1:17" s="73" customFormat="1" ht="18" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="86" spans="1:17" s="73" customFormat="1" ht="18.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B86" s="93"/>
       <c r="C86" s="93"/>
       <c r="D86" s="77"/>
@@ -8040,7 +8040,7 @@
       <c r="P86" s="93"/>
       <c r="Q86" s="93"/>
     </row>
-    <row r="87" spans="1:17" s="73" customFormat="1" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="87" spans="1:17" s="73" customFormat="1" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B87" s="93"/>
       <c r="C87" s="93"/>
       <c r="D87" s="77"/>
@@ -8060,7 +8060,7 @@
       <c r="P87" s="93"/>
       <c r="Q87" s="93"/>
     </row>
-    <row r="88" spans="1:17" s="73" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="88" spans="1:17" s="73" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B88" s="93"/>
       <c r="C88" s="93"/>
       <c r="D88" s="77"/>
@@ -8080,7 +8080,7 @@
       <c r="P88" s="93"/>
       <c r="Q88" s="93"/>
     </row>
-    <row r="89" spans="1:17" s="73" customFormat="1" ht="45" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="89" spans="1:17" s="73" customFormat="1" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B89" s="93"/>
       <c r="C89" s="93"/>
       <c r="D89" s="77"/>
@@ -8098,7 +8098,7 @@
       <c r="P89" s="93"/>
       <c r="Q89" s="93"/>
     </row>
-    <row r="90" spans="1:17" s="73" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="90" spans="1:17" s="73" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B90" s="93"/>
       <c r="C90" s="93"/>
       <c r="D90" s="77"/>
@@ -8116,7 +8116,7 @@
       <c r="P90" s="93"/>
       <c r="Q90" s="93"/>
     </row>
-    <row r="91" spans="1:17" s="73" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="91" spans="1:17" s="73" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B91" s="93"/>
       <c r="C91" s="93"/>
       <c r="D91" s="77"/>
@@ -8134,13 +8134,13 @@
       <c r="P91" s="93"/>
       <c r="Q91" s="93"/>
     </row>
-    <row r="92" spans="1:17" s="73" customFormat="1" ht="16.8" x14ac:dyDescent="0.3">
+    <row r="92" spans="1:17" s="73" customFormat="1" ht="18" x14ac:dyDescent="0.25">
       <c r="B92" s="93"/>
       <c r="C92" s="93"/>
       <c r="P92" s="93"/>
       <c r="Q92" s="93"/>
     </row>
-    <row r="93" spans="1:17" s="73" customFormat="1" ht="21" x14ac:dyDescent="0.3">
+    <row r="93" spans="1:17" s="73" customFormat="1" ht="19.5" x14ac:dyDescent="0.25">
       <c r="A93" s="142"/>
       <c r="B93" s="141"/>
       <c r="C93" s="141"/>
@@ -8149,7 +8149,7 @@
       <c r="P93" s="141"/>
       <c r="Q93" s="141"/>
     </row>
-    <row r="94" spans="1:17" s="73" customFormat="1" ht="21" x14ac:dyDescent="0.3">
+    <row r="94" spans="1:17" s="73" customFormat="1" ht="19.5" x14ac:dyDescent="0.25">
       <c r="A94" s="142"/>
       <c r="B94" s="141"/>
       <c r="C94" s="141"/>
@@ -8158,7 +8158,7 @@
       <c r="P94" s="141"/>
       <c r="Q94" s="141"/>
     </row>
-    <row r="95" spans="1:17" ht="21" x14ac:dyDescent="0.3">
+    <row r="95" spans="1:17" ht="19.5" x14ac:dyDescent="0.25">
       <c r="A95" s="142"/>
       <c r="B95" s="141"/>
       <c r="C95" s="141"/>
@@ -8177,7 +8177,7 @@
       <c r="P95" s="141"/>
       <c r="Q95" s="141"/>
     </row>
-    <row r="96" spans="1:17" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="96" spans="1:17" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A96" s="145"/>
       <c r="B96" s="144"/>
       <c r="C96" s="144"/>
@@ -8196,7 +8196,7 @@
       <c r="P96" s="144"/>
       <c r="Q96" s="144"/>
     </row>
-    <row r="97" spans="1:17" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="97" spans="1:17" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A97" s="145"/>
       <c r="B97" s="144"/>
       <c r="C97" s="144"/>
@@ -8215,7 +8215,7 @@
       <c r="P97" s="144"/>
       <c r="Q97" s="144"/>
     </row>
-    <row r="98" spans="1:17" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="98" spans="1:17" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A98" s="145"/>
       <c r="B98" s="144"/>
       <c r="C98" s="144"/>
@@ -8234,7 +8234,7 @@
       <c r="P98" s="144"/>
       <c r="Q98" s="144"/>
     </row>
-    <row r="99" spans="1:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="99" spans="1:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A99" s="145"/>
       <c r="B99" s="144"/>
       <c r="C99" s="144"/>
@@ -8253,24 +8253,24 @@
       <c r="P99" s="144"/>
       <c r="Q99" s="144"/>
     </row>
-    <row r="100" spans="1:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="100" spans="1:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C100" s="144"/>
       <c r="P100" s="144"/>
     </row>
-    <row r="101" spans="1:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="101" spans="1:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="P101" s="144"/>
     </row>
-    <row r="102" spans="1:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="103" spans="1:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="104" spans="1:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="105" spans="1:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="106" spans="1:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="107" spans="1:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="108" spans="1:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="109" spans="1:17" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="110" spans="1:17" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="111" spans="1:17" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="142" spans="7:12" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="102" spans="1:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="103" spans="1:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="104" spans="1:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="105" spans="1:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="106" spans="1:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="107" spans="1:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="108" spans="1:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="109" spans="1:17" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="110" spans="1:17" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="111" spans="1:17" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="142" spans="7:12" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="G142" s="192" t="s">
         <v>336</v>
       </c>
@@ -8280,7 +8280,7 @@
       <c r="K142" s="192"/>
       <c r="L142" s="193"/>
     </row>
-    <row r="143" spans="7:12" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="143" spans="7:12" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="G143" s="146" t="s">
         <v>335</v>
       </c>
@@ -8655,20 +8655,20 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
   <sheetPr codeName="Hoja5"/>
   <dimension ref="A1:AS23"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="2" width="52.88671875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="11.44140625" style="11"/>
-    <col min="5" max="5" width="53.6640625" customWidth="1"/>
-    <col min="6" max="6" width="12.6640625" style="11" customWidth="1"/>
+    <col min="2" max="2" width="52.85546875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="11.42578125" style="11"/>
+    <col min="5" max="5" width="53.7109375" customWidth="1"/>
+    <col min="6" max="6" width="12.7109375" style="11" customWidth="1"/>
     <col min="15" max="15" width="13" hidden="1" customWidth="1"/>
     <col min="16" max="16" width="14" hidden="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:45" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:45" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="E1" s="162"/>
     </row>
-    <row r="2" spans="1:45" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:45" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="E2" s="163" t="s">
         <v>323</v>
       </c>
@@ -8677,7 +8677,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:45" ht="21.6" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="3" spans="1:45" ht="21.75" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A3" s="165">
         <v>1</v>
       </c>
@@ -8700,7 +8700,7 @@
         <v>325</v>
       </c>
     </row>
-    <row r="4" spans="1:45" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A4" s="170">
         <v>2</v>
       </c>
@@ -8718,7 +8718,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="5" spans="1:45" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A5" s="170">
         <v>3</v>
       </c>
@@ -8729,7 +8729,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="6" spans="1:45" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:45" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A6" s="174">
         <v>4</v>
       </c>
@@ -8740,8 +8740,8 @@
         <v>325</v>
       </c>
     </row>
-    <row r="18" spans="2:4" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
-    <row r="19" spans="2:4" x14ac:dyDescent="0.3">
+    <row r="18" spans="2:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="19" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B19" s="177" t="s">
         <v>329</v>
       </c>
@@ -8750,7 +8750,7 @@
       </c>
       <c r="D19" s="179"/>
     </row>
-    <row r="20" spans="2:4" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="20" spans="2:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B20" s="180" t="s">
         <v>330</v>
       </c>
@@ -8762,7 +8762,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="21" spans="2:4" x14ac:dyDescent="0.3">
+    <row r="21" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B21" s="183" t="s">
         <v>331</v>
       </c>
@@ -8774,7 +8774,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="22" spans="2:4" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="22" spans="2:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B22" s="186" t="s">
         <v>332</v>
       </c>
@@ -8786,7 +8786,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="23" spans="2:4" x14ac:dyDescent="0.3">
+    <row r="23" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B23" s="6"/>
       <c r="C23" s="189"/>
     </row>
@@ -8808,29 +8808,29 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:Q90"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="11.44140625" defaultRowHeight="13.2" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11.42578125" defaultRowHeight="13.5" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="2" width="4.88671875" style="62" customWidth="1"/>
-    <col min="3" max="4" width="4.88671875" style="61" customWidth="1"/>
-    <col min="5" max="5" width="5.33203125" style="61" customWidth="1"/>
+    <col min="1" max="2" width="4.85546875" style="62" customWidth="1"/>
+    <col min="3" max="4" width="4.85546875" style="61" customWidth="1"/>
+    <col min="5" max="5" width="5.28515625" style="61" customWidth="1"/>
     <col min="6" max="6" width="47" style="61" customWidth="1"/>
-    <col min="7" max="7" width="9.44140625" style="61" customWidth="1"/>
+    <col min="7" max="7" width="9.42578125" style="61" customWidth="1"/>
     <col min="8" max="8" width="12" style="61" customWidth="1"/>
-    <col min="9" max="9" width="44.33203125" style="61" customWidth="1"/>
+    <col min="9" max="9" width="44.28515625" style="61" customWidth="1"/>
     <col min="10" max="10" width="20" style="61" customWidth="1"/>
-    <col min="11" max="11" width="12.33203125" style="61" customWidth="1"/>
-    <col min="12" max="12" width="33.88671875" style="61" customWidth="1"/>
-    <col min="13" max="13" width="5.6640625" style="61" customWidth="1"/>
-    <col min="14" max="14" width="5.44140625" style="61" customWidth="1"/>
+    <col min="11" max="11" width="12.28515625" style="61" customWidth="1"/>
+    <col min="12" max="12" width="33.85546875" style="61" customWidth="1"/>
+    <col min="13" max="13" width="5.7109375" style="61" customWidth="1"/>
+    <col min="14" max="14" width="5.42578125" style="61" customWidth="1"/>
     <col min="15" max="15" width="9" style="61" hidden="1" customWidth="1"/>
-    <col min="16" max="16" width="5.44140625" style="62" customWidth="1"/>
-    <col min="17" max="17" width="9.109375" style="62" customWidth="1"/>
-    <col min="18" max="18" width="11.44140625" style="61"/>
-    <col min="19" max="19" width="17.88671875" style="61" bestFit="1" customWidth="1"/>
-    <col min="20" max="16384" width="11.44140625" style="61"/>
+    <col min="16" max="16" width="5.42578125" style="62" customWidth="1"/>
+    <col min="17" max="17" width="9.140625" style="62" customWidth="1"/>
+    <col min="18" max="18" width="11.42578125" style="61"/>
+    <col min="19" max="19" width="17.85546875" style="61" bestFit="1" customWidth="1"/>
+    <col min="20" max="16384" width="11.42578125" style="61"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:17" s="63" customFormat="1" ht="17.399999999999999" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:17" s="63" customFormat="1" ht="18" x14ac:dyDescent="0.25">
       <c r="A1" s="66"/>
       <c r="B1" s="66"/>
       <c r="C1" s="66"/>
@@ -8849,7 +8849,7 @@
       <c r="P1" s="66"/>
       <c r="Q1" s="66"/>
     </row>
-    <row r="2" spans="1:17" s="63" customFormat="1" ht="17.399999999999999" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:17" s="63" customFormat="1" ht="18" x14ac:dyDescent="0.25">
       <c r="A2" s="66"/>
       <c r="B2" s="66"/>
       <c r="C2" s="66"/>
@@ -8868,14 +8868,14 @@
       <c r="P2" s="66"/>
       <c r="Q2" s="66"/>
     </row>
-    <row r="3" spans="1:17" s="63" customFormat="1" ht="17.399999999999999" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:17" s="63" customFormat="1" ht="18.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A3" s="66"/>
       <c r="B3" s="66"/>
       <c r="C3" s="66"/>
       <c r="P3" s="66"/>
       <c r="Q3" s="66"/>
     </row>
-    <row r="4" spans="1:17" s="63" customFormat="1" ht="45.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:17" s="63" customFormat="1" ht="45.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="66"/>
       <c r="B4" s="66"/>
       <c r="C4" s="66"/>
@@ -8887,7 +8887,7 @@
       <c r="P4" s="66"/>
       <c r="Q4" s="66"/>
     </row>
-    <row r="5" spans="1:17" s="63" customFormat="1" ht="17.399999999999999" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:17" s="63" customFormat="1" ht="18.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A5" s="66"/>
       <c r="B5" s="66"/>
       <c r="C5" s="66"/>
@@ -8916,7 +8916,7 @@
       <c r="P7" s="66"/>
       <c r="Q7" s="66"/>
     </row>
-    <row r="8" spans="1:17" s="63" customFormat="1" ht="18" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:17" s="63" customFormat="1" ht="18.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A8" s="66"/>
       <c r="B8" s="66"/>
       <c r="C8" s="66"/>
@@ -8924,7 +8924,7 @@
       <c r="P8" s="66"/>
       <c r="Q8" s="66"/>
     </row>
-    <row r="9" spans="1:17" s="63" customFormat="1" ht="23.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:17" s="63" customFormat="1" ht="23.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="66"/>
       <c r="B9" s="66"/>
       <c r="C9" s="66"/>
@@ -8940,14 +8940,14 @@
       <c r="P9" s="66"/>
       <c r="Q9" s="66"/>
     </row>
-    <row r="10" spans="1:17" s="63" customFormat="1" ht="17.399999999999999" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:17" s="63" customFormat="1" ht="18.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A10" s="66"/>
       <c r="B10" s="66"/>
       <c r="C10" s="66"/>
       <c r="P10" s="66"/>
       <c r="Q10" s="66"/>
     </row>
-    <row r="11" spans="1:17" s="63" customFormat="1" ht="20.399999999999999" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:17" s="63" customFormat="1" ht="20.25" x14ac:dyDescent="0.3">
       <c r="A11" s="66"/>
       <c r="B11" s="66"/>
       <c r="C11" s="66"/>
@@ -8964,7 +8964,7 @@
       <c r="P11" s="66"/>
       <c r="Q11" s="66"/>
     </row>
-    <row r="12" spans="1:17" s="63" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:17" s="63" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="66"/>
       <c r="B12" s="66"/>
       <c r="C12" s="66"/>
@@ -8981,7 +8981,7 @@
       <c r="P12" s="66"/>
       <c r="Q12" s="66"/>
     </row>
-    <row r="13" spans="1:17" s="63" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:17" s="63" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="66"/>
       <c r="B13" s="66"/>
       <c r="C13" s="66"/>
@@ -8998,7 +8998,7 @@
       <c r="P13" s="66"/>
       <c r="Q13" s="66"/>
     </row>
-    <row r="14" spans="1:17" s="63" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:17" s="63" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="66"/>
       <c r="B14" s="66"/>
       <c r="C14" s="66"/>
@@ -9015,7 +9015,7 @@
       <c r="P14" s="66"/>
       <c r="Q14" s="66"/>
     </row>
-    <row r="15" spans="1:17" s="63" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:17" s="63" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="66"/>
       <c r="B15" s="66"/>
       <c r="C15" s="66"/>
@@ -9032,7 +9032,7 @@
       <c r="P15" s="66"/>
       <c r="Q15" s="66"/>
     </row>
-    <row r="16" spans="1:17" s="63" customFormat="1" ht="17.399999999999999" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:17" s="63" customFormat="1" ht="18" x14ac:dyDescent="0.25">
       <c r="A16" s="66"/>
       <c r="B16" s="66"/>
       <c r="C16" s="66"/>
@@ -9049,7 +9049,7 @@
       <c r="P16" s="66"/>
       <c r="Q16" s="66"/>
     </row>
-    <row r="17" spans="1:17" s="63" customFormat="1" ht="17.399999999999999" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:17" s="63" customFormat="1" ht="18" x14ac:dyDescent="0.25">
       <c r="A17" s="66"/>
       <c r="B17" s="66"/>
       <c r="C17" s="66"/>
@@ -9071,7 +9071,7 @@
       <c r="P17" s="66"/>
       <c r="Q17" s="66"/>
     </row>
-    <row r="18" spans="1:17" s="63" customFormat="1" ht="18" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:17" s="63" customFormat="1" ht="18.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A18" s="66"/>
       <c r="B18" s="66"/>
       <c r="C18" s="66"/>
@@ -9088,7 +9088,7 @@
       <c r="P18" s="66"/>
       <c r="Q18" s="66"/>
     </row>
-    <row r="19" spans="1:17" s="63" customFormat="1" ht="18" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:17" s="63" customFormat="1" ht="18.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A19" s="66"/>
       <c r="B19" s="66"/>
       <c r="C19" s="66"/>
@@ -9100,7 +9100,7 @@
       <c r="P19" s="66"/>
       <c r="Q19" s="66"/>
     </row>
-    <row r="20" spans="1:17" s="63" customFormat="1" ht="20.399999999999999" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:17" s="63" customFormat="1" ht="20.25" x14ac:dyDescent="0.3">
       <c r="A20" s="66"/>
       <c r="B20" s="66"/>
       <c r="C20" s="66"/>
@@ -9116,7 +9116,7 @@
       <c r="P20" s="66"/>
       <c r="Q20" s="66"/>
     </row>
-    <row r="21" spans="1:17" s="63" customFormat="1" ht="18" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:17" s="63" customFormat="1" ht="18.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A21" s="66"/>
       <c r="B21" s="66"/>
       <c r="C21" s="66"/>
@@ -9130,7 +9130,7 @@
       <c r="P21" s="66"/>
       <c r="Q21" s="66"/>
     </row>
-    <row r="22" spans="1:17" s="63" customFormat="1" ht="36" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:17" s="63" customFormat="1" ht="36" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A22" s="66"/>
       <c r="B22" s="66"/>
       <c r="C22" s="66"/>
@@ -9149,7 +9149,7 @@
       <c r="P22" s="66"/>
       <c r="Q22" s="66"/>
     </row>
-    <row r="23" spans="1:17" s="63" customFormat="1" ht="36" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:17" s="63" customFormat="1" ht="36" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A23" s="66"/>
       <c r="B23" s="66"/>
       <c r="C23" s="66"/>
@@ -9165,7 +9165,7 @@
       <c r="P23" s="66"/>
       <c r="Q23" s="66"/>
     </row>
-    <row r="24" spans="1:17" s="63" customFormat="1" ht="36.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:17" s="63" customFormat="1" ht="36.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A24" s="66"/>
       <c r="B24" s="66"/>
       <c r="C24" s="66"/>
@@ -9181,7 +9181,7 @@
       <c r="P24" s="66"/>
       <c r="Q24" s="66"/>
     </row>
-    <row r="25" spans="1:17" s="63" customFormat="1" ht="36.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:17" s="63" customFormat="1" ht="36.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A25" s="66"/>
       <c r="B25" s="66"/>
       <c r="C25" s="66"/>
@@ -9194,7 +9194,7 @@
       <c r="P25" s="66"/>
       <c r="Q25" s="66"/>
     </row>
-    <row r="26" spans="1:17" s="63" customFormat="1" ht="20.399999999999999" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:17" s="63" customFormat="1" ht="20.25" x14ac:dyDescent="0.3">
       <c r="A26" s="66"/>
       <c r="B26" s="66"/>
       <c r="C26" s="66"/>
@@ -9210,7 +9210,7 @@
       <c r="P26" s="66"/>
       <c r="Q26" s="66"/>
     </row>
-    <row r="27" spans="1:17" s="63" customFormat="1" ht="21" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="27" spans="1:17" s="63" customFormat="1" ht="21" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A27" s="66"/>
       <c r="B27" s="66"/>
       <c r="C27" s="66"/>
@@ -9224,7 +9224,7 @@
       <c r="P27" s="66"/>
       <c r="Q27" s="66"/>
     </row>
-    <row r="28" spans="1:17" s="63" customFormat="1" ht="20.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:17" s="63" customFormat="1" ht="20.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A28" s="66"/>
       <c r="B28" s="66"/>
       <c r="C28" s="66"/>
@@ -9280,7 +9280,7 @@
       <c r="P31" s="66"/>
       <c r="Q31" s="66"/>
     </row>
-    <row r="32" spans="1:17" s="63" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:17" s="63" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A32" s="66"/>
       <c r="B32" s="66"/>
       <c r="C32" s="66"/>
@@ -9354,7 +9354,7 @@
       <c r="P36" s="66"/>
       <c r="Q36" s="66"/>
     </row>
-    <row r="37" spans="1:17" s="63" customFormat="1" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="37" spans="1:17" s="63" customFormat="1" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A37" s="66"/>
       <c r="B37" s="66"/>
       <c r="C37" s="66"/>
@@ -9368,7 +9368,7 @@
       <c r="P37" s="66"/>
       <c r="Q37" s="66"/>
     </row>
-    <row r="38" spans="1:17" s="63" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:17" s="63" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A38" s="66"/>
       <c r="B38" s="66"/>
       <c r="C38" s="66"/>
@@ -9384,7 +9384,7 @@
       <c r="P38" s="66"/>
       <c r="Q38" s="66"/>
     </row>
-    <row r="39" spans="1:17" s="63" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:17" s="63" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A39" s="66"/>
       <c r="B39" s="66"/>
       <c r="C39" s="66"/>
@@ -9405,7 +9405,7 @@
       <c r="P39" s="66"/>
       <c r="Q39" s="66"/>
     </row>
-    <row r="40" spans="1:17" s="63" customFormat="1" ht="17.399999999999999" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:17" s="63" customFormat="1" ht="18" x14ac:dyDescent="0.25">
       <c r="A40" s="66"/>
       <c r="B40" s="66"/>
       <c r="C40" s="66"/>
@@ -9429,7 +9429,7 @@
       <c r="P40" s="66"/>
       <c r="Q40" s="66"/>
     </row>
-    <row r="41" spans="1:17" s="63" customFormat="1" ht="17.399999999999999" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:17" s="63" customFormat="1" ht="18" x14ac:dyDescent="0.25">
       <c r="A41" s="66"/>
       <c r="B41" s="66"/>
       <c r="C41" s="66"/>
@@ -9466,7 +9466,7 @@
       <c r="P42" s="66"/>
       <c r="Q42" s="66"/>
     </row>
-    <row r="43" spans="1:17" s="63" customFormat="1" ht="17.399999999999999" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:17" s="63" customFormat="1" ht="18" x14ac:dyDescent="0.25">
       <c r="A43" s="66"/>
       <c r="B43" s="66"/>
       <c r="C43" s="66"/>
@@ -9487,7 +9487,7 @@
       <c r="P43" s="66"/>
       <c r="Q43" s="66"/>
     </row>
-    <row r="44" spans="1:17" s="63" customFormat="1" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="44" spans="1:17" s="63" customFormat="1" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A44" s="66"/>
       <c r="B44" s="66"/>
       <c r="C44" s="66"/>
@@ -9508,7 +9508,7 @@
       <c r="P44" s="66"/>
       <c r="Q44" s="66"/>
     </row>
-    <row r="45" spans="1:17" s="63" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:17" s="63" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A45" s="66"/>
       <c r="B45" s="66"/>
       <c r="C45" s="66"/>
@@ -9527,7 +9527,7 @@
       <c r="P45" s="66"/>
       <c r="Q45" s="66"/>
     </row>
-    <row r="46" spans="1:17" s="63" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:17" s="63" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A46" s="66"/>
       <c r="B46" s="66"/>
       <c r="C46" s="66"/>
@@ -9546,7 +9546,7 @@
       <c r="P46" s="66"/>
       <c r="Q46" s="66"/>
     </row>
-    <row r="47" spans="1:17" s="63" customFormat="1" ht="45" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:17" s="63" customFormat="1" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A47" s="66"/>
       <c r="B47" s="66"/>
       <c r="C47" s="66"/>
@@ -9565,7 +9565,7 @@
       <c r="P47" s="66"/>
       <c r="Q47" s="66"/>
     </row>
-    <row r="48" spans="1:17" s="63" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:17" s="63" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A48" s="66"/>
       <c r="B48" s="66"/>
       <c r="C48" s="66"/>
@@ -9584,7 +9584,7 @@
       <c r="P48" s="66"/>
       <c r="Q48" s="66"/>
     </row>
-    <row r="49" spans="1:17" s="63" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:17" s="63" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A49" s="66"/>
       <c r="B49" s="66"/>
       <c r="C49" s="66"/>
@@ -9603,7 +9603,7 @@
       <c r="P49" s="66"/>
       <c r="Q49" s="66"/>
     </row>
-    <row r="50" spans="1:17" s="63" customFormat="1" ht="16.8" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:17" s="63" customFormat="1" ht="18" x14ac:dyDescent="0.25">
       <c r="A50" s="66"/>
       <c r="B50" s="66"/>
       <c r="C50" s="66"/>
@@ -9613,7 +9613,7 @@
       <c r="P50" s="66"/>
       <c r="Q50" s="66"/>
     </row>
-    <row r="51" spans="1:17" s="63" customFormat="1" ht="21" x14ac:dyDescent="0.35">
+    <row r="51" spans="1:17" s="63" customFormat="1" ht="19.5" x14ac:dyDescent="0.25">
       <c r="A51" s="64"/>
       <c r="B51" s="64"/>
       <c r="C51" s="64"/>
@@ -9625,7 +9625,7 @@
       <c r="P51" s="64"/>
       <c r="Q51" s="64"/>
     </row>
-    <row r="52" spans="1:17" s="63" customFormat="1" ht="21" x14ac:dyDescent="0.35">
+    <row r="52" spans="1:17" s="63" customFormat="1" ht="19.5" x14ac:dyDescent="0.25">
       <c r="A52" s="64"/>
       <c r="B52" s="64"/>
       <c r="C52" s="64"/>
@@ -9634,7 +9634,7 @@
       <c r="P52" s="64"/>
       <c r="Q52" s="64"/>
     </row>
-    <row r="53" spans="1:17" ht="21" x14ac:dyDescent="0.35">
+    <row r="53" spans="1:17" ht="19.5" x14ac:dyDescent="0.25">
       <c r="A53" s="64"/>
       <c r="B53" s="64"/>
       <c r="C53" s="64"/>
@@ -9653,7 +9653,7 @@
       <c r="P53" s="64"/>
       <c r="Q53" s="64"/>
     </row>
-    <row r="54" spans="1:17" ht="13.8" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:17" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A54" s="59"/>
       <c r="B54" s="59"/>
       <c r="C54" s="59"/>
@@ -9672,7 +9672,7 @@
       <c r="P54" s="59"/>
       <c r="Q54" s="59"/>
     </row>
-    <row r="55" spans="1:17" ht="13.8" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:17" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A55" s="59"/>
       <c r="B55" s="59"/>
       <c r="C55" s="59"/>
@@ -9691,7 +9691,7 @@
       <c r="P55" s="59"/>
       <c r="Q55" s="59"/>
     </row>
-    <row r="56" spans="1:17" ht="13.8" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:17" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A56" s="59"/>
       <c r="B56" s="59"/>
       <c r="C56" s="59"/>
@@ -9710,7 +9710,7 @@
       <c r="P56" s="59"/>
       <c r="Q56" s="59"/>
     </row>
-    <row r="57" spans="1:17" ht="13.8" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:17" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A57" s="59"/>
       <c r="B57" s="59"/>
       <c r="C57" s="59"/>
@@ -9729,11 +9729,11 @@
       <c r="P57" s="59"/>
       <c r="Q57" s="59"/>
     </row>
-    <row r="58" spans="1:17" ht="13.8" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:17" ht="16.5" x14ac:dyDescent="0.3">
       <c r="C58" s="59"/>
       <c r="P58" s="59"/>
     </row>
-    <row r="59" spans="1:17" ht="13.8" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:17" ht="16.5" x14ac:dyDescent="0.3">
       <c r="C59" s="62"/>
       <c r="P59" s="59"/>
     </row>
@@ -9995,22 +9995,22 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0600-000000000000}">
   <sheetPr codeName="Hoja7"/>
   <dimension ref="A11:R54"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="4.109375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="2.44140625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.33203125" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="4.109375" customWidth="1"/>
-    <col min="6" max="6" width="9.33203125" customWidth="1"/>
+    <col min="1" max="1" width="4.140625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="2.42578125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="14.28515625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="4.140625" customWidth="1"/>
+    <col min="6" max="6" width="9.28515625" customWidth="1"/>
     <col min="8" max="8" width="5" customWidth="1"/>
-    <col min="10" max="10" width="10.88671875" customWidth="1"/>
-    <col min="11" max="11" width="15.44140625" customWidth="1"/>
-    <col min="12" max="12" width="10.88671875" customWidth="1"/>
-    <col min="13" max="13" width="22.33203125" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="17.44140625" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="10.85546875" customWidth="1"/>
+    <col min="11" max="11" width="15.42578125" customWidth="1"/>
+    <col min="12" max="12" width="10.85546875" customWidth="1"/>
+    <col min="13" max="13" width="22.28515625" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="17.42578125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="11" spans="1:18" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:18" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="197"/>
       <c r="B11" s="197"/>
       <c r="C11" s="197"/>
@@ -10023,7 +10023,7 @@
       <c r="H11" s="336"/>
       <c r="I11" s="336"/>
     </row>
-    <row r="12" spans="1:18" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:18" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="197"/>
       <c r="B12" s="197"/>
       <c r="C12" s="197"/>
@@ -10034,12 +10034,12 @@
       <c r="H12" s="336"/>
       <c r="I12" s="336"/>
     </row>
-    <row r="13" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:18" x14ac:dyDescent="0.25">
       <c r="O13" t="s">
         <v>357</v>
       </c>
     </row>
-    <row r="14" spans="1:18" ht="24" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:18" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="197" t="s">
         <v>338</v>
       </c>
@@ -10057,7 +10057,7 @@
         <v>355</v>
       </c>
     </row>
-    <row r="15" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A15" s="197"/>
       <c r="B15" s="197"/>
       <c r="C15" s="197"/>
@@ -10075,18 +10075,18 @@
       </c>
       <c r="O15">
         <f>'FORMATO  FACT'!J35-'FORMATO  FACT'!G35</f>
-        <v>3804</v>
+        <v>66026</v>
       </c>
       <c r="Q15">
         <f>N15*O15</f>
-        <v>380400</v>
+        <v>6602600</v>
       </c>
       <c r="R15">
         <f>IF((Q15)&lt;0,0,Q15)</f>
-        <v>380400</v>
-      </c>
-    </row>
-    <row r="16" spans="1:18" ht="24" customHeight="1" x14ac:dyDescent="0.3">
+        <v>6602600</v>
+      </c>
+    </row>
+    <row r="16" spans="1:18" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="197" t="s">
         <v>339</v>
       </c>
@@ -10116,7 +10116,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="1:18" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:18" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="F17" s="197"/>
       <c r="G17" s="197"/>
       <c r="H17" s="197"/>
@@ -10140,7 +10140,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="18" spans="1:18" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:18" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="197"/>
       <c r="B18" s="197"/>
       <c r="C18" s="197"/>
@@ -10162,7 +10162,7 @@
         <v>504.14</v>
       </c>
     </row>
-    <row r="19" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A19" s="197"/>
       <c r="B19" s="197"/>
       <c r="C19" s="197"/>
@@ -10180,10 +10180,10 @@
       </c>
       <c r="R19">
         <f ca="1">SUM(R15:R18)</f>
-        <v>380904.14</v>
-      </c>
-    </row>
-    <row r="20" spans="1:18" ht="24.9" customHeight="1" x14ac:dyDescent="0.3">
+        <v>6603104.1399999997</v>
+      </c>
+    </row>
+    <row r="20" spans="1:18" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="197" t="s">
         <v>340</v>
       </c>
@@ -10205,10 +10205,10 @@
       </c>
       <c r="R20">
         <f ca="1">R19*Q20</f>
-        <v>95226.035000000003</v>
-      </c>
-    </row>
-    <row r="21" spans="1:18" ht="24.9" customHeight="1" x14ac:dyDescent="0.3">
+        <v>1650776.0349999999</v>
+      </c>
+    </row>
+    <row r="21" spans="1:18" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="337" t="s">
         <v>348</v>
       </c>
@@ -10223,7 +10223,7 @@
       <c r="J21" s="337"/>
       <c r="K21" s="337"/>
     </row>
-    <row r="22" spans="1:18" ht="24.9" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:18" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="337" t="s">
         <v>349</v>
       </c>
@@ -10239,7 +10239,7 @@
       <c r="K22" s="337"/>
       <c r="N22" s="168"/>
     </row>
-    <row r="23" spans="1:18" ht="24.9" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:18" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A23" s="197" t="s">
         <v>346</v>
       </c>
@@ -10247,7 +10247,7 @@
       <c r="C23" s="197"/>
       <c r="D23" s="202">
         <f ca="1">R20</f>
-        <v>95226.035000000003</v>
+        <v>1650776.0349999999</v>
       </c>
       <c r="E23" s="337" t="s">
         <v>356</v>
@@ -10260,7 +10260,7 @@
       <c r="K23" s="337"/>
       <c r="P23" s="201"/>
     </row>
-    <row r="24" spans="1:18" ht="24.9" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:18" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="199" t="str">
         <f>FACTIBILIDAD!D12</f>
         <v xml:space="preserve">UNIFAMILIAR </v>
@@ -10281,7 +10281,7 @@
       <c r="J24" s="338"/>
       <c r="K24" s="338"/>
     </row>
-    <row r="25" spans="1:18" ht="24.9" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:18" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="197" t="s">
         <v>342</v>
       </c>
@@ -10296,7 +10296,7 @@
       <c r="J25" s="196"/>
       <c r="K25" s="196"/>
     </row>
-    <row r="26" spans="1:18" ht="24.9" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:18" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26" s="335" t="s">
         <v>343</v>
       </c>
@@ -10311,7 +10311,7 @@
       </c>
       <c r="I26" s="197"/>
     </row>
-    <row r="27" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A27" s="197"/>
       <c r="B27" s="197"/>
       <c r="C27" s="197"/>
@@ -10322,7 +10322,7 @@
       <c r="H27" s="197"/>
       <c r="I27" s="197"/>
     </row>
-    <row r="28" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A28" s="197"/>
       <c r="B28" s="197"/>
       <c r="C28" s="197"/>
@@ -10333,7 +10333,7 @@
       <c r="H28" s="197"/>
       <c r="I28" s="197"/>
     </row>
-    <row r="29" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A29" s="197"/>
       <c r="B29" s="197"/>
       <c r="C29" s="197"/>
@@ -10344,7 +10344,7 @@
       <c r="H29" s="197"/>
       <c r="I29" s="197"/>
     </row>
-    <row r="30" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A30" s="197"/>
       <c r="B30" s="197"/>
       <c r="C30" s="197"/>
@@ -10355,7 +10355,7 @@
       <c r="H30" s="197"/>
       <c r="I30" s="197"/>
     </row>
-    <row r="31" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A31" s="197"/>
       <c r="B31" s="197"/>
       <c r="C31" s="197"/>
@@ -10366,7 +10366,7 @@
       <c r="H31" s="197"/>
       <c r="I31" s="197"/>
     </row>
-    <row r="32" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A32" s="197"/>
       <c r="B32" s="197"/>
       <c r="C32" s="197"/>
@@ -10379,7 +10379,7 @@
       <c r="H32" s="198"/>
       <c r="I32" s="197"/>
     </row>
-    <row r="33" spans="1:14" ht="24.9" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:14" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A33" s="197"/>
       <c r="B33" s="197"/>
       <c r="C33" s="197"/>
@@ -10390,7 +10390,7 @@
       <c r="H33" s="197"/>
       <c r="I33" s="197"/>
     </row>
-    <row r="34" spans="1:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A34" s="197"/>
       <c r="B34" s="197"/>
       <c r="C34" s="197"/>
@@ -10401,7 +10401,7 @@
       <c r="H34" s="197"/>
       <c r="I34" s="197"/>
     </row>
-    <row r="35" spans="1:14" ht="24.9" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:14" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A35" s="197" t="s">
         <v>345</v>
       </c>
@@ -10414,7 +10414,7 @@
       <c r="H35" s="197"/>
       <c r="I35" s="197"/>
     </row>
-    <row r="36" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A36" s="197"/>
       <c r="B36" s="197"/>
       <c r="C36" s="197"/>
@@ -10425,7 +10425,7 @@
       <c r="H36" s="197"/>
       <c r="I36" s="197"/>
     </row>
-    <row r="37" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A37" s="197"/>
       <c r="B37" s="197"/>
       <c r="C37" s="197"/>
@@ -10436,7 +10436,7 @@
       <c r="H37" s="197"/>
       <c r="I37" s="197"/>
     </row>
-    <row r="38" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A38" s="197"/>
       <c r="B38" s="197"/>
       <c r="C38" s="197"/>
@@ -10447,7 +10447,7 @@
       <c r="H38" s="197"/>
       <c r="I38" s="197"/>
     </row>
-    <row r="39" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A39" s="197"/>
       <c r="B39" s="197"/>
       <c r="C39" s="197"/>
@@ -10458,7 +10458,7 @@
       <c r="H39" s="197"/>
       <c r="I39" s="197"/>
     </row>
-    <row r="40" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A40" s="197"/>
       <c r="B40" s="197"/>
       <c r="C40" s="197"/>
@@ -10469,7 +10469,7 @@
       <c r="H40" s="197"/>
       <c r="I40" s="197"/>
     </row>
-    <row r="41" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A41" s="197"/>
       <c r="B41" s="197"/>
       <c r="C41" s="197"/>
@@ -10480,7 +10480,7 @@
       <c r="H41" s="197"/>
       <c r="I41" s="197"/>
     </row>
-    <row r="43" spans="1:14" ht="21" x14ac:dyDescent="0.4">
+    <row r="43" spans="1:14" ht="21" x14ac:dyDescent="0.35">
       <c r="A43" s="195"/>
       <c r="B43" s="195"/>
       <c r="C43" s="195"/>
@@ -10496,7 +10496,7 @@
       <c r="M43" s="195"/>
       <c r="N43" s="195"/>
     </row>
-    <row r="44" spans="1:14" ht="21" x14ac:dyDescent="0.4">
+    <row r="44" spans="1:14" ht="21" x14ac:dyDescent="0.35">
       <c r="A44" s="195"/>
       <c r="B44" s="195"/>
       <c r="C44" s="195"/>
@@ -10512,7 +10512,7 @@
       <c r="M44" s="195"/>
       <c r="N44" s="195"/>
     </row>
-    <row r="45" spans="1:14" ht="21" x14ac:dyDescent="0.4">
+    <row r="45" spans="1:14" ht="21" x14ac:dyDescent="0.35">
       <c r="A45" s="195"/>
       <c r="B45" s="195"/>
       <c r="C45" s="195"/>
@@ -10528,7 +10528,7 @@
       <c r="M45" s="195"/>
       <c r="N45" s="195"/>
     </row>
-    <row r="46" spans="1:14" ht="21" x14ac:dyDescent="0.4">
+    <row r="46" spans="1:14" ht="21" x14ac:dyDescent="0.35">
       <c r="A46" s="195"/>
       <c r="B46" s="195"/>
       <c r="C46" s="195"/>
@@ -10544,7 +10544,7 @@
       <c r="M46" s="195"/>
       <c r="N46" s="195"/>
     </row>
-    <row r="47" spans="1:14" ht="21" x14ac:dyDescent="0.4">
+    <row r="47" spans="1:14" ht="21" x14ac:dyDescent="0.35">
       <c r="A47" s="195"/>
       <c r="B47" s="195"/>
       <c r="C47" s="195"/>
@@ -10560,7 +10560,7 @@
       <c r="M47" s="195"/>
       <c r="N47" s="195"/>
     </row>
-    <row r="48" spans="1:14" ht="21" x14ac:dyDescent="0.4">
+    <row r="48" spans="1:14" ht="21" x14ac:dyDescent="0.35">
       <c r="A48" s="195"/>
       <c r="B48" s="195"/>
       <c r="C48" s="195"/>
@@ -10576,7 +10576,7 @@
       <c r="M48" s="195"/>
       <c r="N48" s="195"/>
     </row>
-    <row r="49" spans="1:14" ht="21" x14ac:dyDescent="0.4">
+    <row r="49" spans="1:14" ht="21" x14ac:dyDescent="0.35">
       <c r="A49" s="195"/>
       <c r="B49" s="195"/>
       <c r="C49" s="195"/>
@@ -10592,7 +10592,7 @@
       <c r="M49" s="195"/>
       <c r="N49" s="195"/>
     </row>
-    <row r="50" spans="1:14" ht="21" x14ac:dyDescent="0.4">
+    <row r="50" spans="1:14" ht="21" x14ac:dyDescent="0.35">
       <c r="A50" s="195"/>
       <c r="B50" s="195"/>
       <c r="C50" s="195"/>
@@ -10608,7 +10608,7 @@
       <c r="M50" s="195"/>
       <c r="N50" s="195"/>
     </row>
-    <row r="51" spans="1:14" ht="21" x14ac:dyDescent="0.4">
+    <row r="51" spans="1:14" ht="21" x14ac:dyDescent="0.35">
       <c r="A51" s="195"/>
       <c r="B51" s="195"/>
       <c r="C51" s="195"/>
@@ -10624,7 +10624,7 @@
       <c r="M51" s="195"/>
       <c r="N51" s="195"/>
     </row>
-    <row r="52" spans="1:14" ht="21" x14ac:dyDescent="0.4">
+    <row r="52" spans="1:14" ht="21" x14ac:dyDescent="0.35">
       <c r="A52" s="195"/>
       <c r="B52" s="195"/>
       <c r="C52" s="195"/>
@@ -10640,7 +10640,7 @@
       <c r="M52" s="195"/>
       <c r="N52" s="195"/>
     </row>
-    <row r="53" spans="1:14" ht="21" x14ac:dyDescent="0.4">
+    <row r="53" spans="1:14" ht="21" x14ac:dyDescent="0.35">
       <c r="A53" s="195"/>
       <c r="B53" s="195"/>
       <c r="C53" s="195"/>
@@ -10656,7 +10656,7 @@
       <c r="M53" s="195"/>
       <c r="N53" s="195"/>
     </row>
-    <row r="54" spans="1:14" ht="21" x14ac:dyDescent="0.4">
+    <row r="54" spans="1:14" ht="21" x14ac:dyDescent="0.35">
       <c r="A54" s="195"/>
       <c r="B54" s="195"/>
       <c r="C54" s="195"/>
@@ -10692,20 +10692,20 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0700-000000000000}">
   <sheetPr codeName="Hoja8"/>
   <dimension ref="A1:AD121"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="18.33203125" customWidth="1"/>
-    <col min="5" max="5" width="12.33203125" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="103.44140625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="18.28515625" customWidth="1"/>
+    <col min="5" max="5" width="12.28515625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="103.42578125" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="7" customWidth="1"/>
-    <col min="9" max="9" width="8.44140625" customWidth="1"/>
-    <col min="10" max="10" width="8.88671875" customWidth="1"/>
-    <col min="11" max="11" width="9.88671875" customWidth="1"/>
+    <col min="9" max="9" width="8.42578125" customWidth="1"/>
+    <col min="10" max="10" width="8.85546875" customWidth="1"/>
+    <col min="11" max="11" width="9.85546875" customWidth="1"/>
     <col min="19" max="19" width="14" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="14.6640625" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="14.7109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:30" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:30" ht="15.75" x14ac:dyDescent="0.25">
       <c r="G1" s="27"/>
       <c r="H1" s="339" t="s">
         <v>158</v>
@@ -10728,7 +10728,7 @@
       </c>
       <c r="U1" s="339"/>
     </row>
-    <row r="2" spans="1:30" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:30" ht="15.75" x14ac:dyDescent="0.25">
       <c r="G2" s="27"/>
       <c r="H2" s="339"/>
       <c r="I2" s="339"/>
@@ -10755,7 +10755,7 @@
       <c r="T2" s="339"/>
       <c r="U2" s="339"/>
     </row>
-    <row r="3" spans="1:30" ht="78" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:30" ht="94.5" x14ac:dyDescent="0.25">
       <c r="B3" s="4" t="s">
         <v>17</v>
       </c>
@@ -10808,7 +10808,7 @@
         <v>211</v>
       </c>
     </row>
-    <row r="4" spans="1:30" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:30" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="43">
         <v>1</v>
       </c>
@@ -10885,7 +10885,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="5" spans="1:30" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:30" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="43">
         <v>2</v>
       </c>
@@ -10962,7 +10962,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="6" spans="1:30" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A6" s="43">
         <v>3</v>
       </c>
@@ -11039,7 +11039,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="7" spans="1:30" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A7" s="43">
         <v>4</v>
       </c>
@@ -11116,7 +11116,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="8" spans="1:30" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A8" s="43">
         <v>5</v>
       </c>
@@ -11193,7 +11193,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="9" spans="1:30" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A9" s="43">
         <v>6</v>
       </c>
@@ -11270,7 +11270,7 @@
         <v>1.5</v>
       </c>
     </row>
-    <row r="10" spans="1:30" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A10" s="43">
         <v>7</v>
       </c>
@@ -11344,7 +11344,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="11" spans="1:30" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A11" s="11" t="s">
         <v>22</v>
       </c>
@@ -11418,7 +11418,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="12" spans="1:30" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A12" s="11" t="s">
         <v>56</v>
       </c>
@@ -11426,7 +11426,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="13" spans="1:30" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:30" x14ac:dyDescent="0.25">
       <c r="I13" t="s">
         <v>201</v>
       </c>
@@ -11434,7 +11434,7 @@
         <v>154</v>
       </c>
     </row>
-    <row r="14" spans="1:30" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:30" x14ac:dyDescent="0.25">
       <c r="I14" t="s">
         <v>202</v>
       </c>
@@ -11442,7 +11442,7 @@
         <v>153</v>
       </c>
     </row>
-    <row r="15" spans="1:30" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>59</v>
       </c>
@@ -11450,7 +11450,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="16" spans="1:30" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>60</v>
       </c>
@@ -11458,7 +11458,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="17" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>61</v>
       </c>
@@ -11466,247 +11466,247 @@
         <v>225</v>
       </c>
     </row>
-    <row r="18" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>62</v>
       </c>
     </row>
-    <row r="19" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>63</v>
       </c>
     </row>
-    <row r="20" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>64</v>
       </c>
     </row>
-    <row r="21" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>65</v>
       </c>
     </row>
-    <row r="22" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>66</v>
       </c>
     </row>
-    <row r="23" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>67</v>
       </c>
     </row>
-    <row r="24" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
         <v>68</v>
       </c>
     </row>
-    <row r="25" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
         <v>72</v>
       </c>
     </row>
-    <row r="27" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="28" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
         <v>71</v>
       </c>
     </row>
-    <row r="30" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
         <v>76</v>
       </c>
     </row>
-    <row r="31" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
         <v>77</v>
       </c>
     </row>
-    <row r="32" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
         <v>78</v>
       </c>
     </row>
-    <row r="33" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
         <v>79</v>
       </c>
     </row>
-    <row r="34" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
         <v>80</v>
       </c>
     </row>
-    <row r="35" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
         <v>81</v>
       </c>
     </row>
-    <row r="36" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
         <v>82</v>
       </c>
     </row>
-    <row r="37" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
         <v>83</v>
       </c>
     </row>
-    <row r="38" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
         <v>84</v>
       </c>
     </row>
-    <row r="39" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
         <v>85</v>
       </c>
     </row>
-    <row r="40" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
         <v>72</v>
       </c>
     </row>
-    <row r="42" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
         <v>92</v>
       </c>
     </row>
-    <row r="43" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
         <v>93</v>
       </c>
     </row>
-    <row r="44" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
         <v>105</v>
       </c>
     </row>
-    <row r="45" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
         <v>106</v>
       </c>
     </row>
-    <row r="46" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
         <v>107</v>
       </c>
     </row>
-    <row r="47" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
         <v>108</v>
       </c>
     </row>
-    <row r="48" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
         <v>109</v>
       </c>
     </row>
-    <row r="49" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
         <v>110</v>
       </c>
     </row>
-    <row r="50" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
         <v>111</v>
       </c>
     </row>
-    <row r="51" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
         <v>112</v>
       </c>
     </row>
-    <row r="52" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
         <v>113</v>
       </c>
     </row>
-    <row r="53" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
         <v>114</v>
       </c>
     </row>
-    <row r="54" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
         <v>115</v>
       </c>
     </row>
-    <row r="55" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
         <v>116</v>
       </c>
     </row>
-    <row r="56" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
         <v>94</v>
       </c>
     </row>
-    <row r="57" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
         <v>95</v>
       </c>
     </row>
-    <row r="58" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
         <v>96</v>
       </c>
     </row>
-    <row r="59" spans="1:1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
         <v>97</v>
       </c>
     </row>
-    <row r="60" spans="1:1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
         <v>98</v>
       </c>
     </row>
-    <row r="61" spans="1:1" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
         <v>99</v>
       </c>
     </row>
-    <row r="62" spans="1:1" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
         <v>100</v>
       </c>
     </row>
-    <row r="63" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
         <v>101</v>
       </c>
     </row>
-    <row r="64" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
         <v>102</v>
       </c>
     </row>
-    <row r="65" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
         <v>103</v>
       </c>
     </row>
-    <row r="66" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
         <v>104</v>
       </c>
     </row>
-    <row r="67" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="67" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
         <v>72</v>
       </c>
     </row>
-    <row r="68" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="68" spans="1:9" x14ac:dyDescent="0.25">
       <c r="E68" t="s">
         <v>119</v>
       </c>
     </row>
-    <row r="69" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="69" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
         <v>119</v>
       </c>
@@ -11717,7 +11717,7 @@
         <v>131</v>
       </c>
     </row>
-    <row r="70" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="70" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
         <v>177</v>
       </c>
@@ -11728,7 +11728,7 @@
         <v>132</v>
       </c>
     </row>
-    <row r="71" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="71" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
         <v>178</v>
       </c>
@@ -11739,7 +11739,7 @@
         <v>133</v>
       </c>
     </row>
-    <row r="72" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="72" spans="1:9" x14ac:dyDescent="0.25">
       <c r="G72" t="s">
         <v>122</v>
       </c>
@@ -11747,7 +11747,7 @@
         <v>134</v>
       </c>
     </row>
-    <row r="73" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="73" spans="1:9" x14ac:dyDescent="0.25">
       <c r="G73" t="s">
         <v>123</v>
       </c>
@@ -11755,7 +11755,7 @@
         <v>135</v>
       </c>
     </row>
-    <row r="74" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="74" spans="1:9" x14ac:dyDescent="0.25">
       <c r="G74" t="s">
         <v>124</v>
       </c>
@@ -11763,7 +11763,7 @@
         <v>136</v>
       </c>
     </row>
-    <row r="75" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="75" spans="1:9" x14ac:dyDescent="0.25">
       <c r="G75" t="s">
         <v>125</v>
       </c>
@@ -11771,7 +11771,7 @@
         <v>137</v>
       </c>
     </row>
-    <row r="76" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="76" spans="1:9" x14ac:dyDescent="0.25">
       <c r="G76" t="s">
         <v>126</v>
       </c>
@@ -11779,7 +11779,7 @@
         <v>138</v>
       </c>
     </row>
-    <row r="77" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="77" spans="1:9" x14ac:dyDescent="0.25">
       <c r="G77" t="s">
         <v>127</v>
       </c>
@@ -11787,7 +11787,7 @@
         <v>139</v>
       </c>
     </row>
-    <row r="78" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="78" spans="1:9" x14ac:dyDescent="0.25">
       <c r="G78" t="s">
         <v>128</v>
       </c>
@@ -11795,7 +11795,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="79" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="79" spans="1:9" x14ac:dyDescent="0.25">
       <c r="G79" t="s">
         <v>129</v>
       </c>
@@ -11803,7 +11803,7 @@
         <v>141</v>
       </c>
     </row>
-    <row r="80" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="80" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="G80" t="s">
         <v>132</v>
       </c>
@@ -11811,7 +11811,7 @@
         <v>142</v>
       </c>
     </row>
-    <row r="81" spans="7:9" x14ac:dyDescent="0.3">
+    <row r="81" spans="7:9" x14ac:dyDescent="0.25">
       <c r="G81" t="s">
         <v>133</v>
       </c>
@@ -11819,7 +11819,7 @@
         <v>143</v>
       </c>
     </row>
-    <row r="82" spans="7:9" x14ac:dyDescent="0.3">
+    <row r="82" spans="7:9" x14ac:dyDescent="0.25">
       <c r="G82" t="s">
         <v>134</v>
       </c>
@@ -11827,7 +11827,7 @@
         <v>144</v>
       </c>
     </row>
-    <row r="83" spans="7:9" x14ac:dyDescent="0.3">
+    <row r="83" spans="7:9" x14ac:dyDescent="0.25">
       <c r="G83" t="s">
         <v>135</v>
       </c>
@@ -11835,7 +11835,7 @@
         <v>145</v>
       </c>
     </row>
-    <row r="84" spans="7:9" x14ac:dyDescent="0.3">
+    <row r="84" spans="7:9" x14ac:dyDescent="0.25">
       <c r="G84" t="s">
         <v>136</v>
       </c>
@@ -11843,7 +11843,7 @@
         <v>146</v>
       </c>
     </row>
-    <row r="85" spans="7:9" x14ac:dyDescent="0.3">
+    <row r="85" spans="7:9" x14ac:dyDescent="0.25">
       <c r="G85" t="s">
         <v>137</v>
       </c>
@@ -11851,7 +11851,7 @@
         <v>147</v>
       </c>
     </row>
-    <row r="86" spans="7:9" x14ac:dyDescent="0.3">
+    <row r="86" spans="7:9" x14ac:dyDescent="0.25">
       <c r="G86" t="s">
         <v>138</v>
       </c>
@@ -11859,7 +11859,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="87" spans="7:9" x14ac:dyDescent="0.3">
+    <row r="87" spans="7:9" x14ac:dyDescent="0.25">
       <c r="G87" t="s">
         <v>139</v>
       </c>
@@ -11867,7 +11867,7 @@
         <v>149</v>
       </c>
     </row>
-    <row r="88" spans="7:9" x14ac:dyDescent="0.3">
+    <row r="88" spans="7:9" x14ac:dyDescent="0.25">
       <c r="G88" t="s">
         <v>140</v>
       </c>
@@ -11875,7 +11875,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="89" spans="7:9" x14ac:dyDescent="0.3">
+    <row r="89" spans="7:9" x14ac:dyDescent="0.25">
       <c r="G89" t="s">
         <v>141</v>
       </c>
@@ -11883,7 +11883,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="90" spans="7:9" x14ac:dyDescent="0.3">
+    <row r="90" spans="7:9" x14ac:dyDescent="0.25">
       <c r="G90" t="s">
         <v>142</v>
       </c>
@@ -11891,117 +11891,117 @@
         <v>152</v>
       </c>
     </row>
-    <row r="91" spans="7:9" x14ac:dyDescent="0.3">
+    <row r="91" spans="7:9" x14ac:dyDescent="0.25">
       <c r="G91" t="s">
         <v>143</v>
       </c>
     </row>
-    <row r="92" spans="7:9" x14ac:dyDescent="0.3">
+    <row r="92" spans="7:9" x14ac:dyDescent="0.25">
       <c r="G92" t="s">
         <v>144</v>
       </c>
     </row>
-    <row r="93" spans="7:9" x14ac:dyDescent="0.3">
+    <row r="93" spans="7:9" x14ac:dyDescent="0.25">
       <c r="G93" t="s">
         <v>145</v>
       </c>
     </row>
-    <row r="94" spans="7:9" x14ac:dyDescent="0.3">
+    <row r="94" spans="7:9" x14ac:dyDescent="0.25">
       <c r="G94" t="s">
         <v>146</v>
       </c>
     </row>
-    <row r="95" spans="7:9" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="95" spans="7:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="G95" t="s">
         <v>147</v>
       </c>
     </row>
-    <row r="96" spans="7:9" x14ac:dyDescent="0.3">
+    <row r="96" spans="7:9" x14ac:dyDescent="0.25">
       <c r="G96" t="s">
         <v>148</v>
       </c>
     </row>
-    <row r="97" spans="7:7" x14ac:dyDescent="0.3">
+    <row r="97" spans="7:7" x14ac:dyDescent="0.25">
       <c r="G97" t="s">
         <v>149</v>
       </c>
     </row>
-    <row r="98" spans="7:7" x14ac:dyDescent="0.3">
+    <row r="98" spans="7:7" x14ac:dyDescent="0.25">
       <c r="G98" t="s">
         <v>150</v>
       </c>
     </row>
-    <row r="99" spans="7:7" x14ac:dyDescent="0.3">
+    <row r="99" spans="7:7" x14ac:dyDescent="0.25">
       <c r="G99" t="s">
         <v>151</v>
       </c>
     </row>
-    <row r="100" spans="7:7" x14ac:dyDescent="0.3">
+    <row r="100" spans="7:7" x14ac:dyDescent="0.25">
       <c r="G100" t="s">
         <v>152</v>
       </c>
     </row>
-    <row r="101" spans="7:7" x14ac:dyDescent="0.3">
+    <row r="101" spans="7:7" x14ac:dyDescent="0.25">
       <c r="G101" s="1"/>
     </row>
-    <row r="102" spans="7:7" x14ac:dyDescent="0.3">
+    <row r="102" spans="7:7" x14ac:dyDescent="0.25">
       <c r="G102" s="1"/>
     </row>
-    <row r="103" spans="7:7" x14ac:dyDescent="0.3">
+    <row r="103" spans="7:7" x14ac:dyDescent="0.25">
       <c r="G103" s="1"/>
     </row>
-    <row r="104" spans="7:7" x14ac:dyDescent="0.3">
+    <row r="104" spans="7:7" x14ac:dyDescent="0.25">
       <c r="G104" s="1"/>
     </row>
-    <row r="105" spans="7:7" x14ac:dyDescent="0.3">
+    <row r="105" spans="7:7" x14ac:dyDescent="0.25">
       <c r="G105" s="1"/>
     </row>
-    <row r="106" spans="7:7" x14ac:dyDescent="0.3">
+    <row r="106" spans="7:7" x14ac:dyDescent="0.25">
       <c r="G106" s="1"/>
     </row>
-    <row r="107" spans="7:7" x14ac:dyDescent="0.3">
+    <row r="107" spans="7:7" x14ac:dyDescent="0.25">
       <c r="G107" s="1"/>
     </row>
-    <row r="108" spans="7:7" x14ac:dyDescent="0.3">
+    <row r="108" spans="7:7" x14ac:dyDescent="0.25">
       <c r="G108" s="1"/>
     </row>
-    <row r="109" spans="7:7" x14ac:dyDescent="0.3">
+    <row r="109" spans="7:7" x14ac:dyDescent="0.25">
       <c r="G109" s="1"/>
     </row>
-    <row r="110" spans="7:7" x14ac:dyDescent="0.3">
+    <row r="110" spans="7:7" x14ac:dyDescent="0.25">
       <c r="G110" s="1"/>
     </row>
-    <row r="111" spans="7:7" x14ac:dyDescent="0.3">
+    <row r="111" spans="7:7" x14ac:dyDescent="0.25">
       <c r="G111" s="1"/>
     </row>
-    <row r="112" spans="7:7" x14ac:dyDescent="0.3">
+    <row r="112" spans="7:7" x14ac:dyDescent="0.25">
       <c r="G112" s="1"/>
     </row>
-    <row r="113" spans="7:7" x14ac:dyDescent="0.3">
+    <row r="113" spans="7:7" x14ac:dyDescent="0.25">
       <c r="G113" s="1"/>
     </row>
-    <row r="114" spans="7:7" x14ac:dyDescent="0.3">
+    <row r="114" spans="7:7" x14ac:dyDescent="0.25">
       <c r="G114" s="1"/>
     </row>
-    <row r="115" spans="7:7" x14ac:dyDescent="0.3">
+    <row r="115" spans="7:7" x14ac:dyDescent="0.25">
       <c r="G115" s="1"/>
     </row>
-    <row r="116" spans="7:7" x14ac:dyDescent="0.3">
+    <row r="116" spans="7:7" x14ac:dyDescent="0.25">
       <c r="G116" s="1"/>
     </row>
-    <row r="117" spans="7:7" x14ac:dyDescent="0.3">
+    <row r="117" spans="7:7" x14ac:dyDescent="0.25">
       <c r="G117" s="1"/>
     </row>
-    <row r="118" spans="7:7" x14ac:dyDescent="0.3">
+    <row r="118" spans="7:7" x14ac:dyDescent="0.25">
       <c r="G118" s="1"/>
     </row>
-    <row r="119" spans="7:7" x14ac:dyDescent="0.3">
+    <row r="119" spans="7:7" x14ac:dyDescent="0.25">
       <c r="G119" s="1"/>
     </row>
-    <row r="120" spans="7:7" x14ac:dyDescent="0.3">
+    <row r="120" spans="7:7" x14ac:dyDescent="0.25">
       <c r="G120" s="1"/>
     </row>
-    <row r="121" spans="7:7" x14ac:dyDescent="0.3">
+    <row r="121" spans="7:7" x14ac:dyDescent="0.25">
       <c r="G121" s="1"/>
     </row>
   </sheetData>
@@ -12024,64 +12024,64 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0800-000000000000}">
   <sheetPr codeName="Hoja9"/>
   <dimension ref="B1:B12"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="1" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B1" s="21" t="s">
         <v>195</v>
       </c>
     </row>
-    <row r="2" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="2" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B2" s="21" t="s">
         <v>193</v>
       </c>
     </row>
-    <row r="3" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="3" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B3" s="21" t="s">
         <v>194</v>
       </c>
     </row>
-    <row r="4" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="4" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B4" s="21" t="s">
         <v>196</v>
       </c>
     </row>
-    <row r="5" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="5" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B5" s="21" t="s">
         <v>197</v>
       </c>
     </row>
-    <row r="6" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="6" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B6" s="21" t="s">
         <v>198</v>
       </c>
     </row>
-    <row r="7" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="7" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B7" s="21" t="s">
         <v>199</v>
       </c>
     </row>
-    <row r="8" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="8" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B8" s="21" t="s">
         <v>207</v>
       </c>
     </row>
-    <row r="9" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="9" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B9" s="21" t="s">
         <v>221</v>
       </c>
     </row>
-    <row r="10" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="10" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B10" s="21" t="s">
         <v>226</v>
       </c>
     </row>
-    <row r="11" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="11" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B11" s="21" t="s">
         <v>227</v>
       </c>
     </row>
-    <row r="12" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="12" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B12" s="21" t="s">
         <v>231</v>
       </c>

--- a/macros fac/FAC_ RPNC1-4240426.xlsx
+++ b/macros fac/FAC_ RPNC1-4240426.xlsx
@@ -5,12 +5,12 @@
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Ivan\Documents\gitdocs-2026\macros fac\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Ubicacion C a D\Documentos\gitdocs-2026\macros fac\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BB046319-A8A1-47BE-903E-2DF27D0CE184}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5AABCA2B-1719-450D-8812-AAD80CE7EB9E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" tabRatio="682" firstSheet="2" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" tabRatio="682" firstSheet="2" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="menore" sheetId="1" state="hidden" r:id="rId1"/>
@@ -2951,11 +2951,164 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="15" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="10" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="10" borderId="34" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="10" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="8" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="8" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="8" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="48" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="51" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="53" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="45" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="170" fontId="12" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="170" fontId="12" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="8" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="8" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="8" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="8" borderId="38" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="2" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="15" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="52" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="49" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -2963,24 +3116,12 @@
     <xf numFmtId="0" fontId="13" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="10" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="10" borderId="34" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="10" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -3014,146 +3155,119 @@
     <xf numFmtId="0" fontId="15" fillId="0" borderId="45" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="47" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="48" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="47" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="48" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="10" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="10" borderId="34" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="10" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="2" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="46" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="48" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="14" fontId="15" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="52" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="49" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="48" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="51" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="53" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="45" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="170" fontId="12" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="170" fontId="12" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="8" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="8" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="8" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="8" borderId="38" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="8" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="8" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="8" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="48" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
@@ -3164,7 +3278,13 @@
     <xf numFmtId="0" fontId="12" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -3173,127 +3293,7 @@
     <xf numFmtId="0" fontId="13" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="10" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="10" borderId="34" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="10" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="48" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="46" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="48" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="48" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="47" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="47" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="48" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="32" fillId="22" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
@@ -4543,8 +4543,8 @@
       </xdr:nvGrpSpPr>
       <xdr:grpSpPr>
         <a:xfrm>
-          <a:off x="0" y="9017413"/>
-          <a:ext cx="7036253" cy="1168893"/>
+          <a:off x="0" y="8949378"/>
+          <a:ext cx="7066188" cy="1158007"/>
           <a:chOff x="0" y="0"/>
           <a:chExt cx="6918960" cy="1096453"/>
         </a:xfrm>
@@ -5013,14 +5013,14 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr codeName="Hoja1"/>
   <dimension ref="A1:R21"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" width="48" customWidth="1"/>
-    <col min="4" max="4" width="16.140625" customWidth="1"/>
-    <col min="7" max="8" width="11.42578125" customWidth="1"/>
+    <col min="4" max="4" width="16.109375" customWidth="1"/>
+    <col min="7" max="8" width="11.44140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A1" s="208" t="s">
         <v>27</v>
       </c>
@@ -5033,7 +5033,7 @@
       <c r="H1" s="208"/>
       <c r="I1" s="208"/>
     </row>
-    <row r="2" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A2" s="7"/>
       <c r="B2" s="7"/>
       <c r="C2" s="7"/>
@@ -5044,7 +5044,7 @@
       <c r="H2" s="7"/>
       <c r="I2" s="7"/>
     </row>
-    <row r="3" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A3" s="7"/>
       <c r="B3" s="7"/>
       <c r="C3" s="7"/>
@@ -5055,7 +5055,7 @@
       <c r="H3" s="7"/>
       <c r="I3" s="7"/>
     </row>
-    <row r="4" spans="1:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:18" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A4" s="6" t="s">
         <v>0</v>
       </c>
@@ -5070,7 +5070,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="5" spans="1:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:18" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A5" s="6" t="s">
         <v>2</v>
       </c>
@@ -5105,7 +5105,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="6" spans="1:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:18" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A6" s="6" t="s">
         <v>4</v>
       </c>
@@ -5138,7 +5138,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="7" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A7" s="6" t="s">
         <v>7</v>
       </c>
@@ -5152,7 +5152,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="8" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A8" s="6" t="s">
         <v>10</v>
       </c>
@@ -5167,7 +5167,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="9" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A9" s="6" t="s">
         <v>14</v>
       </c>
@@ -5185,7 +5185,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="12" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:18" x14ac:dyDescent="0.3">
       <c r="B12" s="6" t="s">
         <v>35</v>
       </c>
@@ -5197,7 +5197,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="13" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:18" x14ac:dyDescent="0.3">
       <c r="B13" s="6" t="s">
         <v>36</v>
       </c>
@@ -5208,7 +5208,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="14" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:18" x14ac:dyDescent="0.3">
       <c r="B14" s="6" t="s">
         <v>37</v>
       </c>
@@ -5223,7 +5223,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="15" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:18" x14ac:dyDescent="0.3">
       <c r="B15" s="6" t="s">
         <v>38</v>
       </c>
@@ -5239,7 +5239,7 @@
         <v>0.1</v>
       </c>
     </row>
-    <row r="16" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A16" s="6"/>
       <c r="B16" s="6" t="s">
         <v>40</v>
@@ -5256,7 +5256,7 @@
       <c r="H16" s="6"/>
       <c r="I16" s="6"/>
     </row>
-    <row r="17" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="17" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B17" s="6" t="s">
         <v>41</v>
       </c>
@@ -5268,7 +5268,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="18" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="18" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B18" s="6" t="s">
         <v>42</v>
       </c>
@@ -5280,7 +5280,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="19" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="19" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B19" s="13" t="s">
         <v>44</v>
       </c>
@@ -5299,7 +5299,7 @@
         <v>3499.9999999999991</v>
       </c>
     </row>
-    <row r="20" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="20" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B20" s="13" t="s">
         <v>45</v>
       </c>
@@ -5310,7 +5310,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="21" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="21" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B21" s="6" t="s">
         <v>46</v>
       </c>
@@ -5361,15 +5361,15 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <sheetPr codeName="Hoja2"/>
   <dimension ref="A1:S19"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="2" max="2" width="34.85546875" customWidth="1"/>
+    <col min="2" max="2" width="34.88671875" customWidth="1"/>
     <col min="4" max="4" width="22" bestFit="1" customWidth="1"/>
-    <col min="7" max="8" width="11.42578125" hidden="1" customWidth="1"/>
-    <col min="9" max="9" width="16.28515625" bestFit="1" customWidth="1"/>
+    <col min="7" max="8" width="11.44140625" hidden="1" customWidth="1"/>
+    <col min="9" max="9" width="16.33203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A1" s="208" t="s">
         <v>28</v>
       </c>
@@ -5382,7 +5382,7 @@
       <c r="H1" s="208"/>
       <c r="I1" s="208"/>
     </row>
-    <row r="2" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A2" s="7"/>
       <c r="B2" s="7"/>
       <c r="C2" s="6"/>
@@ -5393,7 +5393,7 @@
       <c r="H2" s="7"/>
       <c r="I2" s="7"/>
     </row>
-    <row r="3" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:19" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A3" s="7"/>
       <c r="B3" s="7"/>
       <c r="C3" s="6"/>
@@ -5404,7 +5404,7 @@
       <c r="H3" s="7"/>
       <c r="I3" s="7"/>
     </row>
-    <row r="4" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:19" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A4" s="6" t="s">
         <v>8</v>
       </c>
@@ -5422,7 +5422,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="5" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:19" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A5" s="6" t="s">
         <v>2</v>
       </c>
@@ -5457,7 +5457,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="6" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:19" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A6" s="6" t="s">
         <v>4</v>
       </c>
@@ -5490,7 +5490,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="7" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:19" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A7" s="6" t="s">
         <v>7</v>
       </c>
@@ -5504,7 +5504,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="8" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:19" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A8" s="6" t="s">
         <v>14</v>
       </c>
@@ -5522,7 +5522,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="13" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:19" x14ac:dyDescent="0.3">
       <c r="B13" s="6" t="s">
         <v>29</v>
       </c>
@@ -5534,7 +5534,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="14" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:19" x14ac:dyDescent="0.3">
       <c r="B14" s="6" t="s">
         <v>30</v>
       </c>
@@ -5546,7 +5546,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="15" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:19" x14ac:dyDescent="0.3">
       <c r="B15" s="6" t="s">
         <v>32</v>
       </c>
@@ -5563,7 +5563,7 @@
       <c r="H15" s="6"/>
       <c r="I15" s="6"/>
     </row>
-    <row r="19" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="19" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B19" t="s">
         <v>34</v>
       </c>
@@ -5601,21 +5601,21 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <sheetPr codeName="Hoja3"/>
   <dimension ref="A1:J82"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="11.42578125" defaultRowHeight="14.25" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11.44140625" defaultRowHeight="13.2" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="6.42578125" style="56" customWidth="1"/>
-    <col min="2" max="2" width="3.85546875" style="19" customWidth="1"/>
-    <col min="3" max="3" width="51.42578125" style="18" customWidth="1"/>
-    <col min="4" max="4" width="24.42578125" style="24" customWidth="1"/>
-    <col min="5" max="5" width="20.85546875" style="18" customWidth="1"/>
-    <col min="6" max="6" width="42.42578125" style="18" customWidth="1"/>
-    <col min="7" max="7" width="3.7109375" style="18" customWidth="1"/>
-    <col min="8" max="9" width="22.28515625" style="18" hidden="1" customWidth="1"/>
-    <col min="10" max="10" width="6.28515625" style="56" customWidth="1"/>
-    <col min="11" max="16384" width="11.42578125" style="18"/>
+    <col min="1" max="1" width="6.44140625" style="56" customWidth="1"/>
+    <col min="2" max="2" width="3.88671875" style="19" customWidth="1"/>
+    <col min="3" max="3" width="51.44140625" style="18" customWidth="1"/>
+    <col min="4" max="4" width="24.44140625" style="24" customWidth="1"/>
+    <col min="5" max="5" width="20.88671875" style="18" customWidth="1"/>
+    <col min="6" max="6" width="42.44140625" style="18" customWidth="1"/>
+    <col min="7" max="7" width="3.6640625" style="18" customWidth="1"/>
+    <col min="8" max="9" width="22.33203125" style="18" hidden="1" customWidth="1"/>
+    <col min="10" max="10" width="6.33203125" style="56" customWidth="1"/>
+    <col min="11" max="16384" width="11.44140625" style="18"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:10" ht="13.8" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A1" s="54"/>
       <c r="B1" s="16"/>
       <c r="C1" s="17"/>
@@ -5661,18 +5661,18 @@
       <c r="A6" s="55"/>
       <c r="J6" s="58"/>
     </row>
-    <row r="7" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:10" ht="13.8" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A7" s="55"/>
       <c r="J7" s="58"/>
     </row>
-    <row r="8" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:10" ht="13.8" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A8" s="55"/>
       <c r="C8" s="18" t="s">
         <v>117</v>
       </c>
       <c r="D8" s="214">
         <f ca="1">TODAY()</f>
-        <v>46180</v>
+        <v>46183</v>
       </c>
       <c r="E8" s="215"/>
       <c r="J8" s="58"/>
@@ -5758,7 +5758,7 @@
       <c r="A16" s="55"/>
       <c r="J16" s="58"/>
     </row>
-    <row r="17" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:10" ht="13.8" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A17" s="55"/>
       <c r="D17" s="32" t="s">
         <v>88</v>
@@ -5784,7 +5784,7 @@
       <c r="E18" s="52"/>
       <c r="J18" s="58"/>
     </row>
-    <row r="19" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:10" ht="13.8" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A19" s="55"/>
       <c r="B19" s="19">
         <v>2</v>
@@ -5797,7 +5797,7 @@
       </c>
       <c r="J19" s="58"/>
     </row>
-    <row r="20" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:10" ht="13.8" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A20" s="55"/>
       <c r="B20" s="19">
         <v>3</v>
@@ -5810,7 +5810,7 @@
       </c>
       <c r="J20" s="58"/>
     </row>
-    <row r="21" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:10" ht="13.8" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A21" s="55"/>
       <c r="B21" s="19">
         <v>4</v>
@@ -5823,7 +5823,7 @@
       </c>
       <c r="J21" s="58"/>
     </row>
-    <row r="22" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:10" ht="13.8" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A22" s="55"/>
       <c r="B22" s="19">
         <v>5</v>
@@ -5836,7 +5836,7 @@
       </c>
       <c r="J22" s="58"/>
     </row>
-    <row r="23" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:10" ht="13.8" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A23" s="55"/>
       <c r="B23" s="19">
         <v>6</v>
@@ -5849,7 +5849,7 @@
       </c>
       <c r="J23" s="58"/>
     </row>
-    <row r="24" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:10" ht="13.8" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A24" s="55"/>
       <c r="B24" s="19">
         <v>7</v>
@@ -5862,7 +5862,7 @@
       </c>
       <c r="J24" s="58"/>
     </row>
-    <row r="25" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:10" ht="13.8" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A25" s="55"/>
       <c r="B25" s="19">
         <v>8</v>
@@ -5875,7 +5875,7 @@
       </c>
       <c r="J25" s="58"/>
     </row>
-    <row r="26" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:10" ht="13.8" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A26" s="55"/>
       <c r="B26" s="19">
         <v>9</v>
@@ -5888,7 +5888,7 @@
       </c>
       <c r="J26" s="58"/>
     </row>
-    <row r="27" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:10" ht="13.8" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A27" s="55"/>
       <c r="C27" s="23" t="s">
         <v>219</v>
@@ -5898,7 +5898,7 @@
       </c>
       <c r="J27" s="58"/>
     </row>
-    <row r="28" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:10" ht="13.8" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A28" s="55"/>
       <c r="C28" s="23" t="s">
         <v>242</v>
@@ -5908,17 +5908,17 @@
       </c>
       <c r="J28" s="58"/>
     </row>
-    <row r="29" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:10" ht="13.8" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A29" s="55"/>
       <c r="C29" s="23"/>
       <c r="F29" s="51"/>
       <c r="J29" s="58"/>
     </row>
-    <row r="30" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:10" ht="13.8" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A30" s="55"/>
       <c r="J30" s="58"/>
     </row>
-    <row r="31" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:10" ht="13.8" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A31" s="55"/>
       <c r="C31" s="21" t="s">
         <v>300</v>
@@ -5929,7 +5929,7 @@
       <c r="F31" s="24"/>
       <c r="J31" s="58"/>
     </row>
-    <row r="32" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:10" ht="13.8" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A32" s="55"/>
       <c r="C32" s="21" t="s">
         <v>183</v>
@@ -5944,12 +5944,12 @@
       <c r="C33" s="21"/>
       <c r="J33" s="58"/>
     </row>
-    <row r="34" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="34" spans="1:10" ht="13.8" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A34" s="55"/>
       <c r="D34" s="18"/>
       <c r="J34" s="58"/>
     </row>
-    <row r="35" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="35" spans="1:10" ht="13.8" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A35" s="55"/>
       <c r="C35" s="21" t="s">
         <v>297</v>
@@ -5963,7 +5963,7 @@
       </c>
       <c r="J35" s="58"/>
     </row>
-    <row r="36" spans="1:10" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="36" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A36" s="55"/>
       <c r="C36" s="21" t="s">
         <v>295</v>
@@ -5979,13 +5979,13 @@
       </c>
       <c r="J36" s="58"/>
     </row>
-    <row r="37" spans="1:10" ht="42" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="37" spans="1:10" ht="27" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A37" s="55"/>
       <c r="C37" s="23" t="s">
         <v>292</v>
       </c>
       <c r="D37" s="147">
-        <v>66666</v>
+        <v>4444</v>
       </c>
       <c r="E37" s="18" t="s">
         <v>315</v>
@@ -5995,7 +5995,7 @@
       </c>
       <c r="J37" s="58"/>
     </row>
-    <row r="38" spans="1:10" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="38" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A38" s="55"/>
       <c r="C38" s="23" t="s">
         <v>293</v>
@@ -6012,13 +6012,13 @@
       </c>
       <c r="J38" s="58"/>
     </row>
-    <row r="39" spans="1:10" ht="29.25" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="39" spans="1:10" ht="27" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A39" s="55"/>
       <c r="C39" s="23" t="s">
         <v>294</v>
       </c>
       <c r="D39" s="147">
-        <v>77777</v>
+        <v>30</v>
       </c>
       <c r="E39" s="18" t="s">
         <v>315</v>
@@ -6028,7 +6028,7 @@
       </c>
       <c r="J39" s="58"/>
     </row>
-    <row r="40" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="40" spans="1:10" ht="13.8" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A40" s="55"/>
       <c r="C40" s="21" t="s">
         <v>299</v>
@@ -6044,21 +6044,21 @@
       </c>
       <c r="J40" s="58"/>
     </row>
-    <row r="41" spans="1:10" ht="29.25" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="41" spans="1:10" ht="27" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A41" s="55"/>
       <c r="C41" s="21" t="s">
         <v>291</v>
       </c>
       <c r="D41" s="39">
         <f>ROUNDUP($D$37/D35,2)</f>
-        <v>333.33</v>
+        <v>22.22</v>
       </c>
       <c r="F41" s="104" t="s">
         <v>302</v>
       </c>
       <c r="J41" s="58"/>
     </row>
-    <row r="42" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="42" spans="1:10" ht="13.8" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A42" s="55"/>
       <c r="C42" s="21" t="s">
         <v>289</v>
@@ -6072,21 +6072,21 @@
       </c>
       <c r="J42" s="58"/>
     </row>
-    <row r="43" spans="1:10" ht="29.25" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="43" spans="1:10" ht="27" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A43" s="55"/>
       <c r="C43" s="21" t="s">
         <v>290</v>
       </c>
       <c r="D43" s="101">
         <f>IFERROR(((D36+D37)/D31),"")</f>
-        <v>333.33</v>
+        <v>22.22</v>
       </c>
       <c r="F43" s="105" t="s">
         <v>303</v>
       </c>
       <c r="J43" s="58"/>
     </row>
-    <row r="44" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="44" spans="1:10" ht="13.8" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A44" s="55"/>
       <c r="C44" s="21" t="s">
         <v>222</v>
@@ -6097,7 +6097,7 @@
       </c>
       <c r="J44" s="58"/>
     </row>
-    <row r="45" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="45" spans="1:10" ht="13.8" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A45" s="55"/>
       <c r="C45" s="21" t="s">
         <v>228</v>
@@ -6107,18 +6107,18 @@
       </c>
       <c r="J45" s="58"/>
     </row>
-    <row r="46" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="46" spans="1:10" ht="13.8" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A46" s="55"/>
       <c r="C46" s="21" t="s">
         <v>307</v>
       </c>
       <c r="D46" s="112">
         <f>ROUNDUP(D39/D31,2)</f>
-        <v>388.89</v>
+        <v>0.15</v>
       </c>
       <c r="J46" s="58"/>
     </row>
-    <row r="47" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="47" spans="1:10" ht="13.8" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A47" s="55"/>
       <c r="C47" s="23"/>
       <c r="F47" s="107" t="s">
@@ -6126,7 +6126,7 @@
       </c>
       <c r="J47" s="58"/>
     </row>
-    <row r="48" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="48" spans="1:10" ht="13.8" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A48" s="55"/>
       <c r="C48" s="216" t="s">
         <v>309</v>
@@ -6139,14 +6139,14 @@
       <c r="I48" s="45"/>
       <c r="J48" s="58"/>
     </row>
-    <row r="49" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="49" spans="1:10" ht="13.8" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A49" s="55"/>
       <c r="C49" s="48" t="s">
         <v>179</v>
       </c>
       <c r="D49" s="148">
         <f>+D37</f>
-        <v>66666</v>
+        <v>4444</v>
       </c>
       <c r="E49" s="37" t="s">
         <v>119</v>
@@ -6158,7 +6158,7 @@
       <c r="I49" s="46"/>
       <c r="J49" s="58"/>
     </row>
-    <row r="50" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="50" spans="1:10" ht="13.8" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A50" s="55"/>
       <c r="C50" s="48" t="s">
         <v>180</v>
@@ -6171,7 +6171,7 @@
       <c r="I50" s="46"/>
       <c r="J50" s="58"/>
     </row>
-    <row r="51" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="51" spans="1:10" ht="13.8" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A51" s="55"/>
       <c r="C51" s="48" t="s">
         <v>181</v>
@@ -6184,7 +6184,7 @@
       <c r="I51" s="46"/>
       <c r="J51" s="58"/>
     </row>
-    <row r="52" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="52" spans="1:10" ht="13.8" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A52" s="55"/>
       <c r="C52" s="49" t="s">
         <v>182</v>
@@ -6197,19 +6197,19 @@
       <c r="I52" s="46"/>
       <c r="J52" s="58"/>
     </row>
-    <row r="53" spans="1:10" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:10" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A53" s="55"/>
       <c r="C53" s="21"/>
       <c r="D53" s="24">
         <f>SUM(D49:D52)</f>
-        <v>66666</v>
+        <v>4444</v>
       </c>
       <c r="E53" s="18" t="s">
         <v>315</v>
       </c>
       <c r="J53" s="58"/>
     </row>
-    <row r="54" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="54" spans="1:10" ht="13.8" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A54" s="55"/>
       <c r="C54" s="21"/>
       <c r="D54" s="36"/>
@@ -6222,7 +6222,7 @@
       </c>
       <c r="D55" s="40">
         <f>SUMIF(E49:E52,"RESIDENCIAL",D49:D52)</f>
-        <v>66666</v>
+        <v>4444</v>
       </c>
       <c r="J55" s="58"/>
     </row>
@@ -6237,7 +6237,7 @@
       </c>
       <c r="J56" s="58"/>
     </row>
-    <row r="57" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="57" spans="1:10" ht="13.8" thickBot="1" x14ac:dyDescent="0.35">
       <c r="C57" s="21" t="s">
         <v>185</v>
       </c>
@@ -6246,8 +6246,8 @@
         <v>0</v>
       </c>
     </row>
-    <row r="58" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
-    <row r="59" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="58" spans="1:10" ht="13.8" thickBot="1" x14ac:dyDescent="0.35"/>
+    <row r="59" spans="1:10" ht="13.8" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A59" s="55"/>
       <c r="C59" s="21" t="s">
         <v>248</v>
@@ -6258,7 +6258,7 @@
       </c>
       <c r="J59" s="58"/>
     </row>
-    <row r="60" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="60" spans="1:10" ht="13.8" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A60" s="55"/>
       <c r="C60" s="21"/>
       <c r="E60" s="20" t="s">
@@ -6266,7 +6266,7 @@
       </c>
       <c r="J60" s="58"/>
     </row>
-    <row r="61" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="61" spans="1:10" ht="13.8" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A61" s="55"/>
       <c r="C61" s="21" t="s">
         <v>187</v>
@@ -6277,7 +6277,7 @@
       <c r="E61" s="50"/>
       <c r="J61" s="58"/>
     </row>
-    <row r="62" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="62" spans="1:10" ht="13.8" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A62" s="55"/>
       <c r="C62" s="21" t="s">
         <v>189</v>
@@ -6293,7 +6293,7 @@
       </c>
       <c r="J62" s="58"/>
     </row>
-    <row r="63" spans="1:10" ht="28.5" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="63" spans="1:10" ht="24.6" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A63" s="55"/>
       <c r="C63" s="23" t="s">
         <v>220</v>
@@ -6303,20 +6303,20 @@
       </c>
       <c r="J63" s="58"/>
     </row>
-    <row r="64" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="64" spans="1:10" ht="13.8" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A64" s="55"/>
       <c r="C64" s="23"/>
       <c r="D64" s="35"/>
       <c r="J64" s="58"/>
     </row>
-    <row r="65" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="65" spans="1:10" ht="13.8" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A65" s="55"/>
       <c r="C65" s="21" t="s">
         <v>191</v>
       </c>
       <c r="D65" s="53">
         <f>IF($D$35&gt;10000,((($D$35*$D$41)/($F$62+$D$41))*IF($D$59=100%,1,1.3)),(($D$35*($D$41*0.75))/($D$62+($D$41*0.75))*(IF($D$63="NO",1,0.75))*(IF($D$59=100%,1,1.3))))</f>
-        <v>193.14334276526088</v>
+        <v>130.50117462803445</v>
       </c>
       <c r="J65" s="58"/>
     </row>
@@ -6325,12 +6325,12 @@
       <c r="C66" s="21"/>
       <c r="J66" s="58"/>
     </row>
-    <row r="67" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="67" spans="1:10" ht="13.8" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A67" s="55"/>
       <c r="C67" s="21"/>
       <c r="J67" s="58"/>
     </row>
-    <row r="68" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="68" spans="1:10" ht="13.8" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A68" s="55"/>
       <c r="C68" s="71" t="s">
         <v>268</v>
@@ -6343,7 +6343,7 @@
       </c>
       <c r="J68" s="58"/>
     </row>
-    <row r="69" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="69" spans="1:10" ht="13.8" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A69" s="55"/>
       <c r="C69" s="21"/>
       <c r="D69" s="70">
@@ -6352,7 +6352,7 @@
       <c r="E69" s="22"/>
       <c r="J69" s="58"/>
     </row>
-    <row r="70" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="70" spans="1:10" ht="13.8" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A70" s="55"/>
       <c r="C70" s="21"/>
       <c r="D70" s="70">
@@ -6361,7 +6361,7 @@
       <c r="E70" s="22"/>
       <c r="J70" s="58"/>
     </row>
-    <row r="71" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="71" spans="1:10" ht="13.8" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A71" s="55"/>
       <c r="C71" s="21"/>
       <c r="D71" s="70">
@@ -6370,11 +6370,11 @@
       <c r="E71" s="22"/>
       <c r="J71" s="58"/>
     </row>
-    <row r="72" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="72" spans="1:10" ht="13.8" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A72" s="55"/>
       <c r="J72" s="58"/>
     </row>
-    <row r="73" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="73" spans="1:10" ht="13.8" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A73" s="55"/>
       <c r="C73" s="209" t="s">
         <v>269</v>
@@ -6396,7 +6396,7 @@
       <c r="E74" s="22"/>
       <c r="J74" s="58"/>
     </row>
-    <row r="75" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="75" spans="1:10" ht="13.8" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A75" s="55"/>
       <c r="D75" s="70">
         <v>3</v>
@@ -6404,7 +6404,7 @@
       <c r="E75" s="22"/>
       <c r="J75" s="58"/>
     </row>
-    <row r="76" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="76" spans="1:10" ht="13.8" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A76" s="55"/>
       <c r="D76" s="70">
         <v>4</v>
@@ -6420,12 +6420,12 @@
       <c r="A78" s="55"/>
       <c r="J78" s="58"/>
     </row>
-    <row r="79" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="79" spans="1:10" ht="13.8" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A79" s="55"/>
       <c r="C79" s="21"/>
       <c r="J79" s="58"/>
     </row>
-    <row r="80" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="80" spans="1:10" ht="13.8" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A80" s="55"/>
       <c r="C80" s="21" t="s">
         <v>2</v>
@@ -6539,28 +6539,28 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:T143"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="11.42578125" defaultRowHeight="13.5" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11.44140625" defaultRowHeight="13.2" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="4.85546875" style="143" customWidth="1"/>
-    <col min="2" max="3" width="4.85546875" style="146" customWidth="1"/>
-    <col min="4" max="4" width="4.85546875" style="143" customWidth="1"/>
-    <col min="5" max="5" width="5.28515625" style="143" customWidth="1"/>
-    <col min="6" max="6" width="41.7109375" style="143" customWidth="1"/>
-    <col min="7" max="7" width="21.42578125" style="143" customWidth="1"/>
-    <col min="8" max="8" width="10.42578125" style="143" customWidth="1"/>
-    <col min="9" max="9" width="44.28515625" style="143" customWidth="1"/>
+    <col min="1" max="1" width="4.88671875" style="143" customWidth="1"/>
+    <col min="2" max="3" width="4.88671875" style="146" customWidth="1"/>
+    <col min="4" max="4" width="4.88671875" style="143" customWidth="1"/>
+    <col min="5" max="5" width="5.33203125" style="143" customWidth="1"/>
+    <col min="6" max="6" width="41.6640625" style="143" customWidth="1"/>
+    <col min="7" max="7" width="21.44140625" style="143" customWidth="1"/>
+    <col min="8" max="8" width="10.44140625" style="143" customWidth="1"/>
+    <col min="9" max="9" width="44.33203125" style="143" customWidth="1"/>
     <col min="10" max="10" width="20" style="143" customWidth="1"/>
-    <col min="11" max="11" width="12.28515625" style="143" customWidth="1"/>
-    <col min="12" max="12" width="29.28515625" style="143" customWidth="1"/>
-    <col min="13" max="13" width="5.7109375" style="143" customWidth="1"/>
-    <col min="14" max="14" width="5.42578125" style="143" customWidth="1"/>
+    <col min="11" max="11" width="12.33203125" style="143" customWidth="1"/>
+    <col min="12" max="12" width="29.33203125" style="143" customWidth="1"/>
+    <col min="13" max="13" width="5.6640625" style="143" customWidth="1"/>
+    <col min="14" max="14" width="5.44140625" style="143" customWidth="1"/>
     <col min="15" max="15" width="9" style="143" hidden="1" customWidth="1"/>
-    <col min="16" max="17" width="4.85546875" style="146" customWidth="1"/>
-    <col min="18" max="18" width="4.85546875" style="143" customWidth="1"/>
-    <col min="19" max="16384" width="11.42578125" style="143"/>
+    <col min="16" max="17" width="4.88671875" style="146" customWidth="1"/>
+    <col min="18" max="18" width="4.88671875" style="143" customWidth="1"/>
+    <col min="19" max="16384" width="11.44140625" style="143"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:17" s="73" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="2:17" s="73" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="D1" s="77"/>
       <c r="E1" s="77"/>
       <c r="F1" s="77"/>
@@ -6571,13 +6571,13 @@
       <c r="K1" s="77"/>
       <c r="O1" s="77"/>
     </row>
-    <row r="2" spans="2:17" s="73" customFormat="1" ht="18" x14ac:dyDescent="0.25">
+    <row r="2" spans="2:17" s="73" customFormat="1" ht="17.399999999999999" x14ac:dyDescent="0.3">
       <c r="D2" s="82"/>
       <c r="E2" s="114"/>
       <c r="F2" s="114"/>
-      <c r="G2" s="219"/>
-      <c r="H2" s="219"/>
-      <c r="I2" s="219"/>
+      <c r="G2" s="223"/>
+      <c r="H2" s="223"/>
+      <c r="I2" s="223"/>
       <c r="J2" s="114"/>
       <c r="K2" s="114"/>
       <c r="L2" s="114"/>
@@ -6585,186 +6585,186 @@
       <c r="N2" s="114"/>
       <c r="O2" s="114"/>
     </row>
-    <row r="3" spans="2:17" s="73" customFormat="1" ht="18.75" thickBot="1" x14ac:dyDescent="0.3"/>
-    <row r="4" spans="2:17" s="73" customFormat="1" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="2:17" s="73" customFormat="1" ht="17.399999999999999" thickBot="1" x14ac:dyDescent="0.35"/>
+    <row r="4" spans="2:17" s="73" customFormat="1" ht="20.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B4" s="93"/>
       <c r="C4" s="93"/>
-      <c r="G4" s="221" t="s">
+      <c r="G4" s="272" t="s">
         <v>243</v>
       </c>
-      <c r="H4" s="222"/>
-      <c r="I4" s="222"/>
-      <c r="L4" s="233" t="s">
+      <c r="H4" s="273"/>
+      <c r="I4" s="273"/>
+      <c r="L4" s="280" t="s">
         <v>312</v>
       </c>
-      <c r="M4" s="233"/>
-      <c r="N4" s="233"/>
+      <c r="M4" s="280"/>
+      <c r="N4" s="280"/>
       <c r="P4" s="93"/>
       <c r="Q4" s="93"/>
     </row>
-    <row r="5" spans="2:17" s="73" customFormat="1" ht="18.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="2:17" s="73" customFormat="1" ht="17.399999999999999" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B5" s="93"/>
       <c r="C5" s="93"/>
       <c r="P5" s="93"/>
       <c r="Q5" s="93"/>
     </row>
-    <row r="6" spans="2:17" s="73" customFormat="1" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="2:17" s="73" customFormat="1" ht="21" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B6" s="93"/>
       <c r="C6" s="93"/>
-      <c r="G6" s="234" t="s">
+      <c r="G6" s="281" t="s">
         <v>90</v>
       </c>
-      <c r="H6" s="235"/>
-      <c r="I6" s="236"/>
+      <c r="H6" s="282"/>
+      <c r="I6" s="283"/>
       <c r="P6" s="93"/>
       <c r="Q6" s="93"/>
     </row>
-    <row r="7" spans="2:17" s="73" customFormat="1" ht="18" x14ac:dyDescent="0.25">
+    <row r="7" spans="2:17" s="73" customFormat="1" ht="16.8" x14ac:dyDescent="0.3">
       <c r="B7" s="93"/>
       <c r="C7" s="93"/>
-      <c r="G7" s="237"/>
-      <c r="H7" s="238"/>
-      <c r="I7" s="239"/>
+      <c r="G7" s="284"/>
+      <c r="H7" s="285"/>
+      <c r="I7" s="286"/>
       <c r="P7" s="93"/>
       <c r="Q7" s="93"/>
     </row>
-    <row r="8" spans="2:17" s="73" customFormat="1" ht="18.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="8" spans="2:17" s="73" customFormat="1" ht="18" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B8" s="93"/>
       <c r="C8" s="93"/>
       <c r="F8" s="82"/>
       <c r="P8" s="93"/>
       <c r="Q8" s="93"/>
     </row>
-    <row r="9" spans="2:17" s="73" customFormat="1" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="2:17" s="73" customFormat="1" ht="23.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B9" s="93"/>
       <c r="C9" s="93"/>
-      <c r="F9" s="223" t="s">
+      <c r="F9" s="228" t="s">
         <v>251</v>
       </c>
-      <c r="G9" s="224"/>
-      <c r="H9" s="224"/>
-      <c r="I9" s="224"/>
-      <c r="J9" s="224"/>
-      <c r="K9" s="224"/>
-      <c r="L9" s="225"/>
+      <c r="G9" s="229"/>
+      <c r="H9" s="229"/>
+      <c r="I9" s="229"/>
+      <c r="J9" s="229"/>
+      <c r="K9" s="229"/>
+      <c r="L9" s="230"/>
       <c r="P9" s="93"/>
       <c r="Q9" s="93"/>
     </row>
-    <row r="10" spans="2:17" s="73" customFormat="1" ht="18.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="10" spans="2:17" s="73" customFormat="1" ht="17.399999999999999" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B10" s="93"/>
       <c r="C10" s="93"/>
       <c r="P10" s="93"/>
       <c r="Q10" s="93"/>
     </row>
-    <row r="11" spans="2:17" s="73" customFormat="1" ht="20.25" x14ac:dyDescent="0.25">
+    <row r="11" spans="2:17" s="73" customFormat="1" ht="20.399999999999999" x14ac:dyDescent="0.3">
       <c r="B11" s="93"/>
       <c r="C11" s="93"/>
       <c r="F11" s="77" t="s">
         <v>229</v>
       </c>
-      <c r="G11" s="221" t="str">
+      <c r="G11" s="272" t="str">
         <f>FACTIBILIDAD!D11</f>
         <v> RPNC1-4240426</v>
       </c>
-      <c r="H11" s="222"/>
-      <c r="I11" s="222"/>
-      <c r="J11" s="226"/>
+      <c r="H11" s="273"/>
+      <c r="I11" s="273"/>
+      <c r="J11" s="274"/>
       <c r="P11" s="93"/>
       <c r="Q11" s="93"/>
     </row>
-    <row r="12" spans="2:17" s="73" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="2:17" s="73" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B12" s="93"/>
       <c r="C12" s="93"/>
       <c r="F12" s="77" t="s">
         <v>175</v>
       </c>
-      <c r="G12" s="227" t="str">
+      <c r="G12" s="275" t="str">
         <f>FACTIBILIDAD!D9</f>
         <v> CAJAS ITZEP, RAFAEL SALVADOR</v>
       </c>
-      <c r="H12" s="228"/>
-      <c r="I12" s="228"/>
-      <c r="J12" s="229"/>
+      <c r="H12" s="226"/>
+      <c r="I12" s="226"/>
+      <c r="J12" s="276"/>
       <c r="P12" s="93"/>
       <c r="Q12" s="93"/>
     </row>
-    <row r="13" spans="2:17" s="73" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="2:17" s="73" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B13" s="93"/>
       <c r="C13" s="93"/>
       <c r="F13" s="77" t="s">
         <v>233</v>
       </c>
-      <c r="G13" s="227" t="str">
+      <c r="G13" s="275" t="str">
         <f>FACTIBILIDAD!D10</f>
         <v> 8va AVENIDA 0-10</v>
       </c>
-      <c r="H13" s="228"/>
-      <c r="I13" s="228"/>
-      <c r="J13" s="229"/>
+      <c r="H13" s="226"/>
+      <c r="I13" s="226"/>
+      <c r="J13" s="276"/>
       <c r="P13" s="93"/>
       <c r="Q13" s="93"/>
     </row>
-    <row r="14" spans="2:17" s="73" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="2:17" s="73" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B14" s="93"/>
       <c r="C14" s="93"/>
       <c r="F14" s="77" t="s">
         <v>176</v>
       </c>
-      <c r="G14" s="230">
+      <c r="G14" s="277">
         <f ca="1">FACTIBILIDAD!D8</f>
-        <v>46180</v>
-      </c>
-      <c r="H14" s="231"/>
-      <c r="I14" s="231"/>
-      <c r="J14" s="232"/>
+        <v>46183</v>
+      </c>
+      <c r="H14" s="278"/>
+      <c r="I14" s="278"/>
+      <c r="J14" s="279"/>
       <c r="P14" s="93"/>
       <c r="Q14" s="93"/>
     </row>
-    <row r="15" spans="2:17" s="73" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="2:17" s="73" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B15" s="93"/>
       <c r="C15" s="93"/>
       <c r="F15" s="77" t="s">
         <v>235</v>
       </c>
-      <c r="G15" s="227" t="str">
+      <c r="G15" s="275" t="str">
         <f>FACTIBILIDAD!D12</f>
         <v xml:space="preserve">UNIFAMILIAR </v>
       </c>
-      <c r="H15" s="228"/>
-      <c r="I15" s="228"/>
-      <c r="J15" s="229"/>
+      <c r="H15" s="226"/>
+      <c r="I15" s="226"/>
+      <c r="J15" s="276"/>
       <c r="P15" s="93"/>
       <c r="Q15" s="93"/>
     </row>
-    <row r="16" spans="2:17" s="73" customFormat="1" ht="18" x14ac:dyDescent="0.25">
+    <row r="16" spans="2:17" s="73" customFormat="1" ht="17.399999999999999" x14ac:dyDescent="0.3">
       <c r="B16" s="93"/>
       <c r="C16" s="93"/>
       <c r="F16" s="77" t="s">
         <v>239</v>
       </c>
-      <c r="G16" s="227" t="str">
+      <c r="G16" s="275" t="str">
         <f>FACTIBILIDAD!D13</f>
         <v>F</v>
       </c>
-      <c r="H16" s="228"/>
-      <c r="I16" s="228"/>
-      <c r="J16" s="229"/>
+      <c r="H16" s="226"/>
+      <c r="I16" s="226"/>
+      <c r="J16" s="276"/>
       <c r="P16" s="93"/>
       <c r="Q16" s="93"/>
     </row>
-    <row r="17" spans="2:20" s="73" customFormat="1" ht="18" x14ac:dyDescent="0.25">
+    <row r="17" spans="2:20" s="73" customFormat="1" ht="17.399999999999999" x14ac:dyDescent="0.3">
       <c r="B17" s="93"/>
       <c r="C17" s="93"/>
       <c r="F17" s="77" t="s">
         <v>240</v>
       </c>
-      <c r="G17" s="227" t="str">
+      <c r="G17" s="275" t="str">
         <f>FACTIBILIDAD!D14</f>
         <v>FOL</v>
       </c>
-      <c r="H17" s="228"/>
-      <c r="I17" s="228"/>
-      <c r="J17" s="229"/>
+      <c r="H17" s="226"/>
+      <c r="I17" s="226"/>
+      <c r="J17" s="276"/>
       <c r="K17" s="114"/>
       <c r="L17" s="114"/>
       <c r="M17" s="114"/>
@@ -6773,23 +6773,23 @@
       <c r="P17" s="93"/>
       <c r="Q17" s="93"/>
     </row>
-    <row r="18" spans="2:20" s="73" customFormat="1" ht="18.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="18" spans="2:20" s="73" customFormat="1" ht="18" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B18" s="93"/>
       <c r="C18" s="93"/>
       <c r="F18" s="77" t="s">
         <v>241</v>
       </c>
-      <c r="G18" s="259" t="str">
+      <c r="G18" s="237" t="str">
         <f>FACTIBILIDAD!D15</f>
         <v>LIB</v>
       </c>
-      <c r="H18" s="257"/>
-      <c r="I18" s="257"/>
-      <c r="J18" s="260"/>
+      <c r="H18" s="238"/>
+      <c r="I18" s="238"/>
+      <c r="J18" s="239"/>
       <c r="P18" s="93"/>
       <c r="Q18" s="93"/>
     </row>
-    <row r="19" spans="2:20" s="73" customFormat="1" ht="18.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="19" spans="2:20" s="73" customFormat="1" ht="18" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B19" s="93"/>
       <c r="C19" s="93"/>
       <c r="F19" s="77"/>
@@ -6800,46 +6800,46 @@
       <c r="P19" s="93"/>
       <c r="Q19" s="93"/>
     </row>
-    <row r="20" spans="2:20" s="73" customFormat="1" ht="20.25" x14ac:dyDescent="0.25">
+    <row r="20" spans="2:20" s="73" customFormat="1" ht="20.399999999999999" x14ac:dyDescent="0.3">
       <c r="B20" s="93"/>
       <c r="C20" s="93"/>
-      <c r="F20" s="223" t="s">
+      <c r="F20" s="228" t="s">
         <v>263</v>
       </c>
-      <c r="G20" s="224"/>
-      <c r="H20" s="224"/>
-      <c r="I20" s="224"/>
-      <c r="J20" s="224"/>
-      <c r="K20" s="224"/>
-      <c r="L20" s="225"/>
+      <c r="G20" s="229"/>
+      <c r="H20" s="229"/>
+      <c r="I20" s="229"/>
+      <c r="J20" s="229"/>
+      <c r="K20" s="229"/>
+      <c r="L20" s="230"/>
       <c r="P20" s="93"/>
       <c r="Q20" s="93"/>
     </row>
-    <row r="21" spans="2:20" s="73" customFormat="1" ht="18.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="21" spans="2:20" s="73" customFormat="1" ht="18" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B21" s="93"/>
       <c r="C21" s="93"/>
       <c r="F21" s="77"/>
       <c r="P21" s="93"/>
       <c r="Q21" s="93"/>
     </row>
-    <row r="22" spans="2:20" s="73" customFormat="1" ht="36" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="22" spans="2:20" s="73" customFormat="1" ht="36" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B22" s="93"/>
       <c r="C22" s="93"/>
       <c r="F22" s="118" t="s">
         <v>280</v>
       </c>
-      <c r="G22" s="251" t="str">
+      <c r="G22" s="240" t="str">
         <f>IF(N35="", "NO ESTA SUJETO A CARGAS URBANISTICAS",FACTIBILIDAD!D19)</f>
         <v>URBANO Q2 (URB-Q2)</v>
       </c>
-      <c r="H22" s="252"/>
-      <c r="I22" s="252"/>
-      <c r="J22" s="253"/>
+      <c r="H22" s="253"/>
+      <c r="I22" s="253"/>
+      <c r="J22" s="241"/>
       <c r="K22" s="82"/>
       <c r="P22" s="93"/>
       <c r="Q22" s="93"/>
     </row>
-    <row r="23" spans="2:20" s="73" customFormat="1" ht="18.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="23" spans="2:20" s="73" customFormat="1" ht="18" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B23" s="93"/>
       <c r="C23" s="93"/>
       <c r="F23" s="118"/>
@@ -6851,18 +6851,18 @@
       <c r="P23" s="93"/>
       <c r="Q23" s="93"/>
     </row>
-    <row r="24" spans="2:20" s="73" customFormat="1" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="24" spans="2:20" s="73" customFormat="1" ht="21" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B24" s="93"/>
       <c r="C24" s="93"/>
-      <c r="F24" s="274" t="s">
+      <c r="F24" s="256" t="s">
         <v>249</v>
       </c>
-      <c r="G24" s="275"/>
+      <c r="G24" s="257"/>
       <c r="H24" s="77"/>
-      <c r="I24" s="272" t="s">
+      <c r="I24" s="254" t="s">
         <v>250</v>
       </c>
-      <c r="J24" s="273"/>
+      <c r="J24" s="255"/>
       <c r="K24" s="82"/>
       <c r="L24" s="119" t="s">
         <v>252</v>
@@ -6870,7 +6870,7 @@
       <c r="P24" s="93"/>
       <c r="Q24" s="93"/>
     </row>
-    <row r="25" spans="2:20" s="73" customFormat="1" ht="20.25" x14ac:dyDescent="0.25">
+    <row r="25" spans="2:20" s="73" customFormat="1" ht="19.8" x14ac:dyDescent="0.3">
       <c r="B25" s="93"/>
       <c r="C25" s="93"/>
       <c r="F25" s="120" t="s">
@@ -6896,7 +6896,7 @@
       <c r="P25" s="93"/>
       <c r="Q25" s="93"/>
     </row>
-    <row r="26" spans="2:20" s="73" customFormat="1" ht="18" x14ac:dyDescent="0.25">
+    <row r="26" spans="2:20" s="73" customFormat="1" ht="17.399999999999999" x14ac:dyDescent="0.3">
       <c r="B26" s="93"/>
       <c r="C26" s="93"/>
       <c r="F26" s="74" t="s">
@@ -6922,7 +6922,7 @@
       <c r="P26" s="93"/>
       <c r="Q26" s="93"/>
     </row>
-    <row r="27" spans="2:20" s="73" customFormat="1" ht="18" x14ac:dyDescent="0.25">
+    <row r="27" spans="2:20" s="73" customFormat="1" ht="17.399999999999999" x14ac:dyDescent="0.3">
       <c r="B27" s="93"/>
       <c r="C27" s="93"/>
       <c r="F27" s="74" t="s">
@@ -6948,7 +6948,7 @@
       <c r="P27" s="93"/>
       <c r="Q27" s="93"/>
     </row>
-    <row r="28" spans="2:20" s="73" customFormat="1" ht="36" x14ac:dyDescent="0.25">
+    <row r="28" spans="2:20" s="73" customFormat="1" ht="17.399999999999999" x14ac:dyDescent="0.3">
       <c r="B28" s="93"/>
       <c r="C28" s="93"/>
       <c r="F28" s="74" t="s">
@@ -6974,7 +6974,7 @@
       <c r="P28" s="93"/>
       <c r="Q28" s="93"/>
     </row>
-    <row r="29" spans="2:20" s="73" customFormat="1" ht="36" x14ac:dyDescent="0.25">
+    <row r="29" spans="2:20" s="73" customFormat="1" ht="34.799999999999997" x14ac:dyDescent="0.3">
       <c r="B29" s="93"/>
       <c r="C29" s="93"/>
       <c r="F29" s="74" t="s">
@@ -7000,7 +7000,7 @@
       <c r="P29" s="93"/>
       <c r="Q29" s="93"/>
     </row>
-    <row r="30" spans="2:20" s="73" customFormat="1" ht="54.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="30" spans="2:20" s="73" customFormat="1" ht="54.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B30" s="93"/>
       <c r="C30" s="93"/>
       <c r="F30" s="74" t="s">
@@ -7016,7 +7016,7 @@
       </c>
       <c r="J30" s="123">
         <f>IF(J25&lt;150,"NO DEBE DEJAR AREA PERMEABLE",FACTIBILIDAD!D39/FACTIBILIDAD!D35)</f>
-        <v>388.88499999999999</v>
+        <v>0.15</v>
       </c>
       <c r="K30" s="124"/>
       <c r="L30" s="99" t="str">
@@ -7026,7 +7026,7 @@
       <c r="P30" s="93"/>
       <c r="Q30" s="93"/>
     </row>
-    <row r="31" spans="2:20" s="73" customFormat="1" ht="38.25" x14ac:dyDescent="0.25">
+    <row r="31" spans="2:20" s="73" customFormat="1" ht="19.8" x14ac:dyDescent="0.3">
       <c r="B31" s="93"/>
       <c r="C31" s="93"/>
       <c r="F31" s="74" t="s">
@@ -7052,7 +7052,7 @@
       <c r="P31" s="93"/>
       <c r="Q31" s="93"/>
     </row>
-    <row r="32" spans="2:20" s="73" customFormat="1" ht="38.25" x14ac:dyDescent="0.25">
+    <row r="32" spans="2:20" s="73" customFormat="1" ht="37.200000000000003" x14ac:dyDescent="0.3">
       <c r="B32" s="93"/>
       <c r="C32" s="93"/>
       <c r="F32" s="74" t="s">
@@ -7079,7 +7079,7 @@
       <c r="Q32" s="93"/>
       <c r="T32" s="206"/>
     </row>
-    <row r="33" spans="2:20" s="73" customFormat="1" ht="36" x14ac:dyDescent="0.25">
+    <row r="33" spans="2:20" s="73" customFormat="1" ht="34.799999999999997" x14ac:dyDescent="0.3">
       <c r="B33" s="93"/>
       <c r="C33" s="93"/>
       <c r="F33" s="74" t="s">
@@ -7105,7 +7105,7 @@
       <c r="P33" s="93"/>
       <c r="Q33" s="93"/>
     </row>
-    <row r="34" spans="2:20" s="73" customFormat="1" ht="36" x14ac:dyDescent="0.25">
+    <row r="34" spans="2:20" s="73" customFormat="1" ht="17.399999999999999" x14ac:dyDescent="0.3">
       <c r="B34" s="93"/>
       <c r="C34" s="93"/>
       <c r="F34" s="74" t="s">
@@ -7121,7 +7121,7 @@
       </c>
       <c r="J34" s="127">
         <f>FACTIBILIDAD!D43</f>
-        <v>333.33</v>
+        <v>22.22</v>
       </c>
       <c r="K34" s="114"/>
       <c r="L34" s="99" t="str">
@@ -7132,7 +7132,7 @@
       <c r="Q34" s="93"/>
       <c r="S34" s="207"/>
     </row>
-    <row r="35" spans="2:20" s="73" customFormat="1" ht="39" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="35" spans="2:20" s="73" customFormat="1" ht="37.799999999999997" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B35" s="93"/>
       <c r="C35" s="93"/>
       <c r="F35" s="128" t="s">
@@ -7148,24 +7148,24 @@
       </c>
       <c r="J35" s="129">
         <f>FACTIBILIDAD!D37+FACTIBILIDAD!D36</f>
-        <v>66666</v>
+        <v>4444</v>
       </c>
       <c r="K35" s="114"/>
       <c r="L35" s="100" t="str">
         <f>IF(J35&gt;G35,"NO CUMPLE","SI CUMPLE")</f>
         <v>NO CUMPLE</v>
       </c>
-      <c r="N35" s="278" t="str">
+      <c r="N35" s="221" t="str">
         <f>IF(J25&lt;=250,"NO ESTA SUJETO A CARGAS URBANISTICAS"," ")</f>
         <v>NO ESTA SUJETO A CARGAS URBANISTICAS</v>
       </c>
-      <c r="O35" s="278"/>
+      <c r="O35" s="221"/>
       <c r="P35" s="93"/>
       <c r="Q35" s="93"/>
       <c r="S35" s="206"/>
       <c r="T35" s="206"/>
     </row>
-    <row r="36" spans="2:20" s="73" customFormat="1" ht="18.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="36" spans="2:20" s="73" customFormat="1" ht="18" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B36" s="93"/>
       <c r="C36" s="93"/>
       <c r="F36" s="77"/>
@@ -7174,31 +7174,31 @@
       <c r="I36" s="77"/>
       <c r="J36" s="114"/>
       <c r="K36" s="114"/>
-      <c r="N36" s="278"/>
-      <c r="O36" s="278"/>
+      <c r="N36" s="221"/>
+      <c r="O36" s="221"/>
       <c r="P36" s="93"/>
       <c r="Q36" s="93"/>
     </row>
-    <row r="37" spans="2:20" s="73" customFormat="1" ht="18.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="37" spans="2:20" s="73" customFormat="1" ht="18.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B37" s="93"/>
       <c r="C37" s="93"/>
-      <c r="F37" s="281" t="s">
+      <c r="F37" s="231" t="s">
         <v>208</v>
       </c>
-      <c r="G37" s="282"/>
-      <c r="H37" s="283"/>
+      <c r="G37" s="232"/>
+      <c r="H37" s="233"/>
       <c r="I37" s="152" t="s">
         <v>252</v>
       </c>
       <c r="L37" s="191" t="s">
         <v>333</v>
       </c>
-      <c r="N37" s="278"/>
-      <c r="O37" s="278"/>
+      <c r="N37" s="221"/>
+      <c r="O37" s="221"/>
       <c r="P37" s="93"/>
       <c r="Q37" s="93"/>
     </row>
-    <row r="38" spans="2:20" s="73" customFormat="1" ht="20.25" x14ac:dyDescent="0.25">
+    <row r="38" spans="2:20" s="73" customFormat="1" ht="19.8" x14ac:dyDescent="0.3">
       <c r="B38" s="93"/>
       <c r="C38" s="93"/>
       <c r="F38" s="149" t="s">
@@ -7210,20 +7210,20 @@
       <c r="H38" s="153" t="s">
         <v>316</v>
       </c>
-      <c r="I38" s="262" t="s">
+      <c r="I38" s="243" t="s">
         <v>201</v>
       </c>
       <c r="K38" s="190"/>
-      <c r="L38" s="270">
+      <c r="L38" s="251">
         <f>'CARGA U'!C22</f>
         <v>200</v>
       </c>
-      <c r="N38" s="278"/>
-      <c r="O38" s="278"/>
+      <c r="N38" s="221"/>
+      <c r="O38" s="221"/>
       <c r="P38" s="93"/>
       <c r="Q38" s="93"/>
     </row>
-    <row r="39" spans="2:20" s="73" customFormat="1" ht="37.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="39" spans="2:20" s="73" customFormat="1" ht="37.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B39" s="93"/>
       <c r="C39" s="93"/>
       <c r="F39" s="150" t="s">
@@ -7235,28 +7235,28 @@
       <c r="H39" s="155" t="s">
         <v>316</v>
       </c>
-      <c r="I39" s="263"/>
+      <c r="I39" s="244"/>
       <c r="K39" s="190"/>
-      <c r="L39" s="271"/>
-      <c r="N39" s="278"/>
-      <c r="O39" s="278"/>
+      <c r="L39" s="252"/>
+      <c r="N39" s="221"/>
+      <c r="O39" s="221"/>
       <c r="P39" s="93"/>
       <c r="Q39" s="93"/>
     </row>
-    <row r="40" spans="2:20" s="73" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="40" spans="2:20" s="73" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B40" s="93"/>
       <c r="C40" s="93"/>
-      <c r="F40" s="284" t="str">
+      <c r="F40" s="234" t="str">
         <f>IF(J25&lt;=250,"NO ESTA SUJETO A CARGAS URBANISTICAS"," ")</f>
         <v>NO ESTA SUJETO A CARGAS URBANISTICAS</v>
       </c>
-      <c r="G40" s="284"/>
-      <c r="H40" s="284"/>
-      <c r="I40" s="284"/>
+      <c r="G40" s="234"/>
+      <c r="H40" s="234"/>
+      <c r="I40" s="234"/>
       <c r="P40" s="93"/>
       <c r="Q40" s="93"/>
     </row>
-    <row r="41" spans="2:20" s="73" customFormat="1" ht="21" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="41" spans="2:20" s="73" customFormat="1" ht="21" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B41" s="93"/>
       <c r="C41" s="93"/>
       <c r="F41" s="130"/>
@@ -7264,22 +7264,22 @@
       <c r="P41" s="93"/>
       <c r="Q41" s="93"/>
     </row>
-    <row r="42" spans="2:20" s="73" customFormat="1" ht="20.25" x14ac:dyDescent="0.25">
+    <row r="42" spans="2:20" s="73" customFormat="1" ht="20.399999999999999" x14ac:dyDescent="0.3">
       <c r="B42" s="93"/>
       <c r="C42" s="93"/>
-      <c r="F42" s="223" t="s">
+      <c r="F42" s="228" t="s">
         <v>254</v>
       </c>
-      <c r="G42" s="224"/>
-      <c r="H42" s="224"/>
-      <c r="I42" s="224"/>
-      <c r="J42" s="224"/>
-      <c r="K42" s="224"/>
-      <c r="L42" s="225"/>
+      <c r="G42" s="229"/>
+      <c r="H42" s="229"/>
+      <c r="I42" s="229"/>
+      <c r="J42" s="229"/>
+      <c r="K42" s="229"/>
+      <c r="L42" s="230"/>
       <c r="P42" s="93"/>
       <c r="Q42" s="93"/>
     </row>
-    <row r="43" spans="2:20" s="73" customFormat="1" ht="18.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="43" spans="2:20" s="73" customFormat="1" ht="17.399999999999999" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B43" s="93"/>
       <c r="C43" s="93"/>
       <c r="F43" s="130"/>
@@ -7287,17 +7287,17 @@
       <c r="P43" s="93"/>
       <c r="Q43" s="93"/>
     </row>
-    <row r="44" spans="2:20" s="73" customFormat="1" ht="34.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="44" spans="2:20" s="73" customFormat="1" ht="34.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B44" s="93"/>
       <c r="C44" s="93"/>
       <c r="E44" s="73">
         <v>1</v>
       </c>
-      <c r="F44" s="220" t="str">
+      <c r="F44" s="222" t="str">
         <f>IF(FACTIBILIDAD!D20="N/A","No se encuentra en suelo especial de proteccion","Suelo especial de Proteccion Require dictamen de OT/Gestion de Riesgos")</f>
         <v>No se encuentra en suelo especial de proteccion</v>
       </c>
-      <c r="G44" s="220"/>
+      <c r="G44" s="222"/>
       <c r="H44" s="114"/>
       <c r="I44" s="131" t="str">
         <f>IF(F44="No se encuentra en suelo especial de proteccion","SI CUMPLE","NO CUMPLE")</f>
@@ -7306,17 +7306,17 @@
       <c r="P44" s="93"/>
       <c r="Q44" s="93"/>
     </row>
-    <row r="45" spans="2:20" s="73" customFormat="1" ht="18" x14ac:dyDescent="0.25">
+    <row r="45" spans="2:20" s="73" customFormat="1" ht="16.8" x14ac:dyDescent="0.3">
       <c r="B45" s="93"/>
       <c r="C45" s="93"/>
       <c r="E45" s="73">
         <v>2</v>
       </c>
-      <c r="F45" s="220" t="str">
+      <c r="F45" s="222" t="str">
         <f>IF(FACTIBILIDAD!D21="N/A","No se encuentra en suelo rural o forestal")</f>
         <v>No se encuentra en suelo rural o forestal</v>
       </c>
-      <c r="G45" s="220"/>
+      <c r="G45" s="222"/>
       <c r="H45" s="114"/>
       <c r="I45" s="99" t="str">
         <f>IF(F45="No se encuentra en suelo rural o forestal","SI CUMPLE","NO CUMPLE")</f>
@@ -7325,17 +7325,17 @@
       <c r="P45" s="93"/>
       <c r="Q45" s="93"/>
     </row>
-    <row r="46" spans="2:20" s="73" customFormat="1" ht="18" x14ac:dyDescent="0.25">
+    <row r="46" spans="2:20" s="73" customFormat="1" ht="16.8" x14ac:dyDescent="0.3">
       <c r="B46" s="93"/>
       <c r="C46" s="93"/>
       <c r="E46" s="73">
         <v>3</v>
       </c>
-      <c r="F46" s="220" t="str">
+      <c r="F46" s="222" t="str">
         <f>IF(FACTIBILIDAD!D22="NO","No se encuentra en zona de amenaza de sismo","Requiere dictamen de OT y CONRED")</f>
         <v>No se encuentra en zona de amenaza de sismo</v>
       </c>
-      <c r="G46" s="220"/>
+      <c r="G46" s="222"/>
       <c r="H46" s="114"/>
       <c r="I46" s="99" t="str">
         <f>IF(F46="No se encuentra en zona de amenaza de sismo","SI CUMPLE","NO CUMPLE")</f>
@@ -7344,17 +7344,17 @@
       <c r="P46" s="93"/>
       <c r="Q46" s="93"/>
     </row>
-    <row r="47" spans="2:20" s="73" customFormat="1" ht="18" x14ac:dyDescent="0.25">
+    <row r="47" spans="2:20" s="73" customFormat="1" ht="16.8" x14ac:dyDescent="0.3">
       <c r="B47" s="93"/>
       <c r="C47" s="93"/>
       <c r="E47" s="73">
         <v>4</v>
       </c>
-      <c r="F47" s="220" t="str">
+      <c r="F47" s="222" t="str">
         <f>IF(FACTIBILIDAD!D23="NO","No se encuentra en una zona de inundacion","Requiere dictamen de OT y gestion de Riesgos")</f>
         <v>No se encuentra en una zona de inundacion</v>
       </c>
-      <c r="G47" s="220"/>
+      <c r="G47" s="222"/>
       <c r="H47" s="114"/>
       <c r="I47" s="99" t="str">
         <f>IF(F47="No se encuentra en una zona de inundacion","SI CUMPLE","NO CUMPLE")</f>
@@ -7363,17 +7363,17 @@
       <c r="P47" s="93"/>
       <c r="Q47" s="93"/>
     </row>
-    <row r="48" spans="2:20" s="73" customFormat="1" ht="18" x14ac:dyDescent="0.25">
+    <row r="48" spans="2:20" s="73" customFormat="1" ht="16.8" x14ac:dyDescent="0.3">
       <c r="B48" s="93"/>
       <c r="C48" s="93"/>
       <c r="E48" s="73">
         <v>5</v>
       </c>
-      <c r="F48" s="220" t="str">
+      <c r="F48" s="222" t="str">
         <f>IF(FACTIBILIDAD!D24="NO","Area fuera de amenaza por deslizamiento","Requiere dictamen de OT y Gestion de Riesgos")</f>
         <v>Area fuera de amenaza por deslizamiento</v>
       </c>
-      <c r="G48" s="220"/>
+      <c r="G48" s="222"/>
       <c r="H48" s="114"/>
       <c r="I48" s="99" t="str">
         <f>IF(F48="Area fuera de amenaza por deslizamiento","SI CUMPLE","NO CUMPLE")</f>
@@ -7382,17 +7382,17 @@
       <c r="P48" s="93"/>
       <c r="Q48" s="93"/>
     </row>
-    <row r="49" spans="2:17" s="73" customFormat="1" ht="18" x14ac:dyDescent="0.25">
+    <row r="49" spans="2:17" s="73" customFormat="1" ht="16.8" x14ac:dyDescent="0.3">
       <c r="B49" s="93"/>
       <c r="C49" s="93"/>
       <c r="E49" s="73">
         <v>6</v>
       </c>
-      <c r="F49" s="220" t="str">
+      <c r="F49" s="222" t="str">
         <f>IF(FACTIBILIDAD!D25="NO","No se encuentra en area de proyecto urbano",FACTIBILIDAD!D26)</f>
         <v>No se encuentra en area de proyecto urbano</v>
       </c>
-      <c r="G49" s="220"/>
+      <c r="G49" s="222"/>
       <c r="H49" s="114"/>
       <c r="I49" s="99" t="str">
         <f>IF(F49="No se encuentra en area de proyecto urbano","SI CUMPLE","NO CUMPLE")</f>
@@ -7401,17 +7401,17 @@
       <c r="P49" s="93"/>
       <c r="Q49" s="93"/>
     </row>
-    <row r="50" spans="2:17" s="73" customFormat="1" ht="34.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="50" spans="2:17" s="73" customFormat="1" ht="34.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B50" s="93"/>
       <c r="C50" s="93"/>
       <c r="E50" s="73">
         <v>7</v>
       </c>
-      <c r="F50" s="220" t="str">
+      <c r="F50" s="222" t="str">
         <f>IF(FACTIBILIDAD!D27="NO","No se encuentra en Centro Historico y/o monumento aislado","Se encuentra en centro Historico")</f>
         <v>No se encuentra en Centro Historico y/o monumento aislado</v>
       </c>
-      <c r="G50" s="220"/>
+      <c r="G50" s="222"/>
       <c r="H50" s="114"/>
       <c r="I50" s="99" t="str">
         <f>IF(F50="No se encuentra en Centro Historico y/o monumento aislado","SI CUMPLE","NO CUMPLE")</f>
@@ -7420,17 +7420,17 @@
       <c r="P50" s="93"/>
       <c r="Q50" s="93"/>
     </row>
-    <row r="51" spans="2:17" s="73" customFormat="1" ht="20.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="51" spans="2:17" s="73" customFormat="1" ht="20.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B51" s="93"/>
       <c r="C51" s="93"/>
       <c r="E51" s="73">
         <v>8</v>
       </c>
-      <c r="F51" s="220" t="str">
+      <c r="F51" s="222" t="str">
         <f>IF(FACTIBILIDAD!D28="NO","No se encuentra en sector sujeto a Plan Parcial","Se encuentra en sector Sujeto a Plan Parcial")</f>
         <v>No se encuentra en sector sujeto a Plan Parcial</v>
       </c>
-      <c r="G51" s="220"/>
+      <c r="G51" s="222"/>
       <c r="H51" s="114"/>
       <c r="I51" s="100" t="str">
         <f>IF(F51="No se encuentra en sector sujeto a Plan Parcial","SI CUMPLE","NO CUMPLE")</f>
@@ -7439,44 +7439,44 @@
       <c r="P51" s="93"/>
       <c r="Q51" s="93"/>
     </row>
-    <row r="52" spans="2:17" s="73" customFormat="1" ht="18" x14ac:dyDescent="0.25">
+    <row r="52" spans="2:17" s="73" customFormat="1" ht="16.8" x14ac:dyDescent="0.3">
       <c r="B52" s="93"/>
       <c r="C52" s="93"/>
-      <c r="F52" s="220"/>
-      <c r="G52" s="220"/>
+      <c r="F52" s="222"/>
+      <c r="G52" s="222"/>
       <c r="H52" s="114"/>
       <c r="P52" s="93"/>
       <c r="Q52" s="93"/>
     </row>
-    <row r="53" spans="2:17" s="73" customFormat="1" ht="18" x14ac:dyDescent="0.25">
+    <row r="53" spans="2:17" s="73" customFormat="1" ht="16.8" x14ac:dyDescent="0.3">
       <c r="B53" s="93"/>
       <c r="C53" s="93"/>
-      <c r="F53" s="264" t="s">
+      <c r="F53" s="245" t="s">
         <v>253</v>
       </c>
-      <c r="G53" s="265"/>
-      <c r="H53" s="265"/>
-      <c r="I53" s="265"/>
-      <c r="J53" s="265"/>
-      <c r="K53" s="265"/>
-      <c r="L53" s="266"/>
+      <c r="G53" s="246"/>
+      <c r="H53" s="246"/>
+      <c r="I53" s="246"/>
+      <c r="J53" s="246"/>
+      <c r="K53" s="246"/>
+      <c r="L53" s="247"/>
       <c r="P53" s="93"/>
       <c r="Q53" s="93"/>
     </row>
-    <row r="54" spans="2:17" s="73" customFormat="1" ht="39.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="54" spans="2:17" s="73" customFormat="1" ht="39.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B54" s="93"/>
       <c r="C54" s="93"/>
-      <c r="F54" s="267"/>
-      <c r="G54" s="268"/>
-      <c r="H54" s="268"/>
-      <c r="I54" s="268"/>
-      <c r="J54" s="268"/>
-      <c r="K54" s="268"/>
-      <c r="L54" s="269"/>
+      <c r="F54" s="248"/>
+      <c r="G54" s="249"/>
+      <c r="H54" s="249"/>
+      <c r="I54" s="249"/>
+      <c r="J54" s="249"/>
+      <c r="K54" s="249"/>
+      <c r="L54" s="250"/>
       <c r="P54" s="93"/>
       <c r="Q54" s="93"/>
     </row>
-    <row r="55" spans="2:17" s="73" customFormat="1" ht="18.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="55" spans="2:17" s="73" customFormat="1" ht="17.399999999999999" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B55" s="93"/>
       <c r="C55" s="93"/>
       <c r="F55" s="113"/>
@@ -7485,37 +7485,37 @@
       <c r="P55" s="93"/>
       <c r="Q55" s="93"/>
     </row>
-    <row r="56" spans="2:17" s="73" customFormat="1" ht="20.25" x14ac:dyDescent="0.25">
+    <row r="56" spans="2:17" s="73" customFormat="1" ht="20.399999999999999" x14ac:dyDescent="0.3">
       <c r="B56" s="93"/>
       <c r="C56" s="93"/>
-      <c r="F56" s="223" t="s">
+      <c r="F56" s="228" t="s">
         <v>255</v>
       </c>
-      <c r="G56" s="224"/>
-      <c r="H56" s="224"/>
-      <c r="I56" s="224"/>
-      <c r="J56" s="224"/>
-      <c r="K56" s="224"/>
-      <c r="L56" s="225"/>
+      <c r="G56" s="229"/>
+      <c r="H56" s="229"/>
+      <c r="I56" s="229"/>
+      <c r="J56" s="229"/>
+      <c r="K56" s="229"/>
+      <c r="L56" s="230"/>
       <c r="P56" s="93"/>
       <c r="Q56" s="93"/>
     </row>
-    <row r="57" spans="2:17" s="73" customFormat="1" ht="18.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="57" spans="2:17" s="73" customFormat="1" ht="17.399999999999999" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B57" s="93"/>
       <c r="C57" s="93"/>
-      <c r="F57" s="261"/>
-      <c r="G57" s="261"/>
+      <c r="F57" s="242"/>
+      <c r="G57" s="242"/>
       <c r="H57" s="114"/>
       <c r="P57" s="93"/>
       <c r="Q57" s="93"/>
     </row>
-    <row r="58" spans="2:17" s="73" customFormat="1" ht="36" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="58" spans="2:17" s="73" customFormat="1" ht="36" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B58" s="93"/>
       <c r="C58" s="93"/>
-      <c r="F58" s="251" t="s">
+      <c r="F58" s="240" t="s">
         <v>223</v>
       </c>
-      <c r="G58" s="253"/>
+      <c r="G58" s="241"/>
       <c r="I58" s="115" t="s">
         <v>244</v>
       </c>
@@ -7531,7 +7531,7 @@
       <c r="P58" s="93"/>
       <c r="Q58" s="93"/>
     </row>
-    <row r="59" spans="2:17" s="73" customFormat="1" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="59" spans="2:17" s="73" customFormat="1" ht="23.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B59" s="93"/>
       <c r="C59" s="93"/>
       <c r="F59" s="133" t="s">
@@ -7561,7 +7561,7 @@
       <c r="P59" s="93"/>
       <c r="Q59" s="93"/>
     </row>
-    <row r="60" spans="2:17" s="73" customFormat="1" ht="18.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="60" spans="2:17" s="73" customFormat="1" ht="18" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B60" s="93"/>
       <c r="C60" s="93"/>
       <c r="F60" s="137"/>
@@ -7589,7 +7589,7 @@
       <c r="P60" s="93"/>
       <c r="Q60" s="93"/>
     </row>
-    <row r="61" spans="2:17" s="73" customFormat="1" ht="18" x14ac:dyDescent="0.25">
+    <row r="61" spans="2:17" s="73" customFormat="1" ht="17.399999999999999" x14ac:dyDescent="0.3">
       <c r="B61" s="93"/>
       <c r="C61" s="93"/>
       <c r="F61" s="77"/>
@@ -7614,7 +7614,7 @@
       <c r="P61" s="93"/>
       <c r="Q61" s="93"/>
     </row>
-    <row r="62" spans="2:17" s="73" customFormat="1" ht="18" x14ac:dyDescent="0.25">
+    <row r="62" spans="2:17" s="73" customFormat="1" ht="17.399999999999999" x14ac:dyDescent="0.3">
       <c r="B62" s="93"/>
       <c r="C62" s="93"/>
       <c r="F62" s="77"/>
@@ -7639,7 +7639,7 @@
       <c r="P62" s="93"/>
       <c r="Q62" s="93"/>
     </row>
-    <row r="63" spans="2:17" s="73" customFormat="1" ht="18" x14ac:dyDescent="0.25">
+    <row r="63" spans="2:17" s="73" customFormat="1" ht="17.399999999999999" x14ac:dyDescent="0.3">
       <c r="B63" s="93"/>
       <c r="C63" s="93"/>
       <c r="F63" s="77"/>
@@ -7651,67 +7651,67 @@
       <c r="P63" s="93"/>
       <c r="Q63" s="93"/>
     </row>
-    <row r="64" spans="2:17" s="73" customFormat="1" ht="18" x14ac:dyDescent="0.25">
+    <row r="64" spans="2:17" s="73" customFormat="1" ht="17.399999999999999" x14ac:dyDescent="0.3">
       <c r="B64" s="93"/>
       <c r="C64" s="93"/>
-      <c r="F64" s="286" t="s">
+      <c r="F64" s="236" t="s">
         <v>361</v>
       </c>
-      <c r="G64" s="286"/>
-      <c r="H64" s="286"/>
-      <c r="I64" s="286"/>
-      <c r="J64" s="286"/>
-      <c r="K64" s="286"/>
-      <c r="L64" s="286"/>
+      <c r="G64" s="236"/>
+      <c r="H64" s="236"/>
+      <c r="I64" s="236"/>
+      <c r="J64" s="236"/>
+      <c r="K64" s="236"/>
+      <c r="L64" s="236"/>
       <c r="P64" s="93"/>
       <c r="Q64" s="93"/>
     </row>
-    <row r="65" spans="2:17" s="73" customFormat="1" ht="40.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="65" spans="2:17" s="73" customFormat="1" ht="40.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B65" s="93"/>
       <c r="C65" s="93"/>
-      <c r="F65" s="220" t="s">
+      <c r="F65" s="222" t="s">
         <v>310</v>
       </c>
-      <c r="G65" s="220"/>
-      <c r="H65" s="220"/>
-      <c r="I65" s="220"/>
-      <c r="J65" s="220"/>
-      <c r="K65" s="220"/>
-      <c r="L65" s="220"/>
+      <c r="G65" s="222"/>
+      <c r="H65" s="222"/>
+      <c r="I65" s="222"/>
+      <c r="J65" s="222"/>
+      <c r="K65" s="222"/>
+      <c r="L65" s="222"/>
       <c r="P65" s="93"/>
       <c r="Q65" s="93"/>
     </row>
-    <row r="66" spans="2:17" s="73" customFormat="1" ht="40.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="66" spans="2:17" s="73" customFormat="1" ht="40.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B66" s="93"/>
       <c r="C66" s="93"/>
-      <c r="F66" s="220" t="s">
+      <c r="F66" s="222" t="s">
         <v>311</v>
       </c>
-      <c r="G66" s="220"/>
-      <c r="H66" s="220"/>
-      <c r="I66" s="220"/>
-      <c r="J66" s="220"/>
-      <c r="K66" s="220"/>
-      <c r="L66" s="220"/>
+      <c r="G66" s="222"/>
+      <c r="H66" s="222"/>
+      <c r="I66" s="222"/>
+      <c r="J66" s="222"/>
+      <c r="K66" s="222"/>
+      <c r="L66" s="222"/>
       <c r="P66" s="93"/>
       <c r="Q66" s="93"/>
     </row>
-    <row r="67" spans="2:17" s="73" customFormat="1" ht="20.25" x14ac:dyDescent="0.25">
+    <row r="67" spans="2:17" s="73" customFormat="1" ht="20.399999999999999" x14ac:dyDescent="0.3">
       <c r="B67" s="93"/>
       <c r="C67" s="93"/>
-      <c r="F67" s="223" t="s">
+      <c r="F67" s="228" t="s">
         <v>276</v>
       </c>
-      <c r="G67" s="224"/>
-      <c r="H67" s="224"/>
-      <c r="I67" s="224"/>
-      <c r="J67" s="224"/>
-      <c r="K67" s="224"/>
-      <c r="L67" s="225"/>
+      <c r="G67" s="229"/>
+      <c r="H67" s="229"/>
+      <c r="I67" s="229"/>
+      <c r="J67" s="229"/>
+      <c r="K67" s="229"/>
+      <c r="L67" s="230"/>
       <c r="P67" s="93"/>
       <c r="Q67" s="93"/>
     </row>
-    <row r="68" spans="2:17" s="73" customFormat="1" ht="18.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="68" spans="2:17" s="73" customFormat="1" ht="18" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B68" s="93"/>
       <c r="C68" s="93"/>
       <c r="F68" s="77"/>
@@ -7723,21 +7723,21 @@
       <c r="P68" s="93"/>
       <c r="Q68" s="93"/>
     </row>
-    <row r="69" spans="2:17" s="73" customFormat="1" ht="21" x14ac:dyDescent="0.25">
+    <row r="69" spans="2:17" s="73" customFormat="1" ht="19.2" x14ac:dyDescent="0.3">
       <c r="B69" s="93"/>
       <c r="C69" s="93"/>
       <c r="F69" s="139" t="s">
         <v>272</v>
       </c>
-      <c r="G69" s="254" t="str">
+      <c r="G69" s="269" t="str">
         <f>FACTIBILIDAD!F49</f>
         <v>RESIDENCIAL</v>
       </c>
-      <c r="H69" s="254"/>
-      <c r="I69" s="255"/>
+      <c r="H69" s="269"/>
+      <c r="I69" s="270"/>
       <c r="J69" s="157">
         <f>IF(FACTIBILIDAD!D49=0,"",FACTIBILIDAD!D49)</f>
-        <v>66666</v>
+        <v>4444</v>
       </c>
       <c r="K69" s="158" t="s">
         <v>322</v>
@@ -7745,18 +7745,18 @@
       <c r="P69" s="93"/>
       <c r="Q69" s="93"/>
     </row>
-    <row r="70" spans="2:17" s="73" customFormat="1" ht="21" x14ac:dyDescent="0.25">
+    <row r="70" spans="2:17" s="73" customFormat="1" ht="19.2" x14ac:dyDescent="0.3">
       <c r="B70" s="93"/>
       <c r="C70" s="93"/>
       <c r="F70" s="74" t="s">
         <v>273</v>
       </c>
-      <c r="G70" s="228" t="str">
+      <c r="G70" s="226" t="str">
         <f>IF(FACTIBILIDAD!F50=0,"",FACTIBILIDAD!F50)</f>
         <v/>
       </c>
-      <c r="H70" s="228"/>
-      <c r="I70" s="256"/>
+      <c r="H70" s="226"/>
+      <c r="I70" s="227"/>
       <c r="J70" s="156" t="str">
         <f>IF(FACTIBILIDAD!D50=0,"",FACTIBILIDAD!D50)</f>
         <v/>
@@ -7767,18 +7767,18 @@
       <c r="P70" s="93"/>
       <c r="Q70" s="93"/>
     </row>
-    <row r="71" spans="2:17" s="73" customFormat="1" ht="21" x14ac:dyDescent="0.25">
+    <row r="71" spans="2:17" s="73" customFormat="1" ht="19.2" x14ac:dyDescent="0.3">
       <c r="B71" s="93"/>
       <c r="C71" s="93"/>
       <c r="F71" s="74" t="s">
         <v>274</v>
       </c>
-      <c r="G71" s="228" t="str">
+      <c r="G71" s="226" t="str">
         <f>IF(FACTIBILIDAD!F51=0,"",FACTIBILIDAD!F51)</f>
         <v/>
       </c>
-      <c r="H71" s="228"/>
-      <c r="I71" s="256"/>
+      <c r="H71" s="226"/>
+      <c r="I71" s="227"/>
       <c r="J71" s="156" t="str">
         <f>IF(FACTIBILIDAD!D51=0,"",FACTIBILIDAD!D51)</f>
         <v/>
@@ -7789,18 +7789,18 @@
       <c r="P71" s="93"/>
       <c r="Q71" s="93"/>
     </row>
-    <row r="72" spans="2:17" s="73" customFormat="1" ht="21.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="72" spans="2:17" s="73" customFormat="1" ht="19.8" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B72" s="93"/>
       <c r="C72" s="93"/>
       <c r="F72" s="128" t="s">
         <v>275</v>
       </c>
-      <c r="G72" s="257" t="str">
+      <c r="G72" s="238" t="str">
         <f>IF(FACTIBILIDAD!F52=0,"")</f>
         <v/>
       </c>
-      <c r="H72" s="257"/>
-      <c r="I72" s="258"/>
+      <c r="H72" s="238"/>
+      <c r="I72" s="271"/>
       <c r="J72" s="160" t="str">
         <f>IF(FACTIBILIDAD!D52=0,"",FACTIBILIDAD!D52)</f>
         <v/>
@@ -7811,7 +7811,7 @@
       <c r="P72" s="93"/>
       <c r="Q72" s="93"/>
     </row>
-    <row r="73" spans="2:17" s="73" customFormat="1" ht="18.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="73" spans="2:17" s="73" customFormat="1" ht="18" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B73" s="93"/>
       <c r="C73" s="93"/>
       <c r="F73" s="77"/>
@@ -7823,21 +7823,21 @@
       <c r="P73" s="93"/>
       <c r="Q73" s="93"/>
     </row>
-    <row r="74" spans="2:17" s="73" customFormat="1" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="74" spans="2:17" s="73" customFormat="1" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B74" s="93"/>
       <c r="C74" s="93"/>
-      <c r="F74" s="251" t="s">
+      <c r="F74" s="240" t="s">
         <v>278</v>
       </c>
-      <c r="G74" s="252"/>
-      <c r="H74" s="253"/>
+      <c r="G74" s="253"/>
+      <c r="H74" s="241"/>
       <c r="I74" s="140"/>
       <c r="J74" s="114"/>
       <c r="K74" s="114"/>
       <c r="P74" s="93"/>
       <c r="Q74" s="93"/>
     </row>
-    <row r="75" spans="2:17" s="73" customFormat="1" ht="18.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="75" spans="2:17" s="73" customFormat="1" ht="18" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B75" s="93"/>
       <c r="C75" s="93"/>
       <c r="F75" s="77"/>
@@ -7849,180 +7849,180 @@
       <c r="P75" s="93"/>
       <c r="Q75" s="93"/>
     </row>
-    <row r="76" spans="2:17" s="73" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="76" spans="2:17" s="73" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B76" s="93"/>
       <c r="C76" s="93"/>
       <c r="D76" s="113"/>
       <c r="E76" s="113"/>
-      <c r="F76" s="223" t="s">
+      <c r="F76" s="228" t="s">
         <v>256</v>
       </c>
-      <c r="G76" s="224"/>
-      <c r="H76" s="224"/>
-      <c r="I76" s="224"/>
-      <c r="J76" s="224"/>
-      <c r="K76" s="224"/>
-      <c r="L76" s="225"/>
+      <c r="G76" s="229"/>
+      <c r="H76" s="229"/>
+      <c r="I76" s="229"/>
+      <c r="J76" s="229"/>
+      <c r="K76" s="229"/>
+      <c r="L76" s="230"/>
       <c r="M76" s="113"/>
       <c r="N76" s="113"/>
       <c r="O76" s="113"/>
       <c r="P76" s="93"/>
       <c r="Q76" s="93"/>
     </row>
-    <row r="77" spans="2:17" s="73" customFormat="1" ht="40.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="77" spans="2:17" s="73" customFormat="1" ht="40.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B77" s="93"/>
       <c r="C77" s="93"/>
-      <c r="F77" s="250" t="s">
+      <c r="F77" s="268" t="s">
         <v>270</v>
       </c>
-      <c r="G77" s="250"/>
-      <c r="H77" s="250"/>
-      <c r="I77" s="250"/>
-      <c r="J77" s="250"/>
-      <c r="K77" s="250"/>
-      <c r="L77" s="250"/>
+      <c r="G77" s="268"/>
+      <c r="H77" s="268"/>
+      <c r="I77" s="268"/>
+      <c r="J77" s="268"/>
+      <c r="K77" s="268"/>
+      <c r="L77" s="268"/>
       <c r="P77" s="93"/>
       <c r="Q77" s="93"/>
     </row>
-    <row r="78" spans="2:17" s="73" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="78" spans="2:17" s="73" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B78" s="93"/>
       <c r="C78" s="93"/>
-      <c r="F78" s="220">
+      <c r="F78" s="222">
         <v>2</v>
       </c>
-      <c r="G78" s="220"/>
-      <c r="H78" s="220"/>
-      <c r="I78" s="220"/>
-      <c r="J78" s="220"/>
-      <c r="K78" s="220"/>
-      <c r="L78" s="220"/>
+      <c r="G78" s="222"/>
+      <c r="H78" s="222"/>
+      <c r="I78" s="222"/>
+      <c r="J78" s="222"/>
+      <c r="K78" s="222"/>
+      <c r="L78" s="222"/>
       <c r="P78" s="93"/>
       <c r="Q78" s="93"/>
     </row>
-    <row r="79" spans="2:17" s="73" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="79" spans="2:17" s="73" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B79" s="93"/>
       <c r="C79" s="93"/>
-      <c r="F79" s="220">
+      <c r="F79" s="222">
         <v>3</v>
       </c>
-      <c r="G79" s="220"/>
-      <c r="H79" s="220"/>
-      <c r="I79" s="220"/>
-      <c r="J79" s="220"/>
-      <c r="K79" s="220"/>
-      <c r="L79" s="220"/>
+      <c r="G79" s="222"/>
+      <c r="H79" s="222"/>
+      <c r="I79" s="222"/>
+      <c r="J79" s="222"/>
+      <c r="K79" s="222"/>
+      <c r="L79" s="222"/>
       <c r="P79" s="93"/>
       <c r="Q79" s="93"/>
     </row>
-    <row r="80" spans="2:17" s="73" customFormat="1" ht="18.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="80" spans="2:17" s="73" customFormat="1" ht="17.399999999999999" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B80" s="93"/>
       <c r="C80" s="93"/>
-      <c r="F80" s="285">
+      <c r="F80" s="235">
         <v>4</v>
       </c>
-      <c r="G80" s="285"/>
-      <c r="H80" s="285"/>
-      <c r="I80" s="285"/>
-      <c r="J80" s="285"/>
-      <c r="K80" s="285"/>
-      <c r="L80" s="285"/>
+      <c r="G80" s="235"/>
+      <c r="H80" s="235"/>
+      <c r="I80" s="235"/>
+      <c r="J80" s="235"/>
+      <c r="K80" s="235"/>
+      <c r="L80" s="235"/>
       <c r="P80" s="93"/>
       <c r="Q80" s="93"/>
     </row>
-    <row r="81" spans="1:17" s="73" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:17" s="73" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B81" s="93"/>
       <c r="C81" s="93"/>
-      <c r="F81" s="245" t="s">
+      <c r="F81" s="263" t="s">
         <v>261</v>
       </c>
-      <c r="G81" s="246"/>
-      <c r="H81" s="246"/>
-      <c r="I81" s="246"/>
-      <c r="J81" s="246"/>
-      <c r="K81" s="246"/>
-      <c r="L81" s="247"/>
+      <c r="G81" s="264"/>
+      <c r="H81" s="264"/>
+      <c r="I81" s="264"/>
+      <c r="J81" s="264"/>
+      <c r="K81" s="264"/>
+      <c r="L81" s="265"/>
       <c r="P81" s="93"/>
       <c r="Q81" s="93"/>
     </row>
-    <row r="82" spans="1:17" s="73" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:17" s="73" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B82" s="93"/>
       <c r="C82" s="93"/>
       <c r="F82" s="94" t="s">
         <v>257</v>
       </c>
-      <c r="G82" s="248">
+      <c r="G82" s="266">
         <f ca="1">G14</f>
-        <v>46180</v>
-      </c>
-      <c r="H82" s="248"/>
-      <c r="I82" s="220" t="s">
+        <v>46183</v>
+      </c>
+      <c r="H82" s="266"/>
+      <c r="I82" s="222" t="s">
         <v>262</v>
       </c>
-      <c r="J82" s="220"/>
-      <c r="K82" s="220"/>
-      <c r="L82" s="249"/>
+      <c r="J82" s="222"/>
+      <c r="K82" s="222"/>
+      <c r="L82" s="267"/>
       <c r="P82" s="93"/>
       <c r="Q82" s="93"/>
     </row>
-    <row r="83" spans="1:17" s="73" customFormat="1" ht="18" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:17" s="73" customFormat="1" ht="17.399999999999999" x14ac:dyDescent="0.3">
       <c r="B83" s="93"/>
       <c r="C83" s="93"/>
       <c r="F83" s="95" t="str">
         <f>G11</f>
         <v> RPNC1-4240426</v>
       </c>
-      <c r="G83" s="219" t="s">
+      <c r="G83" s="223" t="s">
         <v>258</v>
       </c>
-      <c r="H83" s="219"/>
-      <c r="I83" s="279" t="str">
+      <c r="H83" s="223"/>
+      <c r="I83" s="224" t="str">
         <f>G12</f>
         <v> CAJAS ITZEP, RAFAEL SALVADOR</v>
       </c>
-      <c r="J83" s="279"/>
-      <c r="K83" s="219" t="s">
+      <c r="J83" s="224"/>
+      <c r="K83" s="223" t="s">
         <v>259</v>
       </c>
-      <c r="L83" s="280"/>
+      <c r="L83" s="225"/>
       <c r="P83" s="93"/>
       <c r="Q83" s="93"/>
     </row>
-    <row r="84" spans="1:17" s="73" customFormat="1" ht="18" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:17" s="73" customFormat="1" ht="17.399999999999999" x14ac:dyDescent="0.3">
       <c r="B84" s="93"/>
       <c r="C84" s="93"/>
       <c r="F84" s="95"/>
-      <c r="G84" s="219" t="s">
+      <c r="G84" s="223" t="s">
         <v>260</v>
       </c>
-      <c r="H84" s="219"/>
-      <c r="I84" s="219"/>
-      <c r="J84" s="240" t="str">
+      <c r="H84" s="223"/>
+      <c r="I84" s="223"/>
+      <c r="J84" s="258" t="str">
         <f>G13</f>
         <v> 8va AVENIDA 0-10</v>
       </c>
-      <c r="K84" s="240"/>
-      <c r="L84" s="244"/>
+      <c r="K84" s="258"/>
+      <c r="L84" s="262"/>
       <c r="P84" s="93"/>
       <c r="Q84" s="93"/>
     </row>
-    <row r="85" spans="1:17" s="73" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:17" s="73" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B85" s="93"/>
       <c r="C85" s="93"/>
       <c r="F85" s="94" t="s">
         <v>285</v>
       </c>
-      <c r="G85" s="276" t="s">
+      <c r="G85" s="219" t="s">
         <v>336</v>
       </c>
-      <c r="H85" s="276"/>
-      <c r="I85" s="276"/>
-      <c r="J85" s="276"/>
-      <c r="K85" s="276"/>
-      <c r="L85" s="277"/>
+      <c r="H85" s="219"/>
+      <c r="I85" s="219"/>
+      <c r="J85" s="219"/>
+      <c r="K85" s="219"/>
+      <c r="L85" s="220"/>
       <c r="P85" s="93"/>
       <c r="Q85" s="93"/>
     </row>
-    <row r="86" spans="1:17" s="73" customFormat="1" ht="18.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="86" spans="1:17" s="73" customFormat="1" ht="18" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B86" s="93"/>
       <c r="C86" s="93"/>
       <c r="D86" s="77"/>
@@ -8040,65 +8040,65 @@
       <c r="P86" s="93"/>
       <c r="Q86" s="93"/>
     </row>
-    <row r="87" spans="1:17" s="73" customFormat="1" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="87" spans="1:17" s="73" customFormat="1" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B87" s="93"/>
       <c r="C87" s="93"/>
       <c r="D87" s="77"/>
       <c r="E87" s="77"/>
-      <c r="F87" s="241" t="s">
+      <c r="F87" s="259" t="s">
         <v>271</v>
       </c>
-      <c r="G87" s="242"/>
-      <c r="H87" s="242"/>
-      <c r="I87" s="242"/>
-      <c r="J87" s="242"/>
-      <c r="K87" s="242"/>
-      <c r="L87" s="243"/>
+      <c r="G87" s="260"/>
+      <c r="H87" s="260"/>
+      <c r="I87" s="260"/>
+      <c r="J87" s="260"/>
+      <c r="K87" s="260"/>
+      <c r="L87" s="261"/>
       <c r="M87" s="77"/>
       <c r="N87" s="77"/>
       <c r="O87" s="77"/>
       <c r="P87" s="93"/>
       <c r="Q87" s="93"/>
     </row>
-    <row r="88" spans="1:17" s="73" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:17" s="73" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B88" s="93"/>
       <c r="C88" s="93"/>
       <c r="D88" s="77"/>
       <c r="E88" s="77"/>
-      <c r="F88" s="240" t="s">
+      <c r="F88" s="258" t="s">
         <v>277</v>
       </c>
-      <c r="G88" s="240"/>
-      <c r="H88" s="240"/>
-      <c r="I88" s="240"/>
-      <c r="J88" s="240"/>
-      <c r="K88" s="240"/>
-      <c r="L88" s="240"/>
+      <c r="G88" s="258"/>
+      <c r="H88" s="258"/>
+      <c r="I88" s="258"/>
+      <c r="J88" s="258"/>
+      <c r="K88" s="258"/>
+      <c r="L88" s="258"/>
       <c r="M88" s="77"/>
       <c r="N88" s="77"/>
       <c r="O88" s="77"/>
       <c r="P88" s="93"/>
       <c r="Q88" s="93"/>
     </row>
-    <row r="89" spans="1:17" s="73" customFormat="1" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:17" s="73" customFormat="1" ht="45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B89" s="93"/>
       <c r="C89" s="93"/>
       <c r="D89" s="77"/>
       <c r="E89" s="77"/>
-      <c r="F89" s="240"/>
-      <c r="G89" s="240"/>
-      <c r="H89" s="240"/>
-      <c r="I89" s="240"/>
-      <c r="J89" s="240"/>
-      <c r="K89" s="240"/>
-      <c r="L89" s="240"/>
+      <c r="F89" s="258"/>
+      <c r="G89" s="258"/>
+      <c r="H89" s="258"/>
+      <c r="I89" s="258"/>
+      <c r="J89" s="258"/>
+      <c r="K89" s="258"/>
+      <c r="L89" s="258"/>
       <c r="M89" s="77"/>
       <c r="N89" s="77"/>
       <c r="O89" s="77"/>
       <c r="P89" s="93"/>
       <c r="Q89" s="93"/>
     </row>
-    <row r="90" spans="1:17" s="73" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:17" s="73" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B90" s="93"/>
       <c r="C90" s="93"/>
       <c r="D90" s="77"/>
@@ -8116,7 +8116,7 @@
       <c r="P90" s="93"/>
       <c r="Q90" s="93"/>
     </row>
-    <row r="91" spans="1:17" s="73" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:17" s="73" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B91" s="93"/>
       <c r="C91" s="93"/>
       <c r="D91" s="77"/>
@@ -8134,13 +8134,13 @@
       <c r="P91" s="93"/>
       <c r="Q91" s="93"/>
     </row>
-    <row r="92" spans="1:17" s="73" customFormat="1" ht="18" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:17" s="73" customFormat="1" ht="16.8" x14ac:dyDescent="0.3">
       <c r="B92" s="93"/>
       <c r="C92" s="93"/>
       <c r="P92" s="93"/>
       <c r="Q92" s="93"/>
     </row>
-    <row r="93" spans="1:17" s="73" customFormat="1" ht="19.5" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:17" s="73" customFormat="1" ht="21" x14ac:dyDescent="0.3">
       <c r="A93" s="142"/>
       <c r="B93" s="141"/>
       <c r="C93" s="141"/>
@@ -8149,7 +8149,7 @@
       <c r="P93" s="141"/>
       <c r="Q93" s="141"/>
     </row>
-    <row r="94" spans="1:17" s="73" customFormat="1" ht="19.5" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:17" s="73" customFormat="1" ht="21" x14ac:dyDescent="0.3">
       <c r="A94" s="142"/>
       <c r="B94" s="141"/>
       <c r="C94" s="141"/>
@@ -8158,7 +8158,7 @@
       <c r="P94" s="141"/>
       <c r="Q94" s="141"/>
     </row>
-    <row r="95" spans="1:17" ht="19.5" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:17" ht="21" x14ac:dyDescent="0.3">
       <c r="A95" s="142"/>
       <c r="B95" s="141"/>
       <c r="C95" s="141"/>
@@ -8177,7 +8177,7 @@
       <c r="P95" s="141"/>
       <c r="Q95" s="141"/>
     </row>
-    <row r="96" spans="1:17" ht="16.5" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:17" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A96" s="145"/>
       <c r="B96" s="144"/>
       <c r="C96" s="144"/>
@@ -8196,7 +8196,7 @@
       <c r="P96" s="144"/>
       <c r="Q96" s="144"/>
     </row>
-    <row r="97" spans="1:17" ht="16.5" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:17" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A97" s="145"/>
       <c r="B97" s="144"/>
       <c r="C97" s="144"/>
@@ -8215,7 +8215,7 @@
       <c r="P97" s="144"/>
       <c r="Q97" s="144"/>
     </row>
-    <row r="98" spans="1:17" ht="16.5" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:17" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A98" s="145"/>
       <c r="B98" s="144"/>
       <c r="C98" s="144"/>
@@ -8234,7 +8234,7 @@
       <c r="P98" s="144"/>
       <c r="Q98" s="144"/>
     </row>
-    <row r="99" spans="1:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A99" s="145"/>
       <c r="B99" s="144"/>
       <c r="C99" s="144"/>
@@ -8253,24 +8253,24 @@
       <c r="P99" s="144"/>
       <c r="Q99" s="144"/>
     </row>
-    <row r="100" spans="1:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C100" s="144"/>
       <c r="P100" s="144"/>
     </row>
-    <row r="101" spans="1:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="P101" s="144"/>
     </row>
-    <row r="102" spans="1:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="103" spans="1:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="104" spans="1:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="105" spans="1:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="106" spans="1:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="107" spans="1:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="108" spans="1:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="109" spans="1:17" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="110" spans="1:17" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="111" spans="1:17" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="142" spans="7:12" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="103" spans="1:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="104" spans="1:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="105" spans="1:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="106" spans="1:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="107" spans="1:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="108" spans="1:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="109" spans="1:17" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="110" spans="1:17" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="111" spans="1:17" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="142" spans="7:12" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="G142" s="192" t="s">
         <v>336</v>
       </c>
@@ -8280,7 +8280,7 @@
       <c r="K142" s="192"/>
       <c r="L142" s="193"/>
     </row>
-    <row r="143" spans="7:12" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="143" spans="7:12" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="G143" s="146" t="s">
         <v>335</v>
       </c>
@@ -8292,35 +8292,22 @@
     </row>
   </sheetData>
   <mergeCells count="61">
-    <mergeCell ref="G85:L85"/>
-    <mergeCell ref="N35:O39"/>
-    <mergeCell ref="F47:G47"/>
-    <mergeCell ref="G83:H83"/>
-    <mergeCell ref="I83:J83"/>
-    <mergeCell ref="K83:L83"/>
-    <mergeCell ref="G71:I71"/>
-    <mergeCell ref="F78:L78"/>
-    <mergeCell ref="F42:L42"/>
-    <mergeCell ref="F37:H37"/>
-    <mergeCell ref="F40:I40"/>
-    <mergeCell ref="F79:L79"/>
-    <mergeCell ref="F80:L80"/>
-    <mergeCell ref="F64:L64"/>
-    <mergeCell ref="F51:G51"/>
-    <mergeCell ref="G18:J18"/>
-    <mergeCell ref="F56:L56"/>
-    <mergeCell ref="F58:G58"/>
-    <mergeCell ref="F57:G57"/>
-    <mergeCell ref="I38:I39"/>
-    <mergeCell ref="F53:L54"/>
-    <mergeCell ref="L38:L39"/>
-    <mergeCell ref="F20:L20"/>
-    <mergeCell ref="G22:J22"/>
-    <mergeCell ref="F44:G44"/>
-    <mergeCell ref="F45:G45"/>
-    <mergeCell ref="F46:G46"/>
-    <mergeCell ref="I24:J24"/>
-    <mergeCell ref="F24:G24"/>
+    <mergeCell ref="G2:I2"/>
+    <mergeCell ref="F52:G52"/>
+    <mergeCell ref="F50:G50"/>
+    <mergeCell ref="G4:I4"/>
+    <mergeCell ref="F9:L9"/>
+    <mergeCell ref="G11:J11"/>
+    <mergeCell ref="G12:J12"/>
+    <mergeCell ref="G13:J13"/>
+    <mergeCell ref="G14:J14"/>
+    <mergeCell ref="G15:J15"/>
+    <mergeCell ref="F48:G48"/>
+    <mergeCell ref="L4:N4"/>
+    <mergeCell ref="G16:J16"/>
+    <mergeCell ref="G17:J17"/>
+    <mergeCell ref="F49:G49"/>
+    <mergeCell ref="G6:I7"/>
     <mergeCell ref="F88:L89"/>
     <mergeCell ref="F87:L87"/>
     <mergeCell ref="G84:I84"/>
@@ -8337,22 +8324,35 @@
     <mergeCell ref="G69:I69"/>
     <mergeCell ref="G70:I70"/>
     <mergeCell ref="G72:I72"/>
-    <mergeCell ref="G2:I2"/>
-    <mergeCell ref="F52:G52"/>
-    <mergeCell ref="F50:G50"/>
-    <mergeCell ref="G4:I4"/>
-    <mergeCell ref="F9:L9"/>
-    <mergeCell ref="G11:J11"/>
-    <mergeCell ref="G12:J12"/>
-    <mergeCell ref="G13:J13"/>
-    <mergeCell ref="G14:J14"/>
-    <mergeCell ref="G15:J15"/>
-    <mergeCell ref="F48:G48"/>
-    <mergeCell ref="L4:N4"/>
-    <mergeCell ref="G16:J16"/>
-    <mergeCell ref="G17:J17"/>
-    <mergeCell ref="F49:G49"/>
-    <mergeCell ref="G6:I7"/>
+    <mergeCell ref="G18:J18"/>
+    <mergeCell ref="F56:L56"/>
+    <mergeCell ref="F58:G58"/>
+    <mergeCell ref="F57:G57"/>
+    <mergeCell ref="I38:I39"/>
+    <mergeCell ref="F53:L54"/>
+    <mergeCell ref="L38:L39"/>
+    <mergeCell ref="F20:L20"/>
+    <mergeCell ref="G22:J22"/>
+    <mergeCell ref="F44:G44"/>
+    <mergeCell ref="F45:G45"/>
+    <mergeCell ref="F46:G46"/>
+    <mergeCell ref="I24:J24"/>
+    <mergeCell ref="F24:G24"/>
+    <mergeCell ref="G85:L85"/>
+    <mergeCell ref="N35:O39"/>
+    <mergeCell ref="F47:G47"/>
+    <mergeCell ref="G83:H83"/>
+    <mergeCell ref="I83:J83"/>
+    <mergeCell ref="K83:L83"/>
+    <mergeCell ref="G71:I71"/>
+    <mergeCell ref="F78:L78"/>
+    <mergeCell ref="F42:L42"/>
+    <mergeCell ref="F37:H37"/>
+    <mergeCell ref="F40:I40"/>
+    <mergeCell ref="F79:L79"/>
+    <mergeCell ref="F80:L80"/>
+    <mergeCell ref="F64:L64"/>
+    <mergeCell ref="F51:G51"/>
   </mergeCells>
   <conditionalFormatting sqref="G85:L85">
     <cfRule type="containsText" dxfId="27" priority="1" operator="containsText" text="NO FACTIBLE">
@@ -8655,20 +8655,20 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
   <sheetPr codeName="Hoja5"/>
   <dimension ref="A1:AS23"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="2" max="2" width="52.85546875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="11.42578125" style="11"/>
-    <col min="5" max="5" width="53.7109375" customWidth="1"/>
-    <col min="6" max="6" width="12.7109375" style="11" customWidth="1"/>
+    <col min="2" max="2" width="52.88671875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="11.44140625" style="11"/>
+    <col min="5" max="5" width="53.6640625" customWidth="1"/>
+    <col min="6" max="6" width="12.6640625" style="11" customWidth="1"/>
     <col min="15" max="15" width="13" hidden="1" customWidth="1"/>
     <col min="16" max="16" width="14" hidden="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:45" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:45" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="E1" s="162"/>
     </row>
-    <row r="2" spans="1:45" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:45" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="E2" s="163" t="s">
         <v>323</v>
       </c>
@@ -8677,7 +8677,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:45" ht="21.75" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="3" spans="1:45" ht="21.6" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A3" s="165">
         <v>1</v>
       </c>
@@ -8700,7 +8700,7 @@
         <v>325</v>
       </c>
     </row>
-    <row r="4" spans="1:45" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:45" x14ac:dyDescent="0.3">
       <c r="A4" s="170">
         <v>2</v>
       </c>
@@ -8718,7 +8718,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="5" spans="1:45" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:45" x14ac:dyDescent="0.3">
       <c r="A5" s="170">
         <v>3</v>
       </c>
@@ -8729,7 +8729,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="6" spans="1:45" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:45" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A6" s="174">
         <v>4</v>
       </c>
@@ -8740,8 +8740,8 @@
         <v>325</v>
       </c>
     </row>
-    <row r="18" spans="2:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
-    <row r="19" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="18" spans="2:4" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
+    <row r="19" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B19" s="177" t="s">
         <v>329</v>
       </c>
@@ -8750,7 +8750,7 @@
       </c>
       <c r="D19" s="179"/>
     </row>
-    <row r="20" spans="2:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="20" spans="2:4" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B20" s="180" t="s">
         <v>330</v>
       </c>
@@ -8762,7 +8762,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="21" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="21" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B21" s="183" t="s">
         <v>331</v>
       </c>
@@ -8774,7 +8774,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="22" spans="2:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="22" spans="2:4" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B22" s="186" t="s">
         <v>332</v>
       </c>
@@ -8786,7 +8786,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="23" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="23" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B23" s="6"/>
       <c r="C23" s="189"/>
     </row>
@@ -8808,29 +8808,29 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:Q90"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="11.42578125" defaultRowHeight="13.5" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11.44140625" defaultRowHeight="13.2" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="2" width="4.85546875" style="62" customWidth="1"/>
-    <col min="3" max="4" width="4.85546875" style="61" customWidth="1"/>
-    <col min="5" max="5" width="5.28515625" style="61" customWidth="1"/>
+    <col min="1" max="2" width="4.88671875" style="62" customWidth="1"/>
+    <col min="3" max="4" width="4.88671875" style="61" customWidth="1"/>
+    <col min="5" max="5" width="5.33203125" style="61" customWidth="1"/>
     <col min="6" max="6" width="47" style="61" customWidth="1"/>
-    <col min="7" max="7" width="9.42578125" style="61" customWidth="1"/>
+    <col min="7" max="7" width="9.44140625" style="61" customWidth="1"/>
     <col min="8" max="8" width="12" style="61" customWidth="1"/>
-    <col min="9" max="9" width="44.28515625" style="61" customWidth="1"/>
+    <col min="9" max="9" width="44.33203125" style="61" customWidth="1"/>
     <col min="10" max="10" width="20" style="61" customWidth="1"/>
-    <col min="11" max="11" width="12.28515625" style="61" customWidth="1"/>
-    <col min="12" max="12" width="33.85546875" style="61" customWidth="1"/>
-    <col min="13" max="13" width="5.7109375" style="61" customWidth="1"/>
-    <col min="14" max="14" width="5.42578125" style="61" customWidth="1"/>
+    <col min="11" max="11" width="12.33203125" style="61" customWidth="1"/>
+    <col min="12" max="12" width="33.88671875" style="61" customWidth="1"/>
+    <col min="13" max="13" width="5.6640625" style="61" customWidth="1"/>
+    <col min="14" max="14" width="5.44140625" style="61" customWidth="1"/>
     <col min="15" max="15" width="9" style="61" hidden="1" customWidth="1"/>
-    <col min="16" max="16" width="5.42578125" style="62" customWidth="1"/>
-    <col min="17" max="17" width="9.140625" style="62" customWidth="1"/>
-    <col min="18" max="18" width="11.42578125" style="61"/>
-    <col min="19" max="19" width="17.85546875" style="61" bestFit="1" customWidth="1"/>
-    <col min="20" max="16384" width="11.42578125" style="61"/>
+    <col min="16" max="16" width="5.44140625" style="62" customWidth="1"/>
+    <col min="17" max="17" width="9.109375" style="62" customWidth="1"/>
+    <col min="18" max="18" width="11.44140625" style="61"/>
+    <col min="19" max="19" width="17.88671875" style="61" bestFit="1" customWidth="1"/>
+    <col min="20" max="16384" width="11.44140625" style="61"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:17" s="63" customFormat="1" ht="18" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:17" s="63" customFormat="1" ht="17.399999999999999" x14ac:dyDescent="0.3">
       <c r="A1" s="66"/>
       <c r="B1" s="66"/>
       <c r="C1" s="66"/>
@@ -8849,16 +8849,16 @@
       <c r="P1" s="66"/>
       <c r="Q1" s="66"/>
     </row>
-    <row r="2" spans="1:17" s="63" customFormat="1" ht="18" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:17" s="63" customFormat="1" ht="17.399999999999999" x14ac:dyDescent="0.3">
       <c r="A2" s="66"/>
       <c r="B2" s="66"/>
       <c r="C2" s="66"/>
       <c r="D2" s="68"/>
       <c r="E2" s="69"/>
       <c r="F2" s="69"/>
-      <c r="G2" s="290"/>
-      <c r="H2" s="290"/>
-      <c r="I2" s="290"/>
+      <c r="G2" s="298"/>
+      <c r="H2" s="298"/>
+      <c r="I2" s="298"/>
       <c r="J2" s="69"/>
       <c r="K2" s="69"/>
       <c r="L2" s="69"/>
@@ -8868,26 +8868,26 @@
       <c r="P2" s="66"/>
       <c r="Q2" s="66"/>
     </row>
-    <row r="3" spans="1:17" s="63" customFormat="1" ht="18.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:17" s="63" customFormat="1" ht="17.399999999999999" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A3" s="66"/>
       <c r="B3" s="66"/>
       <c r="C3" s="66"/>
       <c r="P3" s="66"/>
       <c r="Q3" s="66"/>
     </row>
-    <row r="4" spans="1:17" s="63" customFormat="1" ht="45.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:17" s="63" customFormat="1" ht="45.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A4" s="66"/>
       <c r="B4" s="66"/>
       <c r="C4" s="66"/>
-      <c r="G4" s="291" t="s">
+      <c r="G4" s="331" t="s">
         <v>279</v>
       </c>
-      <c r="H4" s="292"/>
-      <c r="I4" s="292"/>
+      <c r="H4" s="332"/>
+      <c r="I4" s="332"/>
       <c r="P4" s="66"/>
       <c r="Q4" s="66"/>
     </row>
-    <row r="5" spans="1:17" s="63" customFormat="1" ht="18.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:17" s="63" customFormat="1" ht="17.399999999999999" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A5" s="66"/>
       <c r="B5" s="66"/>
       <c r="C5" s="66"/>
@@ -8898,11 +8898,11 @@
       <c r="A6" s="66"/>
       <c r="B6" s="66"/>
       <c r="C6" s="66"/>
-      <c r="G6" s="234" t="s">
+      <c r="G6" s="281" t="s">
         <v>90</v>
       </c>
-      <c r="H6" s="235"/>
-      <c r="I6" s="236"/>
+      <c r="H6" s="282"/>
+      <c r="I6" s="283"/>
       <c r="P6" s="66"/>
       <c r="Q6" s="66"/>
     </row>
@@ -8910,13 +8910,13 @@
       <c r="A7" s="66"/>
       <c r="B7" s="66"/>
       <c r="C7" s="66"/>
-      <c r="G7" s="237"/>
-      <c r="H7" s="238"/>
-      <c r="I7" s="239"/>
+      <c r="G7" s="284"/>
+      <c r="H7" s="285"/>
+      <c r="I7" s="286"/>
       <c r="P7" s="66"/>
       <c r="Q7" s="66"/>
     </row>
-    <row r="8" spans="1:17" s="63" customFormat="1" ht="18.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:17" s="63" customFormat="1" ht="18" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A8" s="66"/>
       <c r="B8" s="66"/>
       <c r="C8" s="66"/>
@@ -8924,145 +8924,145 @@
       <c r="P8" s="66"/>
       <c r="Q8" s="66"/>
     </row>
-    <row r="9" spans="1:17" s="63" customFormat="1" ht="23.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:17" s="63" customFormat="1" ht="23.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A9" s="66"/>
       <c r="B9" s="66"/>
       <c r="C9" s="66"/>
-      <c r="F9" s="293" t="s">
+      <c r="F9" s="299" t="s">
         <v>251</v>
       </c>
-      <c r="G9" s="294"/>
-      <c r="H9" s="294"/>
-      <c r="I9" s="294"/>
-      <c r="J9" s="294"/>
-      <c r="K9" s="294"/>
-      <c r="L9" s="295"/>
+      <c r="G9" s="300"/>
+      <c r="H9" s="300"/>
+      <c r="I9" s="300"/>
+      <c r="J9" s="300"/>
+      <c r="K9" s="300"/>
+      <c r="L9" s="301"/>
       <c r="P9" s="66"/>
       <c r="Q9" s="66"/>
     </row>
-    <row r="10" spans="1:17" s="63" customFormat="1" ht="18.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:17" s="63" customFormat="1" ht="17.399999999999999" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A10" s="66"/>
       <c r="B10" s="66"/>
       <c r="C10" s="66"/>
       <c r="P10" s="66"/>
       <c r="Q10" s="66"/>
     </row>
-    <row r="11" spans="1:17" s="63" customFormat="1" ht="20.25" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:17" s="63" customFormat="1" ht="20.399999999999999" x14ac:dyDescent="0.35">
       <c r="A11" s="66"/>
       <c r="B11" s="66"/>
       <c r="C11" s="66"/>
       <c r="F11" s="67" t="s">
         <v>229</v>
       </c>
-      <c r="G11" s="291" t="str">
+      <c r="G11" s="331" t="str">
         <f>FACTIBILIDAD!D11</f>
         <v> RPNC1-4240426</v>
       </c>
-      <c r="H11" s="292"/>
-      <c r="I11" s="292"/>
-      <c r="J11" s="296"/>
+      <c r="H11" s="332"/>
+      <c r="I11" s="332"/>
+      <c r="J11" s="333"/>
       <c r="P11" s="66"/>
       <c r="Q11" s="66"/>
     </row>
-    <row r="12" spans="1:17" s="63" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:17" s="63" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A12" s="66"/>
       <c r="B12" s="66"/>
       <c r="C12" s="66"/>
       <c r="F12" s="67" t="s">
         <v>175</v>
       </c>
-      <c r="G12" s="287" t="str">
+      <c r="G12" s="325" t="str">
         <f>FACTIBILIDAD!D9</f>
         <v> CAJAS ITZEP, RAFAEL SALVADOR</v>
       </c>
-      <c r="H12" s="288"/>
-      <c r="I12" s="288"/>
-      <c r="J12" s="289"/>
+      <c r="H12" s="326"/>
+      <c r="I12" s="326"/>
+      <c r="J12" s="327"/>
       <c r="P12" s="66"/>
       <c r="Q12" s="66"/>
     </row>
-    <row r="13" spans="1:17" s="63" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:17" s="63" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A13" s="66"/>
       <c r="B13" s="66"/>
       <c r="C13" s="66"/>
       <c r="F13" s="67" t="s">
         <v>233</v>
       </c>
-      <c r="G13" s="287" t="str">
+      <c r="G13" s="325" t="str">
         <f>FACTIBILIDAD!D10</f>
         <v> 8va AVENIDA 0-10</v>
       </c>
-      <c r="H13" s="288"/>
-      <c r="I13" s="288"/>
-      <c r="J13" s="289"/>
+      <c r="H13" s="326"/>
+      <c r="I13" s="326"/>
+      <c r="J13" s="327"/>
       <c r="P13" s="66"/>
       <c r="Q13" s="66"/>
     </row>
-    <row r="14" spans="1:17" s="63" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:17" s="63" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A14" s="66"/>
       <c r="B14" s="66"/>
       <c r="C14" s="66"/>
       <c r="F14" s="67" t="s">
         <v>176</v>
       </c>
-      <c r="G14" s="287">
+      <c r="G14" s="325">
         <f ca="1">FACTIBILIDAD!D8</f>
-        <v>46180</v>
-      </c>
-      <c r="H14" s="288"/>
-      <c r="I14" s="288"/>
-      <c r="J14" s="289"/>
+        <v>46183</v>
+      </c>
+      <c r="H14" s="326"/>
+      <c r="I14" s="326"/>
+      <c r="J14" s="327"/>
       <c r="P14" s="66"/>
       <c r="Q14" s="66"/>
     </row>
-    <row r="15" spans="1:17" s="63" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:17" s="63" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A15" s="66"/>
       <c r="B15" s="66"/>
       <c r="C15" s="66"/>
       <c r="F15" s="67" t="s">
         <v>235</v>
       </c>
-      <c r="G15" s="287" t="str">
+      <c r="G15" s="325" t="str">
         <f>FACTIBILIDAD!D12</f>
         <v xml:space="preserve">UNIFAMILIAR </v>
       </c>
-      <c r="H15" s="288"/>
-      <c r="I15" s="288"/>
-      <c r="J15" s="289"/>
+      <c r="H15" s="326"/>
+      <c r="I15" s="326"/>
+      <c r="J15" s="327"/>
       <c r="P15" s="66"/>
       <c r="Q15" s="66"/>
     </row>
-    <row r="16" spans="1:17" s="63" customFormat="1" ht="18" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:17" s="63" customFormat="1" ht="17.399999999999999" x14ac:dyDescent="0.3">
       <c r="A16" s="66"/>
       <c r="B16" s="66"/>
       <c r="C16" s="66"/>
       <c r="F16" s="67" t="s">
         <v>239</v>
       </c>
-      <c r="G16" s="287" t="str">
+      <c r="G16" s="325" t="str">
         <f>FACTIBILIDAD!D13</f>
         <v>F</v>
       </c>
-      <c r="H16" s="288"/>
-      <c r="I16" s="288"/>
-      <c r="J16" s="289"/>
+      <c r="H16" s="326"/>
+      <c r="I16" s="326"/>
+      <c r="J16" s="327"/>
       <c r="P16" s="66"/>
       <c r="Q16" s="66"/>
     </row>
-    <row r="17" spans="1:17" s="63" customFormat="1" ht="18" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:17" s="63" customFormat="1" ht="17.399999999999999" x14ac:dyDescent="0.3">
       <c r="A17" s="66"/>
       <c r="B17" s="66"/>
       <c r="C17" s="66"/>
       <c r="F17" s="67" t="s">
         <v>240</v>
       </c>
-      <c r="G17" s="287" t="str">
+      <c r="G17" s="325" t="str">
         <f>FACTIBILIDAD!D14</f>
         <v>FOL</v>
       </c>
-      <c r="H17" s="288"/>
-      <c r="I17" s="288"/>
-      <c r="J17" s="289"/>
+      <c r="H17" s="326"/>
+      <c r="I17" s="326"/>
+      <c r="J17" s="327"/>
       <c r="K17" s="69"/>
       <c r="L17" s="69"/>
       <c r="M17" s="69"/>
@@ -9071,24 +9071,24 @@
       <c r="P17" s="66"/>
       <c r="Q17" s="66"/>
     </row>
-    <row r="18" spans="1:17" s="63" customFormat="1" ht="18.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:17" s="63" customFormat="1" ht="18" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A18" s="66"/>
       <c r="B18" s="66"/>
       <c r="C18" s="66"/>
       <c r="F18" s="67" t="s">
         <v>241</v>
       </c>
-      <c r="G18" s="301" t="str">
+      <c r="G18" s="328" t="str">
         <f>FACTIBILIDAD!D15</f>
         <v>LIB</v>
       </c>
-      <c r="H18" s="302"/>
-      <c r="I18" s="302"/>
-      <c r="J18" s="303"/>
+      <c r="H18" s="329"/>
+      <c r="I18" s="329"/>
+      <c r="J18" s="330"/>
       <c r="P18" s="66"/>
       <c r="Q18" s="66"/>
     </row>
-    <row r="19" spans="1:17" s="63" customFormat="1" ht="18.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:17" s="63" customFormat="1" ht="18" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A19" s="66"/>
       <c r="B19" s="66"/>
       <c r="C19" s="66"/>
@@ -9100,23 +9100,23 @@
       <c r="P19" s="66"/>
       <c r="Q19" s="66"/>
     </row>
-    <row r="20" spans="1:17" s="63" customFormat="1" ht="20.25" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:17" s="63" customFormat="1" ht="20.399999999999999" x14ac:dyDescent="0.35">
       <c r="A20" s="66"/>
       <c r="B20" s="66"/>
       <c r="C20" s="66"/>
-      <c r="F20" s="293" t="s">
+      <c r="F20" s="299" t="s">
         <v>280</v>
       </c>
-      <c r="G20" s="294"/>
-      <c r="H20" s="294"/>
-      <c r="I20" s="294"/>
-      <c r="J20" s="294"/>
-      <c r="K20" s="294"/>
-      <c r="L20" s="295"/>
+      <c r="G20" s="300"/>
+      <c r="H20" s="300"/>
+      <c r="I20" s="300"/>
+      <c r="J20" s="300"/>
+      <c r="K20" s="300"/>
+      <c r="L20" s="301"/>
       <c r="P20" s="66"/>
       <c r="Q20" s="66"/>
     </row>
-    <row r="21" spans="1:17" s="63" customFormat="1" ht="18.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:17" s="63" customFormat="1" ht="18" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A21" s="66"/>
       <c r="B21" s="66"/>
       <c r="C21" s="66"/>
@@ -9130,58 +9130,58 @@
       <c r="P21" s="66"/>
       <c r="Q21" s="66"/>
     </row>
-    <row r="22" spans="1:17" s="63" customFormat="1" ht="36" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:17" s="63" customFormat="1" ht="36" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A22" s="66"/>
       <c r="B22" s="66"/>
       <c r="C22" s="66"/>
       <c r="F22" s="85">
         <v>1</v>
       </c>
-      <c r="G22" s="251" t="str">
+      <c r="G22" s="240" t="str">
         <f>FACTIBILIDAD!D19</f>
         <v>URBANO Q2 (URB-Q2)</v>
       </c>
-      <c r="H22" s="252"/>
-      <c r="I22" s="252"/>
-      <c r="J22" s="252"/>
+      <c r="H22" s="253"/>
+      <c r="I22" s="253"/>
+      <c r="J22" s="253"/>
       <c r="K22" s="87"/>
       <c r="L22" s="88"/>
       <c r="P22" s="66"/>
       <c r="Q22" s="66"/>
     </row>
-    <row r="23" spans="1:17" s="63" customFormat="1" ht="36" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:17" s="63" customFormat="1" ht="36" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A23" s="66"/>
       <c r="B23" s="66"/>
       <c r="C23" s="66"/>
       <c r="F23" s="85">
         <v>2</v>
       </c>
-      <c r="G23" s="251"/>
-      <c r="H23" s="252"/>
-      <c r="I23" s="252"/>
-      <c r="J23" s="252"/>
+      <c r="G23" s="240"/>
+      <c r="H23" s="253"/>
+      <c r="I23" s="253"/>
+      <c r="J23" s="253"/>
       <c r="K23" s="87"/>
       <c r="L23" s="88"/>
       <c r="P23" s="66"/>
       <c r="Q23" s="66"/>
     </row>
-    <row r="24" spans="1:17" s="63" customFormat="1" ht="36.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:17" s="63" customFormat="1" ht="36.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A24" s="66"/>
       <c r="B24" s="66"/>
       <c r="C24" s="66"/>
       <c r="F24" s="85">
         <v>3</v>
       </c>
-      <c r="G24" s="251"/>
-      <c r="H24" s="252"/>
-      <c r="I24" s="252"/>
-      <c r="J24" s="252"/>
+      <c r="G24" s="240"/>
+      <c r="H24" s="253"/>
+      <c r="I24" s="253"/>
+      <c r="J24" s="253"/>
       <c r="K24" s="81"/>
       <c r="L24" s="88"/>
       <c r="P24" s="66"/>
       <c r="Q24" s="66"/>
     </row>
-    <row r="25" spans="1:17" s="63" customFormat="1" ht="36.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:17" s="63" customFormat="1" ht="36.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A25" s="66"/>
       <c r="B25" s="66"/>
       <c r="C25" s="66"/>
@@ -9194,23 +9194,23 @@
       <c r="P25" s="66"/>
       <c r="Q25" s="66"/>
     </row>
-    <row r="26" spans="1:17" s="63" customFormat="1" ht="20.25" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:17" s="63" customFormat="1" ht="20.399999999999999" x14ac:dyDescent="0.35">
       <c r="A26" s="66"/>
       <c r="B26" s="66"/>
       <c r="C26" s="66"/>
-      <c r="F26" s="293" t="s">
+      <c r="F26" s="299" t="s">
         <v>281</v>
       </c>
-      <c r="G26" s="294"/>
-      <c r="H26" s="294"/>
-      <c r="I26" s="294"/>
-      <c r="J26" s="294"/>
-      <c r="K26" s="294"/>
-      <c r="L26" s="295"/>
+      <c r="G26" s="300"/>
+      <c r="H26" s="300"/>
+      <c r="I26" s="300"/>
+      <c r="J26" s="300"/>
+      <c r="K26" s="300"/>
+      <c r="L26" s="301"/>
       <c r="P26" s="66"/>
       <c r="Q26" s="66"/>
     </row>
-    <row r="27" spans="1:17" s="63" customFormat="1" ht="21" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:17" s="63" customFormat="1" ht="21" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A27" s="66"/>
       <c r="B27" s="66"/>
       <c r="C27" s="66"/>
@@ -9224,16 +9224,16 @@
       <c r="P27" s="66"/>
       <c r="Q27" s="66"/>
     </row>
-    <row r="28" spans="1:17" s="63" customFormat="1" ht="20.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:17" s="63" customFormat="1" ht="20.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A28" s="66"/>
       <c r="B28" s="66"/>
       <c r="C28" s="66"/>
-      <c r="G28" s="304" t="s">
+      <c r="G28" s="302" t="s">
         <v>283</v>
       </c>
-      <c r="H28" s="305"/>
-      <c r="I28" s="318"/>
-      <c r="J28" s="319"/>
+      <c r="H28" s="303"/>
+      <c r="I28" s="314"/>
+      <c r="J28" s="315"/>
       <c r="K28" s="86"/>
       <c r="L28" s="86"/>
       <c r="P28" s="66"/>
@@ -9243,10 +9243,10 @@
       <c r="A29" s="66"/>
       <c r="B29" s="66"/>
       <c r="C29" s="66"/>
-      <c r="G29" s="306"/>
-      <c r="H29" s="307"/>
-      <c r="I29" s="320"/>
-      <c r="J29" s="321"/>
+      <c r="G29" s="304"/>
+      <c r="H29" s="305"/>
+      <c r="I29" s="316"/>
+      <c r="J29" s="317"/>
       <c r="K29" s="83"/>
       <c r="L29" s="83"/>
       <c r="P29" s="66"/>
@@ -9266,33 +9266,33 @@
       <c r="A31" s="66"/>
       <c r="B31" s="66"/>
       <c r="C31" s="66"/>
-      <c r="F31" s="322" t="s">
+      <c r="F31" s="318" t="s">
         <v>284</v>
       </c>
       <c r="G31" s="91">
         <v>1</v>
       </c>
-      <c r="H31" s="297"/>
-      <c r="I31" s="297"/>
-      <c r="J31" s="297"/>
-      <c r="K31" s="297"/>
-      <c r="L31" s="298"/>
+      <c r="H31" s="321"/>
+      <c r="I31" s="321"/>
+      <c r="J31" s="321"/>
+      <c r="K31" s="321"/>
+      <c r="L31" s="322"/>
       <c r="P31" s="66"/>
       <c r="Q31" s="66"/>
     </row>
-    <row r="32" spans="1:17" s="63" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:17" s="63" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A32" s="66"/>
       <c r="B32" s="66"/>
       <c r="C32" s="66"/>
-      <c r="F32" s="323"/>
+      <c r="F32" s="319"/>
       <c r="G32" s="84">
         <v>2</v>
       </c>
-      <c r="H32" s="299"/>
-      <c r="I32" s="299"/>
-      <c r="J32" s="299"/>
-      <c r="K32" s="299"/>
-      <c r="L32" s="300"/>
+      <c r="H32" s="323"/>
+      <c r="I32" s="323"/>
+      <c r="J32" s="323"/>
+      <c r="K32" s="323"/>
+      <c r="L32" s="324"/>
       <c r="P32" s="66"/>
       <c r="Q32" s="66"/>
     </row>
@@ -9300,15 +9300,15 @@
       <c r="A33" s="66"/>
       <c r="B33" s="66"/>
       <c r="C33" s="66"/>
-      <c r="F33" s="324"/>
+      <c r="F33" s="320"/>
       <c r="G33" s="92">
         <v>3</v>
       </c>
-      <c r="H33" s="325"/>
-      <c r="I33" s="325"/>
-      <c r="J33" s="325"/>
-      <c r="K33" s="325"/>
-      <c r="L33" s="326"/>
+      <c r="H33" s="287"/>
+      <c r="I33" s="287"/>
+      <c r="J33" s="287"/>
+      <c r="K33" s="287"/>
+      <c r="L33" s="288"/>
       <c r="P33" s="66"/>
       <c r="Q33" s="66"/>
     </row>
@@ -9354,7 +9354,7 @@
       <c r="P36" s="66"/>
       <c r="Q36" s="66"/>
     </row>
-    <row r="37" spans="1:17" s="63" customFormat="1" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="37" spans="1:17" s="63" customFormat="1" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A37" s="66"/>
       <c r="B37" s="66"/>
       <c r="C37" s="66"/>
@@ -9368,44 +9368,44 @@
       <c r="P37" s="66"/>
       <c r="Q37" s="66"/>
     </row>
-    <row r="38" spans="1:17" s="63" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:17" s="63" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A38" s="66"/>
       <c r="B38" s="66"/>
       <c r="C38" s="66"/>
-      <c r="F38" s="315" t="s">
+      <c r="F38" s="311" t="s">
         <v>261</v>
       </c>
-      <c r="G38" s="316"/>
-      <c r="H38" s="316"/>
-      <c r="I38" s="316"/>
-      <c r="J38" s="316"/>
-      <c r="K38" s="316"/>
-      <c r="L38" s="317"/>
+      <c r="G38" s="312"/>
+      <c r="H38" s="312"/>
+      <c r="I38" s="312"/>
+      <c r="J38" s="312"/>
+      <c r="K38" s="312"/>
+      <c r="L38" s="313"/>
       <c r="P38" s="66"/>
       <c r="Q38" s="66"/>
     </row>
-    <row r="39" spans="1:17" s="63" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:17" s="63" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A39" s="66"/>
       <c r="B39" s="66"/>
       <c r="C39" s="66"/>
       <c r="F39" s="78" t="s">
         <v>257</v>
       </c>
-      <c r="G39" s="308">
+      <c r="G39" s="306">
         <f ca="1">G14</f>
-        <v>46180</v>
-      </c>
-      <c r="H39" s="308"/>
-      <c r="I39" s="309" t="s">
+        <v>46183</v>
+      </c>
+      <c r="H39" s="306"/>
+      <c r="I39" s="307" t="s">
         <v>282</v>
       </c>
-      <c r="J39" s="309"/>
-      <c r="K39" s="309"/>
-      <c r="L39" s="310"/>
+      <c r="J39" s="307"/>
+      <c r="K39" s="307"/>
+      <c r="L39" s="308"/>
       <c r="P39" s="66"/>
       <c r="Q39" s="66"/>
     </row>
-    <row r="40" spans="1:17" s="63" customFormat="1" ht="18" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:17" s="63" customFormat="1" ht="17.399999999999999" x14ac:dyDescent="0.3">
       <c r="A40" s="66"/>
       <c r="B40" s="66"/>
       <c r="C40" s="66"/>
@@ -9413,40 +9413,40 @@
         <f>G11</f>
         <v> RPNC1-4240426</v>
       </c>
-      <c r="G40" s="311" t="s">
+      <c r="G40" s="290" t="s">
         <v>258</v>
       </c>
-      <c r="H40" s="311"/>
-      <c r="I40" s="311" t="str">
+      <c r="H40" s="290"/>
+      <c r="I40" s="290" t="str">
         <f>G12</f>
         <v> CAJAS ITZEP, RAFAEL SALVADOR</v>
       </c>
-      <c r="J40" s="311"/>
-      <c r="K40" s="311" t="s">
+      <c r="J40" s="290"/>
+      <c r="K40" s="290" t="s">
         <v>259</v>
       </c>
-      <c r="L40" s="312"/>
+      <c r="L40" s="291"/>
       <c r="P40" s="66"/>
       <c r="Q40" s="66"/>
     </row>
-    <row r="41" spans="1:17" s="63" customFormat="1" ht="18" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:17" s="63" customFormat="1" ht="17.399999999999999" x14ac:dyDescent="0.3">
       <c r="A41" s="66"/>
       <c r="B41" s="66"/>
       <c r="C41" s="66"/>
       <c r="F41" s="80" t="s">
         <v>264</v>
       </c>
-      <c r="G41" s="311" t="s">
+      <c r="G41" s="290" t="s">
         <v>260</v>
       </c>
-      <c r="H41" s="311"/>
-      <c r="I41" s="311"/>
-      <c r="J41" s="313" t="str">
+      <c r="H41" s="290"/>
+      <c r="I41" s="290"/>
+      <c r="J41" s="309" t="str">
         <f>G13</f>
         <v> 8va AVENIDA 0-10</v>
       </c>
-      <c r="K41" s="313"/>
-      <c r="L41" s="314"/>
+      <c r="K41" s="309"/>
+      <c r="L41" s="310"/>
       <c r="P41" s="66"/>
       <c r="Q41" s="66"/>
     </row>
@@ -9454,61 +9454,61 @@
       <c r="A42" s="66"/>
       <c r="B42" s="66"/>
       <c r="C42" s="66"/>
-      <c r="F42" s="327" t="s">
+      <c r="F42" s="289" t="s">
         <v>286</v>
       </c>
-      <c r="G42" s="311"/>
-      <c r="H42" s="311"/>
-      <c r="I42" s="311"/>
-      <c r="J42" s="311"/>
-      <c r="K42" s="311"/>
-      <c r="L42" s="312"/>
+      <c r="G42" s="290"/>
+      <c r="H42" s="290"/>
+      <c r="I42" s="290"/>
+      <c r="J42" s="290"/>
+      <c r="K42" s="290"/>
+      <c r="L42" s="291"/>
       <c r="P42" s="66"/>
       <c r="Q42" s="66"/>
     </row>
-    <row r="43" spans="1:17" s="63" customFormat="1" ht="18" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:17" s="63" customFormat="1" ht="17.399999999999999" x14ac:dyDescent="0.25">
       <c r="A43" s="66"/>
       <c r="B43" s="66"/>
       <c r="C43" s="66"/>
       <c r="D43" s="77"/>
       <c r="E43" s="77"/>
-      <c r="F43" s="328" t="s">
+      <c r="F43" s="292" t="s">
         <v>287</v>
       </c>
-      <c r="G43" s="329"/>
-      <c r="H43" s="329"/>
-      <c r="I43" s="329"/>
-      <c r="J43" s="329"/>
-      <c r="K43" s="329"/>
-      <c r="L43" s="330"/>
+      <c r="G43" s="293"/>
+      <c r="H43" s="293"/>
+      <c r="I43" s="293"/>
+      <c r="J43" s="293"/>
+      <c r="K43" s="293"/>
+      <c r="L43" s="294"/>
       <c r="M43" s="77"/>
       <c r="N43" s="77"/>
       <c r="O43" s="77"/>
       <c r="P43" s="66"/>
       <c r="Q43" s="66"/>
     </row>
-    <row r="44" spans="1:17" s="63" customFormat="1" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:17" s="63" customFormat="1" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A44" s="66"/>
       <c r="B44" s="66"/>
       <c r="C44" s="66"/>
       <c r="D44" s="67"/>
       <c r="E44" s="67"/>
-      <c r="F44" s="331" t="s">
+      <c r="F44" s="295" t="s">
         <v>288</v>
       </c>
-      <c r="G44" s="332"/>
-      <c r="H44" s="332"/>
-      <c r="I44" s="332"/>
-      <c r="J44" s="332"/>
-      <c r="K44" s="332"/>
-      <c r="L44" s="333"/>
+      <c r="G44" s="296"/>
+      <c r="H44" s="296"/>
+      <c r="I44" s="296"/>
+      <c r="J44" s="296"/>
+      <c r="K44" s="296"/>
+      <c r="L44" s="297"/>
       <c r="M44" s="67"/>
       <c r="N44" s="67"/>
       <c r="O44" s="67"/>
       <c r="P44" s="66"/>
       <c r="Q44" s="66"/>
     </row>
-    <row r="45" spans="1:17" s="63" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:17" s="63" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A45" s="66"/>
       <c r="B45" s="66"/>
       <c r="C45" s="66"/>
@@ -9527,45 +9527,45 @@
       <c r="P45" s="66"/>
       <c r="Q45" s="66"/>
     </row>
-    <row r="46" spans="1:17" s="63" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:17" s="63" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A46" s="66"/>
       <c r="B46" s="66"/>
       <c r="C46" s="66"/>
       <c r="D46" s="67"/>
       <c r="E46" s="67"/>
-      <c r="F46" s="240"/>
-      <c r="G46" s="240"/>
-      <c r="H46" s="240"/>
-      <c r="I46" s="240"/>
-      <c r="J46" s="240"/>
-      <c r="K46" s="240"/>
-      <c r="L46" s="240"/>
+      <c r="F46" s="258"/>
+      <c r="G46" s="258"/>
+      <c r="H46" s="258"/>
+      <c r="I46" s="258"/>
+      <c r="J46" s="258"/>
+      <c r="K46" s="258"/>
+      <c r="L46" s="258"/>
       <c r="M46" s="67"/>
       <c r="N46" s="67"/>
       <c r="O46" s="67"/>
       <c r="P46" s="66"/>
       <c r="Q46" s="66"/>
     </row>
-    <row r="47" spans="1:17" s="63" customFormat="1" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:17" s="63" customFormat="1" ht="45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A47" s="66"/>
       <c r="B47" s="66"/>
       <c r="C47" s="66"/>
       <c r="D47" s="67"/>
       <c r="E47" s="67"/>
-      <c r="F47" s="240"/>
-      <c r="G47" s="240"/>
-      <c r="H47" s="240"/>
-      <c r="I47" s="240"/>
-      <c r="J47" s="240"/>
-      <c r="K47" s="240"/>
-      <c r="L47" s="240"/>
+      <c r="F47" s="258"/>
+      <c r="G47" s="258"/>
+      <c r="H47" s="258"/>
+      <c r="I47" s="258"/>
+      <c r="J47" s="258"/>
+      <c r="K47" s="258"/>
+      <c r="L47" s="258"/>
       <c r="M47" s="67"/>
       <c r="N47" s="67"/>
       <c r="O47" s="67"/>
       <c r="P47" s="66"/>
       <c r="Q47" s="66"/>
     </row>
-    <row r="48" spans="1:17" s="63" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:17" s="63" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A48" s="66"/>
       <c r="B48" s="66"/>
       <c r="C48" s="66"/>
@@ -9584,7 +9584,7 @@
       <c r="P48" s="66"/>
       <c r="Q48" s="66"/>
     </row>
-    <row r="49" spans="1:17" s="63" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:17" s="63" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A49" s="66"/>
       <c r="B49" s="66"/>
       <c r="C49" s="66"/>
@@ -9603,29 +9603,29 @@
       <c r="P49" s="66"/>
       <c r="Q49" s="66"/>
     </row>
-    <row r="50" spans="1:17" s="63" customFormat="1" ht="18" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:17" s="63" customFormat="1" ht="16.8" x14ac:dyDescent="0.25">
       <c r="A50" s="66"/>
       <c r="B50" s="66"/>
       <c r="C50" s="66"/>
-      <c r="F50" s="290"/>
-      <c r="G50" s="290"/>
-      <c r="H50" s="290"/>
+      <c r="F50" s="298"/>
+      <c r="G50" s="298"/>
+      <c r="H50" s="298"/>
       <c r="P50" s="66"/>
       <c r="Q50" s="66"/>
     </row>
-    <row r="51" spans="1:17" s="63" customFormat="1" ht="19.5" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:17" s="63" customFormat="1" ht="21" x14ac:dyDescent="0.35">
       <c r="A51" s="64"/>
       <c r="B51" s="64"/>
       <c r="C51" s="64"/>
       <c r="D51" s="65"/>
       <c r="E51" s="65"/>
-      <c r="F51" s="290"/>
-      <c r="G51" s="290"/>
-      <c r="H51" s="290"/>
+      <c r="F51" s="298"/>
+      <c r="G51" s="298"/>
+      <c r="H51" s="298"/>
       <c r="P51" s="64"/>
       <c r="Q51" s="64"/>
     </row>
-    <row r="52" spans="1:17" s="63" customFormat="1" ht="19.5" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:17" s="63" customFormat="1" ht="21" x14ac:dyDescent="0.35">
       <c r="A52" s="64"/>
       <c r="B52" s="64"/>
       <c r="C52" s="64"/>
@@ -9634,7 +9634,7 @@
       <c r="P52" s="64"/>
       <c r="Q52" s="64"/>
     </row>
-    <row r="53" spans="1:17" ht="19.5" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:17" ht="21" x14ac:dyDescent="0.35">
       <c r="A53" s="64"/>
       <c r="B53" s="64"/>
       <c r="C53" s="64"/>
@@ -9653,7 +9653,7 @@
       <c r="P53" s="64"/>
       <c r="Q53" s="64"/>
     </row>
-    <row r="54" spans="1:17" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:17" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A54" s="59"/>
       <c r="B54" s="59"/>
       <c r="C54" s="59"/>
@@ -9672,7 +9672,7 @@
       <c r="P54" s="59"/>
       <c r="Q54" s="59"/>
     </row>
-    <row r="55" spans="1:17" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:17" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A55" s="59"/>
       <c r="B55" s="59"/>
       <c r="C55" s="59"/>
@@ -9691,7 +9691,7 @@
       <c r="P55" s="59"/>
       <c r="Q55" s="59"/>
     </row>
-    <row r="56" spans="1:17" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:17" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A56" s="59"/>
       <c r="B56" s="59"/>
       <c r="C56" s="59"/>
@@ -9710,7 +9710,7 @@
       <c r="P56" s="59"/>
       <c r="Q56" s="59"/>
     </row>
-    <row r="57" spans="1:17" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:17" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A57" s="59"/>
       <c r="B57" s="59"/>
       <c r="C57" s="59"/>
@@ -9729,11 +9729,11 @@
       <c r="P57" s="59"/>
       <c r="Q57" s="59"/>
     </row>
-    <row r="58" spans="1:17" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:17" ht="13.8" x14ac:dyDescent="0.25">
       <c r="C58" s="59"/>
       <c r="P58" s="59"/>
     </row>
-    <row r="59" spans="1:17" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:17" ht="13.8" x14ac:dyDescent="0.25">
       <c r="C59" s="62"/>
       <c r="P59" s="59"/>
     </row>
@@ -9832,11 +9832,22 @@
     </row>
   </sheetData>
   <mergeCells count="37">
-    <mergeCell ref="H33:L33"/>
-    <mergeCell ref="F42:L42"/>
-    <mergeCell ref="F43:L43"/>
-    <mergeCell ref="F44:L44"/>
-    <mergeCell ref="F46:L47"/>
+    <mergeCell ref="G12:J12"/>
+    <mergeCell ref="G2:I2"/>
+    <mergeCell ref="G4:I4"/>
+    <mergeCell ref="G6:I7"/>
+    <mergeCell ref="F9:L9"/>
+    <mergeCell ref="G11:J11"/>
+    <mergeCell ref="H31:L31"/>
+    <mergeCell ref="H32:L32"/>
+    <mergeCell ref="F20:L20"/>
+    <mergeCell ref="G22:J22"/>
+    <mergeCell ref="G13:J13"/>
+    <mergeCell ref="G14:J14"/>
+    <mergeCell ref="G15:J15"/>
+    <mergeCell ref="G16:J16"/>
+    <mergeCell ref="G17:J17"/>
+    <mergeCell ref="G18:J18"/>
     <mergeCell ref="F50:H50"/>
     <mergeCell ref="F51:H51"/>
     <mergeCell ref="G23:J23"/>
@@ -9853,22 +9864,11 @@
     <mergeCell ref="F38:L38"/>
     <mergeCell ref="I28:J29"/>
     <mergeCell ref="F31:F33"/>
-    <mergeCell ref="H31:L31"/>
-    <mergeCell ref="H32:L32"/>
-    <mergeCell ref="F20:L20"/>
-    <mergeCell ref="G22:J22"/>
-    <mergeCell ref="G13:J13"/>
-    <mergeCell ref="G14:J14"/>
-    <mergeCell ref="G15:J15"/>
-    <mergeCell ref="G16:J16"/>
-    <mergeCell ref="G17:J17"/>
-    <mergeCell ref="G18:J18"/>
-    <mergeCell ref="G12:J12"/>
-    <mergeCell ref="G2:I2"/>
-    <mergeCell ref="G4:I4"/>
-    <mergeCell ref="G6:I7"/>
-    <mergeCell ref="F9:L9"/>
-    <mergeCell ref="G11:J11"/>
+    <mergeCell ref="H33:L33"/>
+    <mergeCell ref="F42:L42"/>
+    <mergeCell ref="F43:L43"/>
+    <mergeCell ref="F44:L44"/>
+    <mergeCell ref="F46:L47"/>
   </mergeCells>
   <printOptions horizontalCentered="1" verticalCentered="1"/>
   <pageMargins left="0.23622047244094491" right="0.23622047244094491" top="0" bottom="0.35433070866141736" header="0.31496062992125984" footer="0.31496062992125984"/>
@@ -9995,22 +9995,22 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0600-000000000000}">
   <sheetPr codeName="Hoja7"/>
   <dimension ref="A11:R54"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="4.140625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="2.42578125" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.28515625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="4.140625" customWidth="1"/>
-    <col min="6" max="6" width="9.28515625" customWidth="1"/>
+    <col min="1" max="1" width="4.109375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="2.44140625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="14.33203125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="4.109375" customWidth="1"/>
+    <col min="6" max="6" width="9.33203125" customWidth="1"/>
     <col min="8" max="8" width="5" customWidth="1"/>
-    <col min="10" max="10" width="10.85546875" customWidth="1"/>
-    <col min="11" max="11" width="15.42578125" customWidth="1"/>
-    <col min="12" max="12" width="10.85546875" customWidth="1"/>
-    <col min="13" max="13" width="22.28515625" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="17.42578125" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="10.88671875" customWidth="1"/>
+    <col min="11" max="11" width="15.44140625" customWidth="1"/>
+    <col min="12" max="12" width="10.88671875" customWidth="1"/>
+    <col min="13" max="13" width="22.33203125" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="17.44140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="11" spans="1:18" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:18" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A11" s="197"/>
       <c r="B11" s="197"/>
       <c r="C11" s="197"/>
@@ -10023,7 +10023,7 @@
       <c r="H11" s="336"/>
       <c r="I11" s="336"/>
     </row>
-    <row r="12" spans="1:18" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:18" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A12" s="197"/>
       <c r="B12" s="197"/>
       <c r="C12" s="197"/>
@@ -10034,12 +10034,12 @@
       <c r="H12" s="336"/>
       <c r="I12" s="336"/>
     </row>
-    <row r="13" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:18" x14ac:dyDescent="0.3">
       <c r="O13" t="s">
         <v>357</v>
       </c>
     </row>
-    <row r="14" spans="1:18" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:18" ht="24" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A14" s="197" t="s">
         <v>338</v>
       </c>
@@ -10057,7 +10057,7 @@
         <v>355</v>
       </c>
     </row>
-    <row r="15" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A15" s="197"/>
       <c r="B15" s="197"/>
       <c r="C15" s="197"/>
@@ -10075,18 +10075,18 @@
       </c>
       <c r="O15">
         <f>'FORMATO  FACT'!J35-'FORMATO  FACT'!G35</f>
-        <v>66026</v>
+        <v>3804</v>
       </c>
       <c r="Q15">
         <f>N15*O15</f>
-        <v>6602600</v>
+        <v>380400</v>
       </c>
       <c r="R15">
         <f>IF((Q15)&lt;0,0,Q15)</f>
-        <v>6602600</v>
-      </c>
-    </row>
-    <row r="16" spans="1:18" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+        <v>380400</v>
+      </c>
+    </row>
+    <row r="16" spans="1:18" ht="24" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A16" s="197" t="s">
         <v>339</v>
       </c>
@@ -10116,7 +10116,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="1:18" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:18" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="F17" s="197"/>
       <c r="G17" s="197"/>
       <c r="H17" s="197"/>
@@ -10140,7 +10140,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="18" spans="1:18" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:18" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A18" s="197"/>
       <c r="B18" s="197"/>
       <c r="C18" s="197"/>
@@ -10162,7 +10162,7 @@
         <v>504.14</v>
       </c>
     </row>
-    <row r="19" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A19" s="197"/>
       <c r="B19" s="197"/>
       <c r="C19" s="197"/>
@@ -10180,10 +10180,10 @@
       </c>
       <c r="R19">
         <f ca="1">SUM(R15:R18)</f>
-        <v>6603104.1399999997</v>
-      </c>
-    </row>
-    <row r="20" spans="1:18" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+        <v>380904.14</v>
+      </c>
+    </row>
+    <row r="20" spans="1:18" ht="24.9" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A20" s="197" t="s">
         <v>340</v>
       </c>
@@ -10205,10 +10205,10 @@
       </c>
       <c r="R20">
         <f ca="1">R19*Q20</f>
-        <v>1650776.0349999999</v>
-      </c>
-    </row>
-    <row r="21" spans="1:18" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+        <v>95226.035000000003</v>
+      </c>
+    </row>
+    <row r="21" spans="1:18" ht="24.9" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A21" s="337" t="s">
         <v>348</v>
       </c>
@@ -10223,7 +10223,7 @@
       <c r="J21" s="337"/>
       <c r="K21" s="337"/>
     </row>
-    <row r="22" spans="1:18" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:18" ht="24.9" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A22" s="337" t="s">
         <v>349</v>
       </c>
@@ -10239,7 +10239,7 @@
       <c r="K22" s="337"/>
       <c r="N22" s="168"/>
     </row>
-    <row r="23" spans="1:18" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:18" ht="24.9" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A23" s="197" t="s">
         <v>346</v>
       </c>
@@ -10247,7 +10247,7 @@
       <c r="C23" s="197"/>
       <c r="D23" s="202">
         <f ca="1">R20</f>
-        <v>1650776.0349999999</v>
+        <v>95226.035000000003</v>
       </c>
       <c r="E23" s="337" t="s">
         <v>356</v>
@@ -10260,7 +10260,7 @@
       <c r="K23" s="337"/>
       <c r="P23" s="201"/>
     </row>
-    <row r="24" spans="1:18" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:18" ht="24.9" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A24" s="199" t="str">
         <f>FACTIBILIDAD!D12</f>
         <v xml:space="preserve">UNIFAMILIAR </v>
@@ -10281,7 +10281,7 @@
       <c r="J24" s="338"/>
       <c r="K24" s="338"/>
     </row>
-    <row r="25" spans="1:18" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:18" ht="24.9" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A25" s="197" t="s">
         <v>342</v>
       </c>
@@ -10296,7 +10296,7 @@
       <c r="J25" s="196"/>
       <c r="K25" s="196"/>
     </row>
-    <row r="26" spans="1:18" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:18" ht="24.9" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A26" s="335" t="s">
         <v>343</v>
       </c>
@@ -10311,7 +10311,7 @@
       </c>
       <c r="I26" s="197"/>
     </row>
-    <row r="27" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A27" s="197"/>
       <c r="B27" s="197"/>
       <c r="C27" s="197"/>
@@ -10322,7 +10322,7 @@
       <c r="H27" s="197"/>
       <c r="I27" s="197"/>
     </row>
-    <row r="28" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A28" s="197"/>
       <c r="B28" s="197"/>
       <c r="C28" s="197"/>
@@ -10333,7 +10333,7 @@
       <c r="H28" s="197"/>
       <c r="I28" s="197"/>
     </row>
-    <row r="29" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A29" s="197"/>
       <c r="B29" s="197"/>
       <c r="C29" s="197"/>
@@ -10344,7 +10344,7 @@
       <c r="H29" s="197"/>
       <c r="I29" s="197"/>
     </row>
-    <row r="30" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A30" s="197"/>
       <c r="B30" s="197"/>
       <c r="C30" s="197"/>
@@ -10355,7 +10355,7 @@
       <c r="H30" s="197"/>
       <c r="I30" s="197"/>
     </row>
-    <row r="31" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A31" s="197"/>
       <c r="B31" s="197"/>
       <c r="C31" s="197"/>
@@ -10366,7 +10366,7 @@
       <c r="H31" s="197"/>
       <c r="I31" s="197"/>
     </row>
-    <row r="32" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A32" s="197"/>
       <c r="B32" s="197"/>
       <c r="C32" s="197"/>
@@ -10379,7 +10379,7 @@
       <c r="H32" s="198"/>
       <c r="I32" s="197"/>
     </row>
-    <row r="33" spans="1:14" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:14" ht="24.9" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A33" s="197"/>
       <c r="B33" s="197"/>
       <c r="C33" s="197"/>
@@ -10390,7 +10390,7 @@
       <c r="H33" s="197"/>
       <c r="I33" s="197"/>
     </row>
-    <row r="34" spans="1:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A34" s="197"/>
       <c r="B34" s="197"/>
       <c r="C34" s="197"/>
@@ -10401,7 +10401,7 @@
       <c r="H34" s="197"/>
       <c r="I34" s="197"/>
     </row>
-    <row r="35" spans="1:14" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:14" ht="24.9" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A35" s="197" t="s">
         <v>345</v>
       </c>
@@ -10414,7 +10414,7 @@
       <c r="H35" s="197"/>
       <c r="I35" s="197"/>
     </row>
-    <row r="36" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A36" s="197"/>
       <c r="B36" s="197"/>
       <c r="C36" s="197"/>
@@ -10425,7 +10425,7 @@
       <c r="H36" s="197"/>
       <c r="I36" s="197"/>
     </row>
-    <row r="37" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A37" s="197"/>
       <c r="B37" s="197"/>
       <c r="C37" s="197"/>
@@ -10436,7 +10436,7 @@
       <c r="H37" s="197"/>
       <c r="I37" s="197"/>
     </row>
-    <row r="38" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A38" s="197"/>
       <c r="B38" s="197"/>
       <c r="C38" s="197"/>
@@ -10447,7 +10447,7 @@
       <c r="H38" s="197"/>
       <c r="I38" s="197"/>
     </row>
-    <row r="39" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A39" s="197"/>
       <c r="B39" s="197"/>
       <c r="C39" s="197"/>
@@ -10458,7 +10458,7 @@
       <c r="H39" s="197"/>
       <c r="I39" s="197"/>
     </row>
-    <row r="40" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A40" s="197"/>
       <c r="B40" s="197"/>
       <c r="C40" s="197"/>
@@ -10469,7 +10469,7 @@
       <c r="H40" s="197"/>
       <c r="I40" s="197"/>
     </row>
-    <row r="41" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A41" s="197"/>
       <c r="B41" s="197"/>
       <c r="C41" s="197"/>
@@ -10480,7 +10480,7 @@
       <c r="H41" s="197"/>
       <c r="I41" s="197"/>
     </row>
-    <row r="43" spans="1:14" ht="21" x14ac:dyDescent="0.35">
+    <row r="43" spans="1:14" ht="21" x14ac:dyDescent="0.4">
       <c r="A43" s="195"/>
       <c r="B43" s="195"/>
       <c r="C43" s="195"/>
@@ -10496,7 +10496,7 @@
       <c r="M43" s="195"/>
       <c r="N43" s="195"/>
     </row>
-    <row r="44" spans="1:14" ht="21" x14ac:dyDescent="0.35">
+    <row r="44" spans="1:14" ht="21" x14ac:dyDescent="0.4">
       <c r="A44" s="195"/>
       <c r="B44" s="195"/>
       <c r="C44" s="195"/>
@@ -10512,7 +10512,7 @@
       <c r="M44" s="195"/>
       <c r="N44" s="195"/>
     </row>
-    <row r="45" spans="1:14" ht="21" x14ac:dyDescent="0.35">
+    <row r="45" spans="1:14" ht="21" x14ac:dyDescent="0.4">
       <c r="A45" s="195"/>
       <c r="B45" s="195"/>
       <c r="C45" s="195"/>
@@ -10528,7 +10528,7 @@
       <c r="M45" s="195"/>
       <c r="N45" s="195"/>
     </row>
-    <row r="46" spans="1:14" ht="21" x14ac:dyDescent="0.35">
+    <row r="46" spans="1:14" ht="21" x14ac:dyDescent="0.4">
       <c r="A46" s="195"/>
       <c r="B46" s="195"/>
       <c r="C46" s="195"/>
@@ -10544,7 +10544,7 @@
       <c r="M46" s="195"/>
       <c r="N46" s="195"/>
     </row>
-    <row r="47" spans="1:14" ht="21" x14ac:dyDescent="0.35">
+    <row r="47" spans="1:14" ht="21" x14ac:dyDescent="0.4">
       <c r="A47" s="195"/>
       <c r="B47" s="195"/>
       <c r="C47" s="195"/>
@@ -10560,7 +10560,7 @@
       <c r="M47" s="195"/>
       <c r="N47" s="195"/>
     </row>
-    <row r="48" spans="1:14" ht="21" x14ac:dyDescent="0.35">
+    <row r="48" spans="1:14" ht="21" x14ac:dyDescent="0.4">
       <c r="A48" s="195"/>
       <c r="B48" s="195"/>
       <c r="C48" s="195"/>
@@ -10576,7 +10576,7 @@
       <c r="M48" s="195"/>
       <c r="N48" s="195"/>
     </row>
-    <row r="49" spans="1:14" ht="21" x14ac:dyDescent="0.35">
+    <row r="49" spans="1:14" ht="21" x14ac:dyDescent="0.4">
       <c r="A49" s="195"/>
       <c r="B49" s="195"/>
       <c r="C49" s="195"/>
@@ -10592,7 +10592,7 @@
       <c r="M49" s="195"/>
       <c r="N49" s="195"/>
     </row>
-    <row r="50" spans="1:14" ht="21" x14ac:dyDescent="0.35">
+    <row r="50" spans="1:14" ht="21" x14ac:dyDescent="0.4">
       <c r="A50" s="195"/>
       <c r="B50" s="195"/>
       <c r="C50" s="195"/>
@@ -10608,7 +10608,7 @@
       <c r="M50" s="195"/>
       <c r="N50" s="195"/>
     </row>
-    <row r="51" spans="1:14" ht="21" x14ac:dyDescent="0.35">
+    <row r="51" spans="1:14" ht="21" x14ac:dyDescent="0.4">
       <c r="A51" s="195"/>
       <c r="B51" s="195"/>
       <c r="C51" s="195"/>
@@ -10624,7 +10624,7 @@
       <c r="M51" s="195"/>
       <c r="N51" s="195"/>
     </row>
-    <row r="52" spans="1:14" ht="21" x14ac:dyDescent="0.35">
+    <row r="52" spans="1:14" ht="21" x14ac:dyDescent="0.4">
       <c r="A52" s="195"/>
       <c r="B52" s="195"/>
       <c r="C52" s="195"/>
@@ -10640,7 +10640,7 @@
       <c r="M52" s="195"/>
       <c r="N52" s="195"/>
     </row>
-    <row r="53" spans="1:14" ht="21" x14ac:dyDescent="0.35">
+    <row r="53" spans="1:14" ht="21" x14ac:dyDescent="0.4">
       <c r="A53" s="195"/>
       <c r="B53" s="195"/>
       <c r="C53" s="195"/>
@@ -10656,7 +10656,7 @@
       <c r="M53" s="195"/>
       <c r="N53" s="195"/>
     </row>
-    <row r="54" spans="1:14" ht="21" x14ac:dyDescent="0.35">
+    <row r="54" spans="1:14" ht="21" x14ac:dyDescent="0.4">
       <c r="A54" s="195"/>
       <c r="B54" s="195"/>
       <c r="C54" s="195"/>
@@ -10692,20 +10692,20 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0700-000000000000}">
   <sheetPr codeName="Hoja8"/>
   <dimension ref="A1:AD121"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="18.28515625" customWidth="1"/>
-    <col min="5" max="5" width="12.28515625" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="103.42578125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="18.33203125" customWidth="1"/>
+    <col min="5" max="5" width="12.33203125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="103.44140625" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="7" customWidth="1"/>
-    <col min="9" max="9" width="8.42578125" customWidth="1"/>
-    <col min="10" max="10" width="8.85546875" customWidth="1"/>
-    <col min="11" max="11" width="9.85546875" customWidth="1"/>
+    <col min="9" max="9" width="8.44140625" customWidth="1"/>
+    <col min="10" max="10" width="8.88671875" customWidth="1"/>
+    <col min="11" max="11" width="9.88671875" customWidth="1"/>
     <col min="19" max="19" width="14" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="14.7109375" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="14.6640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:30" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:30" ht="15.6" x14ac:dyDescent="0.3">
       <c r="G1" s="27"/>
       <c r="H1" s="339" t="s">
         <v>158</v>
@@ -10728,7 +10728,7 @@
       </c>
       <c r="U1" s="339"/>
     </row>
-    <row r="2" spans="1:30" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:30" ht="15.6" x14ac:dyDescent="0.3">
       <c r="G2" s="27"/>
       <c r="H2" s="339"/>
       <c r="I2" s="339"/>
@@ -10755,7 +10755,7 @@
       <c r="T2" s="339"/>
       <c r="U2" s="339"/>
     </row>
-    <row r="3" spans="1:30" ht="94.5" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:30" ht="78" x14ac:dyDescent="0.3">
       <c r="B3" s="4" t="s">
         <v>17</v>
       </c>
@@ -10808,7 +10808,7 @@
         <v>211</v>
       </c>
     </row>
-    <row r="4" spans="1:30" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:30" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="43">
         <v>1</v>
       </c>
@@ -10885,7 +10885,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="5" spans="1:30" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:30" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="43">
         <v>2</v>
       </c>
@@ -10962,7 +10962,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="6" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A6" s="43">
         <v>3</v>
       </c>
@@ -11039,7 +11039,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="7" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A7" s="43">
         <v>4</v>
       </c>
@@ -11116,7 +11116,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="8" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A8" s="43">
         <v>5</v>
       </c>
@@ -11193,7 +11193,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="9" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A9" s="43">
         <v>6</v>
       </c>
@@ -11270,7 +11270,7 @@
         <v>1.5</v>
       </c>
     </row>
-    <row r="10" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A10" s="43">
         <v>7</v>
       </c>
@@ -11344,7 +11344,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="11" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A11" s="11" t="s">
         <v>22</v>
       </c>
@@ -11418,7 +11418,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="12" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A12" s="11" t="s">
         <v>56</v>
       </c>
@@ -11426,7 +11426,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="13" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:30" x14ac:dyDescent="0.3">
       <c r="I13" t="s">
         <v>201</v>
       </c>
@@ -11434,7 +11434,7 @@
         <v>154</v>
       </c>
     </row>
-    <row r="14" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:30" x14ac:dyDescent="0.3">
       <c r="I14" t="s">
         <v>202</v>
       </c>
@@ -11442,7 +11442,7 @@
         <v>153</v>
       </c>
     </row>
-    <row r="15" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
         <v>59</v>
       </c>
@@ -11450,7 +11450,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="16" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
         <v>60</v>
       </c>
@@ -11458,7 +11458,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="17" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
         <v>61</v>
       </c>
@@ -11466,247 +11466,247 @@
         <v>225</v>
       </c>
     </row>
-    <row r="18" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
         <v>62</v>
       </c>
     </row>
-    <row r="19" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
         <v>63</v>
       </c>
     </row>
-    <row r="20" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
         <v>64</v>
       </c>
     </row>
-    <row r="21" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
         <v>65</v>
       </c>
     </row>
-    <row r="22" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
         <v>66</v>
       </c>
     </row>
-    <row r="23" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
         <v>67</v>
       </c>
     </row>
-    <row r="24" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
         <v>68</v>
       </c>
     </row>
-    <row r="25" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
         <v>72</v>
       </c>
     </row>
-    <row r="27" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="28" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
         <v>71</v>
       </c>
     </row>
-    <row r="30" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
         <v>76</v>
       </c>
     </row>
-    <row r="31" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
         <v>77</v>
       </c>
     </row>
-    <row r="32" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
         <v>78</v>
       </c>
     </row>
-    <row r="33" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
         <v>79</v>
       </c>
     </row>
-    <row r="34" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A34" t="s">
         <v>80</v>
       </c>
     </row>
-    <row r="35" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
         <v>81</v>
       </c>
     </row>
-    <row r="36" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
         <v>82</v>
       </c>
     </row>
-    <row r="37" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
         <v>83</v>
       </c>
     </row>
-    <row r="38" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A38" t="s">
         <v>84</v>
       </c>
     </row>
-    <row r="39" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A39" t="s">
         <v>85</v>
       </c>
     </row>
-    <row r="40" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A40" t="s">
         <v>72</v>
       </c>
     </row>
-    <row r="42" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A42" t="s">
         <v>92</v>
       </c>
     </row>
-    <row r="43" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A43" t="s">
         <v>93</v>
       </c>
     </row>
-    <row r="44" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A44" t="s">
         <v>105</v>
       </c>
     </row>
-    <row r="45" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A45" t="s">
         <v>106</v>
       </c>
     </row>
-    <row r="46" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A46" t="s">
         <v>107</v>
       </c>
     </row>
-    <row r="47" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A47" t="s">
         <v>108</v>
       </c>
     </row>
-    <row r="48" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A48" t="s">
         <v>109</v>
       </c>
     </row>
-    <row r="49" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A49" t="s">
         <v>110</v>
       </c>
     </row>
-    <row r="50" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A50" t="s">
         <v>111</v>
       </c>
     </row>
-    <row r="51" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A51" t="s">
         <v>112</v>
       </c>
     </row>
-    <row r="52" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A52" t="s">
         <v>113</v>
       </c>
     </row>
-    <row r="53" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A53" t="s">
         <v>114</v>
       </c>
     </row>
-    <row r="54" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A54" t="s">
         <v>115</v>
       </c>
     </row>
-    <row r="55" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A55" t="s">
         <v>116</v>
       </c>
     </row>
-    <row r="56" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A56" t="s">
         <v>94</v>
       </c>
     </row>
-    <row r="57" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A57" t="s">
         <v>95</v>
       </c>
     </row>
-    <row r="58" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A58" t="s">
         <v>96</v>
       </c>
     </row>
-    <row r="59" spans="1:1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A59" t="s">
         <v>97</v>
       </c>
     </row>
-    <row r="60" spans="1:1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A60" t="s">
         <v>98</v>
       </c>
     </row>
-    <row r="61" spans="1:1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:1" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A61" t="s">
         <v>99</v>
       </c>
     </row>
-    <row r="62" spans="1:1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:1" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A62" t="s">
         <v>100</v>
       </c>
     </row>
-    <row r="63" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A63" t="s">
         <v>101</v>
       </c>
     </row>
-    <row r="64" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A64" t="s">
         <v>102</v>
       </c>
     </row>
-    <row r="65" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A65" t="s">
         <v>103</v>
       </c>
     </row>
-    <row r="66" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A66" t="s">
         <v>104</v>
       </c>
     </row>
-    <row r="67" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A67" t="s">
         <v>72</v>
       </c>
     </row>
-    <row r="68" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:9" x14ac:dyDescent="0.3">
       <c r="E68" t="s">
         <v>119</v>
       </c>
     </row>
-    <row r="69" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A69" t="s">
         <v>119</v>
       </c>
@@ -11717,7 +11717,7 @@
         <v>131</v>
       </c>
     </row>
-    <row r="70" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A70" t="s">
         <v>177</v>
       </c>
@@ -11728,7 +11728,7 @@
         <v>132</v>
       </c>
     </row>
-    <row r="71" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A71" t="s">
         <v>178</v>
       </c>
@@ -11739,7 +11739,7 @@
         <v>133</v>
       </c>
     </row>
-    <row r="72" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:9" x14ac:dyDescent="0.3">
       <c r="G72" t="s">
         <v>122</v>
       </c>
@@ -11747,7 +11747,7 @@
         <v>134</v>
       </c>
     </row>
-    <row r="73" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:9" x14ac:dyDescent="0.3">
       <c r="G73" t="s">
         <v>123</v>
       </c>
@@ -11755,7 +11755,7 @@
         <v>135</v>
       </c>
     </row>
-    <row r="74" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:9" x14ac:dyDescent="0.3">
       <c r="G74" t="s">
         <v>124</v>
       </c>
@@ -11763,7 +11763,7 @@
         <v>136</v>
       </c>
     </row>
-    <row r="75" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:9" x14ac:dyDescent="0.3">
       <c r="G75" t="s">
         <v>125</v>
       </c>
@@ -11771,7 +11771,7 @@
         <v>137</v>
       </c>
     </row>
-    <row r="76" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:9" x14ac:dyDescent="0.3">
       <c r="G76" t="s">
         <v>126</v>
       </c>
@@ -11779,7 +11779,7 @@
         <v>138</v>
       </c>
     </row>
-    <row r="77" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:9" x14ac:dyDescent="0.3">
       <c r="G77" t="s">
         <v>127</v>
       </c>
@@ -11787,7 +11787,7 @@
         <v>139</v>
       </c>
     </row>
-    <row r="78" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:9" x14ac:dyDescent="0.3">
       <c r="G78" t="s">
         <v>128</v>
       </c>
@@ -11795,7 +11795,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="79" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:9" x14ac:dyDescent="0.3">
       <c r="G79" t="s">
         <v>129</v>
       </c>
@@ -11803,7 +11803,7 @@
         <v>141</v>
       </c>
     </row>
-    <row r="80" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="G80" t="s">
         <v>132</v>
       </c>
@@ -11811,7 +11811,7 @@
         <v>142</v>
       </c>
     </row>
-    <row r="81" spans="7:9" x14ac:dyDescent="0.25">
+    <row r="81" spans="7:9" x14ac:dyDescent="0.3">
       <c r="G81" t="s">
         <v>133</v>
       </c>
@@ -11819,7 +11819,7 @@
         <v>143</v>
       </c>
     </row>
-    <row r="82" spans="7:9" x14ac:dyDescent="0.25">
+    <row r="82" spans="7:9" x14ac:dyDescent="0.3">
       <c r="G82" t="s">
         <v>134</v>
       </c>
@@ -11827,7 +11827,7 @@
         <v>144</v>
       </c>
     </row>
-    <row r="83" spans="7:9" x14ac:dyDescent="0.25">
+    <row r="83" spans="7:9" x14ac:dyDescent="0.3">
       <c r="G83" t="s">
         <v>135</v>
       </c>
@@ -11835,7 +11835,7 @@
         <v>145</v>
       </c>
     </row>
-    <row r="84" spans="7:9" x14ac:dyDescent="0.25">
+    <row r="84" spans="7:9" x14ac:dyDescent="0.3">
       <c r="G84" t="s">
         <v>136</v>
       </c>
@@ -11843,7 +11843,7 @@
         <v>146</v>
       </c>
     </row>
-    <row r="85" spans="7:9" x14ac:dyDescent="0.25">
+    <row r="85" spans="7:9" x14ac:dyDescent="0.3">
       <c r="G85" t="s">
         <v>137</v>
       </c>
@@ -11851,7 +11851,7 @@
         <v>147</v>
       </c>
     </row>
-    <row r="86" spans="7:9" x14ac:dyDescent="0.25">
+    <row r="86" spans="7:9" x14ac:dyDescent="0.3">
       <c r="G86" t="s">
         <v>138</v>
       </c>
@@ -11859,7 +11859,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="87" spans="7:9" x14ac:dyDescent="0.25">
+    <row r="87" spans="7:9" x14ac:dyDescent="0.3">
       <c r="G87" t="s">
         <v>139</v>
       </c>
@@ -11867,7 +11867,7 @@
         <v>149</v>
       </c>
     </row>
-    <row r="88" spans="7:9" x14ac:dyDescent="0.25">
+    <row r="88" spans="7:9" x14ac:dyDescent="0.3">
       <c r="G88" t="s">
         <v>140</v>
       </c>
@@ -11875,7 +11875,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="89" spans="7:9" x14ac:dyDescent="0.25">
+    <row r="89" spans="7:9" x14ac:dyDescent="0.3">
       <c r="G89" t="s">
         <v>141</v>
       </c>
@@ -11883,7 +11883,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="90" spans="7:9" x14ac:dyDescent="0.25">
+    <row r="90" spans="7:9" x14ac:dyDescent="0.3">
       <c r="G90" t="s">
         <v>142</v>
       </c>
@@ -11891,117 +11891,117 @@
         <v>152</v>
       </c>
     </row>
-    <row r="91" spans="7:9" x14ac:dyDescent="0.25">
+    <row r="91" spans="7:9" x14ac:dyDescent="0.3">
       <c r="G91" t="s">
         <v>143</v>
       </c>
     </row>
-    <row r="92" spans="7:9" x14ac:dyDescent="0.25">
+    <row r="92" spans="7:9" x14ac:dyDescent="0.3">
       <c r="G92" t="s">
         <v>144</v>
       </c>
     </row>
-    <row r="93" spans="7:9" x14ac:dyDescent="0.25">
+    <row r="93" spans="7:9" x14ac:dyDescent="0.3">
       <c r="G93" t="s">
         <v>145</v>
       </c>
     </row>
-    <row r="94" spans="7:9" x14ac:dyDescent="0.25">
+    <row r="94" spans="7:9" x14ac:dyDescent="0.3">
       <c r="G94" t="s">
         <v>146</v>
       </c>
     </row>
-    <row r="95" spans="7:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="95" spans="7:9" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="G95" t="s">
         <v>147</v>
       </c>
     </row>
-    <row r="96" spans="7:9" x14ac:dyDescent="0.25">
+    <row r="96" spans="7:9" x14ac:dyDescent="0.3">
       <c r="G96" t="s">
         <v>148</v>
       </c>
     </row>
-    <row r="97" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="97" spans="7:7" x14ac:dyDescent="0.3">
       <c r="G97" t="s">
         <v>149</v>
       </c>
     </row>
-    <row r="98" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="98" spans="7:7" x14ac:dyDescent="0.3">
       <c r="G98" t="s">
         <v>150</v>
       </c>
     </row>
-    <row r="99" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="99" spans="7:7" x14ac:dyDescent="0.3">
       <c r="G99" t="s">
         <v>151</v>
       </c>
     </row>
-    <row r="100" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="100" spans="7:7" x14ac:dyDescent="0.3">
       <c r="G100" t="s">
         <v>152</v>
       </c>
     </row>
-    <row r="101" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="101" spans="7:7" x14ac:dyDescent="0.3">
       <c r="G101" s="1"/>
     </row>
-    <row r="102" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="102" spans="7:7" x14ac:dyDescent="0.3">
       <c r="G102" s="1"/>
     </row>
-    <row r="103" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="103" spans="7:7" x14ac:dyDescent="0.3">
       <c r="G103" s="1"/>
     </row>
-    <row r="104" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="104" spans="7:7" x14ac:dyDescent="0.3">
       <c r="G104" s="1"/>
     </row>
-    <row r="105" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="105" spans="7:7" x14ac:dyDescent="0.3">
       <c r="G105" s="1"/>
     </row>
-    <row r="106" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="106" spans="7:7" x14ac:dyDescent="0.3">
       <c r="G106" s="1"/>
     </row>
-    <row r="107" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="107" spans="7:7" x14ac:dyDescent="0.3">
       <c r="G107" s="1"/>
     </row>
-    <row r="108" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="108" spans="7:7" x14ac:dyDescent="0.3">
       <c r="G108" s="1"/>
     </row>
-    <row r="109" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="109" spans="7:7" x14ac:dyDescent="0.3">
       <c r="G109" s="1"/>
     </row>
-    <row r="110" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="110" spans="7:7" x14ac:dyDescent="0.3">
       <c r="G110" s="1"/>
     </row>
-    <row r="111" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="111" spans="7:7" x14ac:dyDescent="0.3">
       <c r="G111" s="1"/>
     </row>
-    <row r="112" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="112" spans="7:7" x14ac:dyDescent="0.3">
       <c r="G112" s="1"/>
     </row>
-    <row r="113" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="113" spans="7:7" x14ac:dyDescent="0.3">
       <c r="G113" s="1"/>
     </row>
-    <row r="114" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="114" spans="7:7" x14ac:dyDescent="0.3">
       <c r="G114" s="1"/>
     </row>
-    <row r="115" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="115" spans="7:7" x14ac:dyDescent="0.3">
       <c r="G115" s="1"/>
     </row>
-    <row r="116" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="116" spans="7:7" x14ac:dyDescent="0.3">
       <c r="G116" s="1"/>
     </row>
-    <row r="117" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="117" spans="7:7" x14ac:dyDescent="0.3">
       <c r="G117" s="1"/>
     </row>
-    <row r="118" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="118" spans="7:7" x14ac:dyDescent="0.3">
       <c r="G118" s="1"/>
     </row>
-    <row r="119" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="119" spans="7:7" x14ac:dyDescent="0.3">
       <c r="G119" s="1"/>
     </row>
-    <row r="120" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="120" spans="7:7" x14ac:dyDescent="0.3">
       <c r="G120" s="1"/>
     </row>
-    <row r="121" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="121" spans="7:7" x14ac:dyDescent="0.3">
       <c r="G121" s="1"/>
     </row>
   </sheetData>
@@ -12024,64 +12024,64 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0800-000000000000}">
   <sheetPr codeName="Hoja9"/>
   <dimension ref="B1:B12"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="1" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B1" s="21" t="s">
         <v>195</v>
       </c>
     </row>
-    <row r="2" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="2" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B2" s="21" t="s">
         <v>193</v>
       </c>
     </row>
-    <row r="3" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="3" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B3" s="21" t="s">
         <v>194</v>
       </c>
     </row>
-    <row r="4" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="4" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B4" s="21" t="s">
         <v>196</v>
       </c>
     </row>
-    <row r="5" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="5" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B5" s="21" t="s">
         <v>197</v>
       </c>
     </row>
-    <row r="6" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="6" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B6" s="21" t="s">
         <v>198</v>
       </c>
     </row>
-    <row r="7" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="7" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B7" s="21" t="s">
         <v>199</v>
       </c>
     </row>
-    <row r="8" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="8" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B8" s="21" t="s">
         <v>207</v>
       </c>
     </row>
-    <row r="9" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="9" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B9" s="21" t="s">
         <v>221</v>
       </c>
     </row>
-    <row r="10" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="10" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B10" s="21" t="s">
         <v>226</v>
       </c>
     </row>
-    <row r="11" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="11" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B11" s="21" t="s">
         <v>227</v>
       </c>
     </row>
-    <row r="12" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="12" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B12" s="21" t="s">
         <v>231</v>
       </c>
